--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -15,9 +15,6 @@
   <sheets>
     <sheet name="Apu's" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Apu''s'!$A$1:$N$52</definedName>
-  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -18683,7 +18683,9 @@
       <c r="I8" s="120"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="294"/>
+      <c r="A9" s="294" t="str">
+        <f>"Cuadrilla: "&amp;O4&amp;"   |   Unidad: "&amp;L4&amp;"   |   Jornada: "&amp;Q4&amp;" h   |   Rendimiento: "&amp;R4&amp;" "&amp;S4&amp;"   |   Consumo M.O.: "&amp;TEXT(Q4/R4,"0.00")&amp;" h/"&amp;L4</f>
+      </c>
       <c r="B9" s="294"/>
       <c r="C9" s="294"/>
       <c r="D9" s="1"/>
@@ -19207,7 +19209,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="49">
     <mergeCell ref="E52:F52"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A16:F16"/>
@@ -19256,6 +19258,7 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -10404,32 +10404,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>237075</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>600075</colOff>
-      <row>46</row>
-      <rowOff>66675</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 44"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>237075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 44"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="10362150"/>
           <a:ext cx="600075" cy="458250"/>
@@ -10441,35 +10441,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>110085</colOff>
-      <row>43</row>
-      <rowOff>256680</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>493125</colOff>
-      <row>45</row>
-      <rowOff>33120</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 38"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>110085</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>256680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>493125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>33120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 38"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="110085" y="10067430"/>
           <a:ext cx="383040" cy="405090"/>
@@ -10481,35 +10481,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>2747250</colOff>
-      <row>8</row>
-      <rowOff>141525</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Imagen 40"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2747250</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>141525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 40"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="4176000" cy="1656000"/>
@@ -10521,36 +10521,36 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>49468</colOff>
-      <row>43</row>
-      <rowOff>27346</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>553468</colOff>
-      <row>44</row>
-      <rowOff>8088</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Imagen 16"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>49468</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>27346</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>553468</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>8088</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Imagen 16"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="49468" y="9838096"/>
           <a:ext cx="504000" cy="295067"/>
@@ -10562,11 +10562,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="169" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="164">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1194,8 +1194,45 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="008A8F99"/>
-      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF17365D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF17365D"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF17365D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF17365D"/>
+      <sz val="16"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF17365D"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="77">
@@ -1652,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="400">
+  <borders count="410">
     <border>
       <left/>
       <right/>
@@ -3210,17 +3247,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB7C3D0"/>
       </left>
@@ -3600,80 +3626,6 @@
       <right/>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -4059,21 +4011,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
@@ -6087,93 +6024,305 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
         <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF17365D"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF17365D"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF17365D"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9E1F2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1F2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
+      <left style="thick">
         <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
+      </left>
+      <right style="thick">
         <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF17365D"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF17365D"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF17365D"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF17365D"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF17365D"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF17365D"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF17365D"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF17365D"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color theme="4" tint="0.5999633777886288"/>
@@ -6226,31 +6375,31 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
+      <right/>
+      <top style="medium">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="medium">
+        <color theme="4" tint="0.5999633777886288"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
         <color rgb="FFB8C2CC"/>
-      </right>
-      <top style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -6342,6 +6491,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF17365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="4" tint="0.5999633777886288"/>
       </left>
@@ -6350,30 +6523,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF17365D"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -6421,7 +6570,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1366">
+  <cellXfs count="1415">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -6553,9 +6702,6 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="39" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6770,9 +6916,6 @@
     <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="105" fillId="44" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6824,7 +6967,7 @@
     <xf numFmtId="0" fontId="20" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6848,46 +6991,46 @@
     <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -6901,32 +7044,32 @@
     <xf numFmtId="0" fontId="113" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="92" fillId="20" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6958,18 +7101,6 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="5" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="112" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
@@ -7046,38 +7177,38 @@
     <xf numFmtId="0" fontId="125" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="54" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
@@ -7093,15 +7224,15 @@
     <xf numFmtId="0" fontId="59" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="69" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="70" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="70" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7119,46 +7250,46 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="140" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="150" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="61" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="61" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7199,10 +7330,10 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7242,19 +7373,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -7318,34 +7449,31 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7356,67 +7484,64 @@
     <xf numFmtId="0" fontId="156" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="25" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="74" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="138" fillId="25" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="74" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="17" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="142" fillId="16" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="28" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="28" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="75" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="17" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="16" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="75" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="17" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="16" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="75" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="17" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="16" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="75" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="17" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="16" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7431,25 +7556,25 @@
     <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7478,11 +7603,11 @@
     </xf>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7521,10 +7646,10 @@
     <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7533,28 +7658,28 @@
     <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7576,7 +7701,7 @@
     <xf numFmtId="165" fontId="35" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="18" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="33" fillId="18" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="56" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7591,11 +7716,11 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7604,7 +7729,7 @@
     <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7614,9 +7739,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7635,22 +7757,22 @@
     <xf numFmtId="0" fontId="54" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7659,33 +7781,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="37" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="42" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="149" fillId="42" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7704,29 +7826,147 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="37" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="161" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7748,20 +7988,38 @@
     <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="85" fillId="52" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7769,167 +8027,142 @@
     <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="41" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="116" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="49" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="49" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="28" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="205" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="93" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="280" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="61" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="62" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="61" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="62" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="135" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7951,56 +8184,66 @@
     <xf numFmtId="0" fontId="41" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="72" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="72" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="61" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="61" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="135" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="62" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="135" fillId="62" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
@@ -8025,26 +8268,29 @@
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="25" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="92" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="71" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="131" fillId="71" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8054,15 +8300,12 @@
     <xf numFmtId="0" fontId="130" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8075,16 +8318,31 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="111" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="155" fillId="3" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="3" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="49" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -8092,98 +8350,83 @@
     <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="49" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="34" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="34" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="20" borderId="200" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="201" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="110" fillId="20" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="28" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="20" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8199,22 +8442,22 @@
     <xf numFmtId="0" fontId="82" fillId="59" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8228,10 +8471,10 @@
     <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="104" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8279,21 +8522,35 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="210" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="211" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="210" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="211" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="207" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -8307,31 +8564,9 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="218" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="219" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8339,20 +8574,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8365,7 +8596,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -8379,10 +8610,10 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="105" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8398,7 +8629,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8409,129 +8640,141 @@
     <xf numFmtId="0" fontId="109" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="106" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="124" fillId="57" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="57" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="28" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="28" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="128" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="229" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="28" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="227" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="28" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="228" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8582,7 +8825,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8596,8 +8839,8 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -8610,74 +8853,108 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="236" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="73" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="228" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8687,1131 +8964,1128 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="232" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="224" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="227" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="229" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="14" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="16" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="14" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="50" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="339" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="28" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="28" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="49" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="25" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="25" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="25" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="28" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="28" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="28" borderId="375" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="28" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="28" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="157" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="54" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="54" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="54" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="408" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="47" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="58" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="260" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="405" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="35" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="18" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="56" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="261" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="50" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="16" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="167" fontId="38" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="34" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="29" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="58" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="157" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="37" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="37" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="37" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="54" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="54" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="54" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="43" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="47" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="58" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="396" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="35" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="35" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="18" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="56" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10409,13 +10683,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>237075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10449,13 +10723,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>110085</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>256680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>493125</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>33120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10493,9 +10767,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2747250</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2556750</xdr:colOff>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>141525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10529,13 +10803,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>49468</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>27346</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>553468</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>8088</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10560,6 +10834,206 @@
         </a:prstGeom>
         <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1362075</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2118075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>49050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 5" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2981325" y="3800475"/>
+          <a:ext cx="756000" cy="792000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>455083</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>34926</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>959083</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>466926</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 9"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="455083" y="3971926"/>
+          <a:ext cx="504000" cy="432000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1485900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>295275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>324150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 19"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="6781800" y="3895725"/>
+          <a:ext cx="648000" cy="648000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1239675</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>551625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 23"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="9553575" y="3962400"/>
+          <a:ext cx="792000" cy="504000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1458900</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>5625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Imagen 25"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="11449050" y="3829050"/>
+          <a:ext cx="1116000" cy="720000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
@@ -10753,801 +11227,3374 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:AB143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20.77734375" customWidth="1" style="1051" min="1" max="1"/>
-    <col width="50.77734375" customWidth="1" style="1051" min="2" max="2"/>
-    <col width="26.33203125" customWidth="1" style="1051" min="3" max="5"/>
-    <col width="26" customWidth="1" style="1051" min="6" max="6"/>
-    <col width="4.77734375" customWidth="1" style="1051" min="10" max="10"/>
+    <col width="20.77734375" customWidth="1" style="1062" min="1" max="1"/>
+    <col width="2.77734375" customWidth="1" style="1062" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="1062" min="3" max="3"/>
+    <col width="2.77734375" customWidth="1" style="1062" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="1062" min="5" max="6"/>
+    <col width="2.77734375" customWidth="1" style="1062" min="7" max="7"/>
+    <col width="26.33203125" customWidth="1" style="1062" min="8" max="8"/>
+    <col width="2.77734375" customWidth="1" style="1062" min="9" max="9"/>
+    <col width="26" customWidth="1" style="1062" min="10" max="10"/>
+    <col width="4.77734375" customWidth="1" style="1062" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" style="1062" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="1062" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" style="1062" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" style="1062" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="1051">
-      <c r="C1" s="513" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="1062">
+      <c r="E1" s="548" t="inlineStr">
         <is>
           <t>ANÁLISIS DE PRECIOS UNITARIOS</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Rendimiento</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="4.95" customHeight="1" s="1051">
-      <c r="C2" s="518" t="n"/>
-      <c r="F2" s="519" t="n"/>
+    <row r="2" ht="4.95" customHeight="1" s="1062">
+      <c r="E2" s="553" t="n"/>
+      <c r="J2" s="554" t="n"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Replanteo general de ejes y niveles</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1 Topógrafo + 1 Cadenero</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>150</v>
+      </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="1051">
-      <c r="C3" s="294" t="n"/>
-      <c r="D3" s="294" t="n"/>
-      <c r="E3" s="520" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="1062">
+      <c r="E3" s="288" t="n"/>
+      <c r="F3" s="288" t="n"/>
+      <c r="G3" s="288" t="n"/>
+      <c r="H3" s="563" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="F3" s="521" t="n"/>
+      <c r="I3" s="694" t="n"/>
+      <c r="J3" s="564" t="n"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Cerramiento provisional de obra</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" hidden="1" ht="15" customHeight="1" s="1051">
-      <c r="C4" s="294" t="n"/>
-      <c r="D4" s="294" t="n"/>
-      <c r="E4" s="10" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="1062">
+      <c r="E4" s="288" t="n"/>
+      <c r="F4" s="288" t="n"/>
+      <c r="G4" s="288" t="n"/>
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="F4" s="83" t="n"/>
-      <c r="G4" s="120" t="n"/>
-      <c r="I4" s="120" t="n"/>
-      <c r="L4" s="120" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="M4" s="120" t="n"/>
-      <c r="N4" s="121" t="n"/>
-      <c r="O4" s="122" t="inlineStr">
-        <is>
-          <t>1 Topógrafo + 1 Cadenero 1o</t>
-        </is>
-      </c>
-      <c r="P4" s="121" t="n"/>
-      <c r="Q4" s="122" t="n">
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="82" t="n"/>
+      <c r="K4" s="119" t="n"/>
+      <c r="M4" s="119" t="n"/>
+      <c r="P4" s="119">
+        <f>IFERROR(VLOOKUP($A$10,$Y$2:$AB$143,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="Q4" s="119" t="n"/>
+      <c r="R4" s="120" t="n"/>
+      <c r="S4" s="121">
+        <f>IFERROR(IF(VLOOKUP($A$10,$Y$2:$AB$143,3,0)=0,"",VLOOKUP($A$10,$Y$2:$AB$143,3,0)),"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="120" t="n"/>
+      <c r="U4" s="600" t="n">
         <v>8</v>
       </c>
-      <c r="R4" s="122" t="n">
+      <c r="V4" s="121">
+        <f>IFERROR(IF(VLOOKUP($A$10,$Y$2:$AB$143,4,0)=0,"",VLOOKUP($A$10,$Y$2:$AB$143,4,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W4" s="121">
+        <f>IF(P4="","",P4&amp;"/jornada")</f>
+        <v/>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Instalación de campamento y oficinas provisionales</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="1062">
+      <c r="E5" s="565" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="H5" s="124" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="I5" s="814" t="n"/>
+      <c r="J5" s="202" t="inlineStr">
+        <is>
+          <t>RYR-AP-001</t>
+        </is>
+      </c>
+      <c r="K5" s="119" t="n"/>
+      <c r="M5" s="119" t="n"/>
+      <c r="P5" s="119" t="n"/>
+      <c r="Q5" s="119" t="n"/>
+      <c r="R5" s="120" t="n"/>
+      <c r="S5" s="121" t="n"/>
+      <c r="T5" s="120" t="n"/>
+      <c r="U5" s="121" t="n"/>
+      <c r="V5" s="121" t="n"/>
+      <c r="W5" s="121" t="n"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Adecuación de área de almacenamiento</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="1062">
+      <c r="E6" s="356" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="F6" s="288" t="n"/>
+      <c r="G6" s="288" t="n"/>
+      <c r="H6" s="216" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="I6" s="823" t="n"/>
+      <c r="J6" s="202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="119" t="n"/>
+      <c r="M6" s="119" t="n"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Señalización preventiva e informativa de obra</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="1062">
+      <c r="E7" s="201" t="n"/>
+      <c r="F7" s="288" t="n"/>
+      <c r="G7" s="288" t="n"/>
+      <c r="H7" s="124" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="I7" s="814" t="n"/>
+      <c r="J7" s="202" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="K7" s="119" t="n"/>
+      <c r="M7" s="119" t="n"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Instalaciones provisionales de agua y energía</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="1062">
+      <c r="E8" s="288" t="n"/>
+      <c r="F8" s="288" t="n"/>
+      <c r="G8" s="288" t="n"/>
+      <c r="H8" s="124" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="I8" s="814" t="n"/>
+      <c r="J8" s="202" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+      <c r="K8" s="119" t="n"/>
+      <c r="M8" s="119" t="n"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Protección de elementos existentes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1062">
+      <c r="A9" s="288" t="n"/>
+      <c r="B9" s="288" t="n"/>
+      <c r="C9" s="288" t="n"/>
+      <c r="D9" s="288" t="n"/>
+      <c r="E9" s="288" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Desmonte y limpieza inicial</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="25.05" customHeight="1" s="1062">
+      <c r="A10" s="573" t="n"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Demoliciones preliminares</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="1062">
+      <c r="A11" s="566" t="n"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Excavación manual en material común</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="1062">
+      <c r="A12" s="550" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Excavación mecánica</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1 Operador retroexcavadora + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1062">
+      <c r="A13" s="535" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B13" s="529" t="n"/>
+      <c r="C13" s="1283" t="n"/>
+      <c r="D13" s="558" t="n"/>
+      <c r="E13" s="558" t="n"/>
+      <c r="F13" s="558" t="n"/>
+      <c r="G13" s="558" t="n"/>
+      <c r="H13" s="558" t="n"/>
+      <c r="I13" s="558" t="n"/>
+      <c r="J13" s="562" t="n"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Excavación en roca</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1 Operador + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1062">
+      <c r="A14" s="535" t="inlineStr">
+        <is>
+          <t>No de Contrato</t>
+        </is>
+      </c>
+      <c r="B14" s="529" t="n"/>
+      <c r="C14" s="567" t="n"/>
+      <c r="D14" s="558" t="n"/>
+      <c r="E14" s="558" t="n"/>
+      <c r="F14" s="530" t="n"/>
+      <c r="G14" s="530" t="n"/>
+      <c r="H14" s="529" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="I14" s="529" t="n"/>
+      <c r="J14" s="536" t="n"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Perfilado y conformación de excavaciones</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="1062">
+      <c r="A15" s="535" t="inlineStr">
+        <is>
+          <t>Contratista</t>
+        </is>
+      </c>
+      <c r="B15" s="529" t="n"/>
+      <c r="C15" s="557" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="D15" s="558" t="n"/>
+      <c r="E15" s="558" t="n"/>
+      <c r="F15" s="530" t="n"/>
+      <c r="G15" s="530" t="n"/>
+      <c r="H15" s="529" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="I15" s="529" t="n"/>
+      <c r="J15" s="536" t="n"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Relleno con material seleccionado compactado</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="1062" thickBot="1">
+      <c r="A16" s="1244" t="n"/>
+      <c r="B16" s="640" t="n"/>
+      <c r="C16" s="640" t="n"/>
+      <c r="D16" s="640" t="n"/>
+      <c r="E16" s="640" t="n"/>
+      <c r="F16" s="640" t="n"/>
+      <c r="G16" s="640" t="n"/>
+      <c r="H16" s="640" t="n"/>
+      <c r="I16" s="640" t="n"/>
+      <c r="J16" s="640" t="n"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Relleno con material proveniente de excavación</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="19.95" customHeight="1" s="1062" thickTop="1">
+      <c r="A17" s="1269" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="B17" s="1278" t="n"/>
+      <c r="C17" s="1269" t="inlineStr">
+        <is>
+          <t>CUADRILLA</t>
+        </is>
+      </c>
+      <c r="D17" s="1260" t="n"/>
+      <c r="E17" s="1269" t="inlineStr">
+        <is>
+          <t>JORNADA</t>
+        </is>
+      </c>
+      <c r="F17" s="1284" t="n"/>
+      <c r="G17" s="1260" t="n"/>
+      <c r="H17" s="1269" t="inlineStr">
+        <is>
+          <t>RENDIMIENTO</t>
+        </is>
+      </c>
+      <c r="I17" s="1277" t="n"/>
+      <c r="J17" s="1269" t="inlineStr">
+        <is>
+          <t>CONSUMO M.O.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Suministro, extendido y compactación de subbase</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="25.05" customFormat="1" customHeight="1" s="1276">
+      <c r="A18" s="1279">
+        <f>P4</f>
+        <v/>
+      </c>
+      <c r="B18" s="1278" t="n"/>
+      <c r="C18" s="1279">
+        <f>S4</f>
+        <v/>
+      </c>
+      <c r="D18" s="1285" t="n"/>
+      <c r="E18" s="1279">
+        <f>U4</f>
+        <v/>
+      </c>
+      <c r="F18" s="1286" t="n"/>
+      <c r="G18" s="1285" t="n"/>
+      <c r="H18" s="1279">
+        <f>IF(V4="","",V4&amp;" "&amp;W4)</f>
+        <v/>
+      </c>
+      <c r="J18" s="1282">
+        <f>IFERROR(U4/V4,"")</f>
+        <v/>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Suministro, extendido y compactación de base granular</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="49.95" customFormat="1" customHeight="1" s="1276" thickBot="1">
+      <c r="A19" s="1272" t="n"/>
+      <c r="B19" s="1261" t="n"/>
+      <c r="C19" s="1273" t="n"/>
+      <c r="D19" s="1285" t="n"/>
+      <c r="E19" s="1272" t="n"/>
+      <c r="F19" s="1287" t="n"/>
+      <c r="G19" s="1285" t="n"/>
+      <c r="H19" s="1272" t="n"/>
+      <c r="J19" s="1272" t="n"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Cargue de material sobrante</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customFormat="1" customHeight="1" s="528" thickTop="1">
+      <c r="A20" s="1245" t="n"/>
+      <c r="B20" s="711" t="n"/>
+      <c r="C20" s="711" t="n"/>
+      <c r="D20" s="711" t="n"/>
+      <c r="E20" s="711" t="n"/>
+      <c r="F20" s="711" t="n"/>
+      <c r="G20" s="711" t="n"/>
+      <c r="H20" s="711" t="n"/>
+      <c r="I20" s="711" t="n"/>
+      <c r="J20" s="711" t="n"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Transporte de material sobrante</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="1062">
+      <c r="A21" s="537" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B21" s="1246" t="n"/>
+      <c r="C21" s="538" t="inlineStr">
+        <is>
+          <t>MATERIALES</t>
+        </is>
+      </c>
+      <c r="D21" s="1262" t="n"/>
+      <c r="E21" s="574" t="n"/>
+      <c r="F21" s="575" t="n"/>
+      <c r="G21" s="575" t="n"/>
+      <c r="H21" s="575" t="n"/>
+      <c r="I21" s="575" t="n"/>
+      <c r="J21" s="1288" t="n"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Disposición final de sobrantes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customFormat="1" customHeight="1" s="665">
+      <c r="A22" s="531" t="n"/>
+      <c r="B22" s="1247" t="n"/>
+      <c r="C22" s="532" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="D22" s="533" t="n"/>
+      <c r="E22" s="533" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F22" s="533" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G22" s="533" t="n"/>
+      <c r="H22" s="533" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="I22" s="533" t="n"/>
+      <c r="J22" s="534" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Concreto de limpieza / solado</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="1062">
+      <c r="A23" s="549" t="n"/>
+      <c r="B23" s="545" t="n"/>
+      <c r="C23" s="545" t="n"/>
+      <c r="D23" s="545" t="n"/>
+      <c r="E23" s="117" t="n"/>
+      <c r="F23" s="118" t="n"/>
+      <c r="G23" s="118" t="n"/>
+      <c r="H23" s="1289" t="n"/>
+      <c r="I23" s="1289" t="n"/>
+      <c r="J23" s="1290">
+        <f>F23*H23</f>
+        <v/>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Concreto para zapatas</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="1062">
+      <c r="A24" s="549" t="n"/>
+      <c r="B24" s="545" t="n"/>
+      <c r="C24" s="545" t="n"/>
+      <c r="D24" s="545" t="n"/>
+      <c r="E24" s="117" t="n"/>
+      <c r="F24" s="118" t="n"/>
+      <c r="G24" s="118" t="n"/>
+      <c r="H24" s="1289" t="n"/>
+      <c r="I24" s="1289" t="n"/>
+      <c r="J24" s="1290">
+        <f>F24*H24</f>
+        <v/>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Concreto para vigas de cimentación</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="1062">
+      <c r="A25" s="549" t="n"/>
+      <c r="B25" s="545" t="n"/>
+      <c r="C25" s="545" t="n"/>
+      <c r="D25" s="545" t="n"/>
+      <c r="E25" s="117" t="n"/>
+      <c r="F25" s="118" t="n"/>
+      <c r="G25" s="118" t="n"/>
+      <c r="H25" s="1289" t="n"/>
+      <c r="I25" s="1289" t="n"/>
+      <c r="J25" s="1290">
+        <f>F25*H25</f>
+        <v/>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Concreto para losas de cimentación</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1 Oficial + 4 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="1062">
+      <c r="A26" s="549" t="n"/>
+      <c r="B26" s="545" t="n"/>
+      <c r="C26" s="545" t="n"/>
+      <c r="D26" s="545" t="n"/>
+      <c r="E26" s="117" t="n"/>
+      <c r="F26" s="118" t="n"/>
+      <c r="G26" s="118" t="n"/>
+      <c r="H26" s="1289" t="n"/>
+      <c r="I26" s="1289" t="n"/>
+      <c r="J26" s="1290">
+        <f>F26*H26</f>
+        <v/>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Concreto para pedestales</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="1062">
+      <c r="A27" s="549" t="n"/>
+      <c r="B27" s="545" t="n"/>
+      <c r="C27" s="545" t="n"/>
+      <c r="D27" s="545" t="n"/>
+      <c r="E27" s="117" t="n"/>
+      <c r="F27" s="118" t="n"/>
+      <c r="G27" s="118" t="n"/>
+      <c r="H27" s="1289" t="n"/>
+      <c r="I27" s="1289" t="n"/>
+      <c r="J27" s="1290">
+        <f>F27*H27</f>
+        <v/>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Acero de refuerzo en cimentación</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1062">
+      <c r="A28" s="549" t="n"/>
+      <c r="B28" s="545" t="n"/>
+      <c r="C28" s="545" t="n"/>
+      <c r="D28" s="545" t="n"/>
+      <c r="E28" s="117" t="n"/>
+      <c r="F28" s="118" t="n"/>
+      <c r="G28" s="118" t="n"/>
+      <c r="H28" s="1291" t="n"/>
+      <c r="I28" s="1291" t="n"/>
+      <c r="J28" s="1290">
+        <f>F28*H28</f>
+        <v/>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Formaleta para elementos de cimentación</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1062">
+      <c r="A29" s="551" t="n"/>
+      <c r="B29" s="552" t="n"/>
+      <c r="C29" s="552" t="n"/>
+      <c r="D29" s="552" t="n"/>
+      <c r="E29" s="582" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES</t>
+        </is>
+      </c>
+      <c r="F29" s="552" t="n"/>
+      <c r="G29" s="552" t="n"/>
+      <c r="H29" s="552" t="n"/>
+      <c r="I29" s="552" t="n"/>
+      <c r="J29" s="1292">
+        <f>SUM(J23:J28)</f>
+        <v/>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Concreto para columnas</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="1062">
+      <c r="A30" s="200" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B30" s="1250" t="n"/>
+      <c r="C30" s="353" t="inlineStr">
+        <is>
+          <t>MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="D30" s="353" t="n"/>
+      <c r="E30" s="541" t="n"/>
+      <c r="F30" s="542" t="n"/>
+      <c r="G30" s="542" t="n"/>
+      <c r="H30" s="542" t="n"/>
+      <c r="I30" s="542" t="n"/>
+      <c r="J30" s="543" t="n"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Concreto para vigas</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1062">
+      <c r="A31" s="67" t="n"/>
+      <c r="B31" s="1251" t="n"/>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="n"/>
+      <c r="E31" s="51" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F31" s="51" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="n"/>
+      <c r="H31" s="51" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="I31" s="51" t="n"/>
+      <c r="J31" s="68" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Concreto para losas</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1 Oficial + 4 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="1062">
+      <c r="A32" s="544" t="n"/>
+      <c r="B32" s="545" t="n"/>
+      <c r="C32" s="545" t="n"/>
+      <c r="D32" s="545" t="n"/>
+      <c r="E32" s="117" t="n"/>
+      <c r="F32" s="1293" t="n"/>
+      <c r="G32" s="1293" t="n"/>
+      <c r="H32" s="1289" t="n"/>
+      <c r="I32" s="1289" t="n"/>
+      <c r="J32" s="1294">
+        <f>F32*H32</f>
+        <v/>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Concreto para escaleras</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="1062">
+      <c r="A33" s="544" t="n"/>
+      <c r="B33" s="545" t="n"/>
+      <c r="C33" s="545" t="n"/>
+      <c r="D33" s="545" t="n"/>
+      <c r="E33" s="117" t="n"/>
+      <c r="F33" s="1293" t="n"/>
+      <c r="G33" s="1293" t="n"/>
+      <c r="H33" s="1289" t="n"/>
+      <c r="I33" s="1289" t="n"/>
+      <c r="J33" s="1294">
+        <f>F33*H33</f>
+        <v/>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Concreto para muros estructurales</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1062">
+      <c r="A34" s="544" t="n"/>
+      <c r="B34" s="545" t="n"/>
+      <c r="C34" s="545" t="n"/>
+      <c r="D34" s="545" t="n"/>
+      <c r="E34" s="117" t="n"/>
+      <c r="F34" s="1293" t="n"/>
+      <c r="G34" s="1293" t="n"/>
+      <c r="H34" s="1289" t="n"/>
+      <c r="I34" s="1289" t="n"/>
+      <c r="J34" s="1294">
+        <f>F34*H34</f>
+        <v/>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Acero de refuerzo de columnas</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="1062">
+      <c r="A35" s="544" t="n"/>
+      <c r="B35" s="545" t="n"/>
+      <c r="C35" s="545" t="n"/>
+      <c r="D35" s="545" t="n"/>
+      <c r="E35" s="117" t="n"/>
+      <c r="F35" s="1293" t="n"/>
+      <c r="G35" s="1293" t="n"/>
+      <c r="H35" s="1289" t="n"/>
+      <c r="I35" s="1289" t="n"/>
+      <c r="J35" s="1294">
+        <f>F35*H35</f>
+        <v/>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Acero de refuerzo de vigas</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1062">
+      <c r="A36" s="544" t="n"/>
+      <c r="B36" s="545" t="n"/>
+      <c r="C36" s="545" t="n"/>
+      <c r="D36" s="545" t="n"/>
+      <c r="E36" s="117" t="n"/>
+      <c r="F36" s="1293" t="n"/>
+      <c r="G36" s="1293" t="n"/>
+      <c r="H36" s="1289" t="n"/>
+      <c r="I36" s="1289" t="n"/>
+      <c r="J36" s="1294">
+        <f>F36*H36</f>
+        <v/>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Acero de refuerzo de losas</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="1062">
+      <c r="A37" s="544" t="n"/>
+      <c r="B37" s="545" t="n"/>
+      <c r="C37" s="545" t="n"/>
+      <c r="D37" s="545" t="n"/>
+      <c r="E37" s="117" t="n"/>
+      <c r="F37" s="1293" t="n"/>
+      <c r="G37" s="1293" t="n"/>
+      <c r="H37" s="1291" t="n"/>
+      <c r="I37" s="1291" t="n"/>
+      <c r="J37" s="1294">
+        <f>F37*H37</f>
+        <v/>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Formaleta de columnas</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="1062">
+      <c r="A38" s="560" t="n"/>
+      <c r="B38" s="545" t="n"/>
+      <c r="C38" s="545" t="n"/>
+      <c r="D38" s="545" t="n"/>
+      <c r="E38" s="559" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="F38" s="545" t="n"/>
+      <c r="G38" s="545" t="n"/>
+      <c r="H38" s="545" t="n"/>
+      <c r="I38" s="545" t="n"/>
+      <c r="J38" s="1295">
+        <f>SUM(J32:J37)</f>
+        <v/>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Formaleta de vigas</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="1062">
+      <c r="A39" s="66" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B39" s="1253" t="n"/>
+      <c r="C39" s="354" t="inlineStr">
+        <is>
+          <t>EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="D39" s="354" t="n"/>
+      <c r="E39" s="555" t="n"/>
+      <c r="F39" s="545" t="n"/>
+      <c r="G39" s="545" t="n"/>
+      <c r="H39" s="545" t="n"/>
+      <c r="I39" s="545" t="n"/>
+      <c r="J39" s="556" t="n"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Formaleta de losas</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1 Oficial + 3 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="1062">
+      <c r="A40" s="69" t="n"/>
+      <c r="B40" s="354" t="n"/>
+      <c r="C40" s="51" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="n"/>
+      <c r="E40" s="51" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G40" s="51" t="n"/>
+      <c r="H40" s="51" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="I40" s="51" t="n"/>
+      <c r="J40" s="68" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Formaleta de escaleras</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="1062">
+      <c r="A41" s="544" t="n"/>
+      <c r="B41" s="545" t="n"/>
+      <c r="C41" s="545" t="n"/>
+      <c r="D41" s="545" t="n"/>
+      <c r="E41" s="117" t="n"/>
+      <c r="F41" s="1293" t="n"/>
+      <c r="G41" s="1293" t="n"/>
+      <c r="H41" s="1289" t="n"/>
+      <c r="I41" s="1289" t="n"/>
+      <c r="J41" s="1294">
+        <f>F41*H41</f>
+        <v/>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Suministro y montaje de perfiles metálicos</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="1062">
+      <c r="A42" s="544" t="n"/>
+      <c r="B42" s="1248" t="n"/>
+      <c r="C42" s="1248" t="n"/>
+      <c r="D42" s="1248" t="n"/>
+      <c r="E42" s="117" t="n"/>
+      <c r="F42" s="1293" t="n"/>
+      <c r="G42" s="1293" t="n"/>
+      <c r="H42" s="1289" t="n"/>
+      <c r="I42" s="1289" t="n"/>
+      <c r="J42" s="1294">
+        <f>F42*H42</f>
+        <v/>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Placas, pernos y conexiones metálicas</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="1062">
+      <c r="A43" s="544" t="n"/>
+      <c r="B43" s="1248" t="n"/>
+      <c r="C43" s="1248" t="n"/>
+      <c r="D43" s="1248" t="n"/>
+      <c r="E43" s="117" t="n"/>
+      <c r="F43" s="1293" t="n"/>
+      <c r="G43" s="1293" t="n"/>
+      <c r="H43" s="1289" t="n"/>
+      <c r="I43" s="1289" t="n"/>
+      <c r="J43" s="1294">
+        <f>F43*H43</f>
+        <v/>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Mampostería en bloque de concreto</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="1062">
+      <c r="A44" s="544" t="n"/>
+      <c r="B44" s="1248" t="n"/>
+      <c r="C44" s="1248" t="n"/>
+      <c r="D44" s="1248" t="n"/>
+      <c r="E44" s="117" t="n"/>
+      <c r="F44" s="1293" t="n"/>
+      <c r="G44" s="1293" t="n"/>
+      <c r="H44" s="1289" t="n"/>
+      <c r="I44" s="1289" t="n"/>
+      <c r="J44" s="1294">
+        <f>F44*H44</f>
+        <v/>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Mampostería en ladrillo</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="1062">
+      <c r="A45" s="544" t="n"/>
+      <c r="B45" s="545" t="n"/>
+      <c r="C45" s="545" t="n"/>
+      <c r="D45" s="545" t="n"/>
+      <c r="E45" s="117" t="n"/>
+      <c r="F45" s="1293" t="n"/>
+      <c r="G45" s="1293" t="n"/>
+      <c r="H45" s="1289" t="n"/>
+      <c r="I45" s="1289" t="n"/>
+      <c r="J45" s="1294">
+        <f>F45*H45</f>
+        <v/>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Mampostería estructural</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="1062">
+      <c r="A46" s="544" t="n"/>
+      <c r="B46" s="545" t="n"/>
+      <c r="C46" s="545" t="n"/>
+      <c r="D46" s="545" t="n"/>
+      <c r="E46" s="117" t="n"/>
+      <c r="F46" s="1293" t="n"/>
+      <c r="G46" s="1293" t="n"/>
+      <c r="H46" s="1289" t="n"/>
+      <c r="I46" s="1289" t="n"/>
+      <c r="J46" s="1294">
+        <f>F46*H46</f>
+        <v/>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Muros en sistema liviano / drywall</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="1062">
+      <c r="A47" s="560" t="n"/>
+      <c r="B47" s="545" t="n"/>
+      <c r="C47" s="545" t="n"/>
+      <c r="D47" s="545" t="n"/>
+      <c r="E47" s="559" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="F47" s="545" t="n"/>
+      <c r="G47" s="545" t="n"/>
+      <c r="H47" s="545" t="n"/>
+      <c r="I47" s="545" t="n"/>
+      <c r="J47" s="1295">
+        <f>SUM(J41:J46)</f>
+        <v/>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Dinteles sobre vanos</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" ht="24.75" customHeight="1" s="1062">
+      <c r="A48" s="546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Materiales</t>
+        </is>
+      </c>
+      <c r="B48" s="545" t="n"/>
+      <c r="C48" s="545" t="n"/>
+      <c r="D48" s="545" t="n"/>
+      <c r="E48" s="545" t="n"/>
+      <c r="F48" s="545" t="n"/>
+      <c r="G48" s="545" t="n"/>
+      <c r="H48" s="545" t="n"/>
+      <c r="I48" s="547" t="n"/>
+      <c r="J48" s="1296">
+        <f>J29</f>
+        <v/>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Alfajías y remates</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" ht="24.75" customHeight="1" s="1062">
+      <c r="A49" s="546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Mano de Obra</t>
+        </is>
+      </c>
+      <c r="B49" s="545" t="n"/>
+      <c r="C49" s="545" t="n"/>
+      <c r="D49" s="545" t="n"/>
+      <c r="E49" s="545" t="n"/>
+      <c r="F49" s="545" t="n"/>
+      <c r="G49" s="545" t="n"/>
+      <c r="H49" s="545" t="n"/>
+      <c r="I49" s="547" t="n"/>
+      <c r="J49" s="1296">
+        <f>J38</f>
+        <v/>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Anclajes y refuerzos de mampostería</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24.75" customHeight="1" s="1062">
+      <c r="A50" s="546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Equipos y herramientas</t>
+        </is>
+      </c>
+      <c r="B50" s="545" t="n"/>
+      <c r="C50" s="545" t="n"/>
+      <c r="D50" s="545" t="n"/>
+      <c r="E50" s="545" t="n"/>
+      <c r="F50" s="545" t="n"/>
+      <c r="G50" s="545" t="n"/>
+      <c r="H50" s="545" t="n"/>
+      <c r="I50" s="547" t="n"/>
+      <c r="J50" s="1296">
+        <f>J47</f>
+        <v/>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1 Oficial soldador + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" ht="19.95" customHeight="1" s="1062">
+      <c r="A51" s="571" t="inlineStr">
+        <is>
+          <t>TOTAL DIRECTO UNITARIO</t>
+        </is>
+      </c>
+      <c r="B51" s="1297" t="n"/>
+      <c r="C51" s="1297" t="n"/>
+      <c r="D51" s="1297" t="n"/>
+      <c r="E51" s="1297" t="n"/>
+      <c r="F51" s="1297" t="n"/>
+      <c r="G51" s="1297" t="n"/>
+      <c r="H51" s="1297" t="n"/>
+      <c r="I51" s="572" t="n"/>
+      <c r="J51" s="1298">
+        <f>SUM(J48:J50)</f>
+        <v/>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Cerchas y elementos estructurales</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="4.5" customHeight="1" s="1062">
+      <c r="A52" s="70" t="n"/>
+      <c r="B52" s="1256" t="n"/>
+      <c r="C52" s="1256" t="n"/>
+      <c r="D52" s="1256" t="n"/>
+      <c r="E52" s="1256" t="n"/>
+      <c r="F52" s="1256" t="n"/>
+      <c r="G52" s="1256" t="n"/>
+      <c r="H52" s="1256" t="n"/>
+      <c r="I52" s="1256" t="n"/>
+      <c r="J52" s="71" t="n"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de teja</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="1062">
+      <c r="A53" s="577" t="inlineStr">
+        <is>
+          <t>ELABORADO POR</t>
+        </is>
+      </c>
+      <c r="B53" s="578" t="n"/>
+      <c r="C53" s="578" t="n"/>
+      <c r="D53" s="578" t="n"/>
+      <c r="E53" s="1257" t="n"/>
+      <c r="F53" s="580" t="inlineStr">
+        <is>
+          <t>Vo. Bo. INTERVENTORÍA:</t>
+        </is>
+      </c>
+      <c r="G53" s="578" t="n"/>
+      <c r="H53" s="578" t="n"/>
+      <c r="I53" s="578" t="n"/>
+      <c r="J53" s="581" t="n"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Impermeabilización de cubierta</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1" s="1062">
+      <c r="A54" s="454" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="B54" s="1258" t="n"/>
+      <c r="C54" s="539" t="n"/>
+      <c r="D54" s="906" t="n"/>
+      <c r="E54" s="906" t="n"/>
+      <c r="F54" s="455" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="G54" s="455" t="n"/>
+      <c r="H54" s="579" t="n"/>
+      <c r="I54" s="906" t="n"/>
+      <c r="J54" s="930" t="n"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Aislamiento térmico/acústico</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24.75" customHeight="1" s="1062">
+      <c r="A55" s="454" t="inlineStr">
+        <is>
+          <t>NOMBRE:</t>
+        </is>
+      </c>
+      <c r="B55" s="1258" t="n"/>
+      <c r="C55" s="539" t="n"/>
+      <c r="D55" s="906" t="n"/>
+      <c r="E55" s="906" t="n"/>
+      <c r="F55" s="455" t="inlineStr">
+        <is>
+          <t>NOMBRE:</t>
+        </is>
+      </c>
+      <c r="G55" s="455" t="n"/>
+      <c r="H55" s="569" t="n"/>
+      <c r="I55" s="906" t="n"/>
+      <c r="J55" s="930" t="n"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Canales de aguas lluvias</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" ht="24.75" customHeight="1" s="1062">
+      <c r="A56" s="454" t="inlineStr">
+        <is>
+          <t>CARGO:</t>
+        </is>
+      </c>
+      <c r="B56" s="1258" t="n"/>
+      <c r="C56" s="539" t="n"/>
+      <c r="D56" s="906" t="n"/>
+      <c r="E56" s="906" t="n"/>
+      <c r="F56" s="455" t="inlineStr">
+        <is>
+          <t>CARGO:</t>
+        </is>
+      </c>
+      <c r="G56" s="455" t="n"/>
+      <c r="H56" s="569" t="n"/>
+      <c r="I56" s="906" t="n"/>
+      <c r="J56" s="930" t="n"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Bajantes de aguas lluvias</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="1062">
+      <c r="A57" s="226" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="1259" t="n"/>
+      <c r="J57" s="496">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Impermeabilización de losas y terrazas</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Impermeabilización de zonas húmedas</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Pañete / revoque exterior</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Pañete impermeabilizado</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Estuco plástico o tradicional</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Mortero de nivelación</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Piso cerámico</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Piso en porcelanato</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Piso vinílico</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Piso laminado</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Enchape cerámico en muros</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Guardaescoba</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>1 Oficial</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Juntas de dilatación / construcción</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Pintura vinílica interior</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Pintura exterior</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Pintura anticorrosiva</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>1 Oficial</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Puertas de madera</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Muebles fijos de madera</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Puertas metálicas</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Pasamanos</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Ventanas de aluminio</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Divisiones de aluminio</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Vidrio templado</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Vidrio laminado</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>1 Oficial + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Espejos</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Sellos y silicona</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Tubería de agua fría</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Tubería de agua caliente</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Válvulas y accesorios</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Tubería sanitaria</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Tubería de aguas lluvias</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Cajas de inspección</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Aparatos sanitarios</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Lavamanos</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Griferías</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Duchas</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Tubería/conduit eléctrica</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>1 Electricista + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Bandejas portacables</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Cajas eléctricas</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Cableado de fuerza</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>1 Electricista + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Cableado de iluminación</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>1 Electricista + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Tableros eléctricos</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Tomacorrientes</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>1 Electricista</t>
+        </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Interruptores</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>1 Electricista</t>
+        </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Luminarias</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>1 Electricista + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Sistema de puesta a tierra</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Pruebas y certificaciones</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Cableado estructurado de datos</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Rack de comunicaciones</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Cámaras y sistema CCTV</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Control de acceso</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Sistema de citofonía</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Equipos de aire acondicionado</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>Ductos de ventilación</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Tubería de refrigerante</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Red interna de gas</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>Válvulas y accesorios</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>Construcción de andenes</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB123" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>Placas de concreto exteriores</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>Pavimento en adoquín</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Sardineles y bordillos</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>1 Oficial + 2 Ayudantes</t>
+        </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Sumideros exteriores</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Suministro y extendido de tierra vegetal</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Siembra y jardinería</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>1 Jardinero + 1 Ayudante</t>
+        </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Rejas metálicas</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>Escaleras metálicas</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Elementos metálicos especiales</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Limpieza gruesa y fina de obra</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2 Aseadores</t>
+        </is>
+      </c>
+      <c r="AB134" t="n">
         <v>100</v>
       </c>
-      <c r="S4" s="122" t="inlineStr">
-        <is>
-          <t>m2/jornada</t>
-        </is>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="1051">
-      <c r="C5" s="522" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="E5" s="125" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="F5" s="208" t="inlineStr">
-        <is>
-          <t>RYR-AP-001</t>
-        </is>
-      </c>
-      <c r="G5" s="120" t="n"/>
-      <c r="I5" s="120" t="n"/>
-      <c r="L5" s="120" t="n"/>
-      <c r="M5" s="120" t="n"/>
-      <c r="N5" s="121" t="n"/>
-      <c r="O5" s="122" t="n"/>
-      <c r="P5" s="121" t="n"/>
-      <c r="Q5" s="122" t="n"/>
-      <c r="R5" s="122" t="n"/>
-      <c r="S5" s="122" t="n"/>
+    <row r="135">
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Limpieza final para entrega</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2 Aseadores</t>
+        </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>80</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="1051">
-      <c r="C6" s="363" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="D6" s="294" t="n"/>
-      <c r="E6" s="222" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="F6" s="208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="120" t="n"/>
-      <c r="I6" s="120" t="n"/>
+    <row r="136">
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Pruebas, puesta en marcha y ajustes</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="1051">
-      <c r="C7" s="207" t="n"/>
-      <c r="D7" s="294" t="n"/>
-      <c r="E7" s="125" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="F7" s="208" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="G7" s="120" t="n"/>
-      <c r="I7" s="120" t="n"/>
+    <row r="137">
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>Actualización de planos récord / as-built</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1051">
-      <c r="C8" s="294" t="n"/>
-      <c r="D8" s="294" t="n"/>
-      <c r="E8" s="125" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="F8" s="208" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-      <c r="G8" s="120" t="n"/>
-      <c r="I8" s="120" t="n"/>
+    <row r="138">
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1051">
-      <c r="A9" s="294">
-        <f>"Cuadrilla: "&amp;O4&amp;"   |   Unidad: "&amp;L4&amp;"   |   Jornada: "&amp;Q4&amp;" h   |   Rendimiento: "&amp;R4&amp;" "&amp;S4&amp;"   |   Consumo M.O.: "&amp;IFERROR(TEXT(Q4/R4,"0.00"),"—")&amp;" h/"&amp;L4</f>
-        <v/>
+    <row r="139">
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de ascensor eléctrico</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
       </c>
     </row>
-    <row r="10" ht="25.05" customHeight="1" s="1051">
-      <c r="A10" s="542" t="inlineStr">
-        <is>
-          <t>LOCALIZACIÓN Y REPLANTEO</t>
+    <row r="140">
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>gl</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1051">
-      <c r="A11" s="528" t="n"/>
+    <row r="141">
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="1051">
-      <c r="A12" s="515" t="inlineStr">
-        <is>
-          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+    <row r="142">
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>gl</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1051">
-      <c r="A13" s="364" t="inlineStr">
-        <is>
-          <t>Proyecto</t>
-        </is>
-      </c>
-      <c r="B13" s="533" t="n"/>
-      <c r="C13" s="534" t="n"/>
-      <c r="D13" s="534" t="n"/>
-      <c r="E13" s="534" t="n"/>
-      <c r="F13" s="526" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="1051">
-      <c r="A14" s="364" t="inlineStr">
-        <is>
-          <t>No de Contrato</t>
-        </is>
-      </c>
-      <c r="B14" s="530" t="n"/>
-      <c r="C14" s="526" t="n"/>
-      <c r="D14" s="206" t="n"/>
-      <c r="E14" s="364" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="F14" s="460" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="1051">
-      <c r="A15" s="364" t="inlineStr">
-        <is>
-          <t>Contratista</t>
-        </is>
-      </c>
-      <c r="B15" s="525" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="C15" s="526" t="n"/>
-      <c r="D15" s="206" t="n"/>
-      <c r="E15" s="364" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="F15" s="460" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="1051">
-      <c r="A16" s="540" t="n"/>
-      <c r="B16" s="541" t="n"/>
-      <c r="C16" s="541" t="n"/>
-      <c r="D16" s="541" t="n"/>
-      <c r="E16" s="541" t="n"/>
-      <c r="F16" s="541" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="1051">
-      <c r="A17" s="203" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B17" s="359" t="inlineStr">
-        <is>
-          <t>MATERIALES</t>
-        </is>
-      </c>
-      <c r="C17" s="543" t="n"/>
-      <c r="D17" s="544" t="n"/>
-      <c r="E17" s="544" t="n"/>
-      <c r="F17" s="545" t="n"/>
-    </row>
-    <row r="18" ht="15" customFormat="1" customHeight="1" s="629">
-      <c r="A18" s="204" t="n"/>
-      <c r="B18" s="132" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="D18" s="50" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="F18" s="205" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1051">
-      <c r="A19" s="514" t="n"/>
-      <c r="B19" s="510" t="n"/>
-      <c r="C19" s="118" t="n"/>
-      <c r="D19" s="119" t="n"/>
-      <c r="E19" s="1234" t="n"/>
-      <c r="F19" s="1235">
-        <f>D19*E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1051">
-      <c r="A20" s="514" t="n"/>
-      <c r="B20" s="510" t="n"/>
-      <c r="C20" s="118" t="n"/>
-      <c r="D20" s="119" t="n"/>
-      <c r="E20" s="1234" t="n"/>
-      <c r="F20" s="1235">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1051">
-      <c r="A21" s="514" t="n"/>
-      <c r="B21" s="510" t="n"/>
-      <c r="C21" s="118" t="n"/>
-      <c r="D21" s="119" t="n"/>
-      <c r="E21" s="1234" t="n"/>
-      <c r="F21" s="1235">
-        <f>D21*E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="1051">
-      <c r="A22" s="514" t="n"/>
-      <c r="B22" s="510" t="n"/>
-      <c r="C22" s="118" t="n"/>
-      <c r="D22" s="119" t="n"/>
-      <c r="E22" s="1234" t="n"/>
-      <c r="F22" s="1235">
-        <f>D22*E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1051">
-      <c r="A23" s="514" t="n"/>
-      <c r="B23" s="510" t="n"/>
-      <c r="C23" s="118" t="n"/>
-      <c r="D23" s="119" t="n"/>
-      <c r="E23" s="1234" t="n"/>
-      <c r="F23" s="1235">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="1051">
-      <c r="A24" s="514" t="n"/>
-      <c r="B24" s="510" t="n"/>
-      <c r="C24" s="118" t="n"/>
-      <c r="D24" s="119" t="n"/>
-      <c r="E24" s="1236" t="n"/>
-      <c r="F24" s="1235">
-        <f>D24*E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="1051">
-      <c r="A25" s="516" t="n"/>
-      <c r="B25" s="517" t="n"/>
-      <c r="C25" s="532" t="inlineStr">
-        <is>
-          <t>SUBTOTAL MATERIALES</t>
-        </is>
-      </c>
-      <c r="D25" s="517" t="n"/>
-      <c r="E25" s="517" t="n"/>
-      <c r="F25" s="1237">
-        <f>SUM(F19:F24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="1051">
-      <c r="A26" s="202" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B26" s="360" t="inlineStr">
-        <is>
-          <t>MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="C26" s="506" t="n"/>
-      <c r="D26" s="507" t="n"/>
-      <c r="E26" s="507" t="n"/>
-      <c r="F26" s="508" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="1051">
-      <c r="A27" s="68" t="n"/>
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C27" s="52" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="D27" s="52" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="E27" s="52" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="F27" s="69" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="1051">
-      <c r="A28" s="509" t="n"/>
-      <c r="B28" s="510" t="n"/>
-      <c r="C28" s="118" t="n"/>
-      <c r="D28" s="1238" t="n"/>
-      <c r="E28" s="1234" t="n"/>
-      <c r="F28" s="1239">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1051">
-      <c r="A29" s="509" t="n"/>
-      <c r="B29" s="510" t="n"/>
-      <c r="C29" s="118" t="n"/>
-      <c r="D29" s="1238" t="n"/>
-      <c r="E29" s="1234" t="n"/>
-      <c r="F29" s="1239">
-        <f>D29*E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="1051">
-      <c r="A30" s="509" t="n"/>
-      <c r="B30" s="510" t="n"/>
-      <c r="C30" s="118" t="n"/>
-      <c r="D30" s="1238" t="n"/>
-      <c r="E30" s="1234" t="n"/>
-      <c r="F30" s="1239">
-        <f>D30*E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1051">
-      <c r="A31" s="509" t="n"/>
-      <c r="B31" s="510" t="n"/>
-      <c r="C31" s="118" t="n"/>
-      <c r="D31" s="1238" t="n"/>
-      <c r="E31" s="1234" t="n"/>
-      <c r="F31" s="1239">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="1051">
-      <c r="A32" s="509" t="n"/>
-      <c r="B32" s="510" t="n"/>
-      <c r="C32" s="118" t="n"/>
-      <c r="D32" s="1238" t="n"/>
-      <c r="E32" s="1234" t="n"/>
-      <c r="F32" s="1239">
-        <f>D32*E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="1051">
-      <c r="A33" s="509" t="n"/>
-      <c r="B33" s="510" t="n"/>
-      <c r="C33" s="118" t="n"/>
-      <c r="D33" s="1238" t="n"/>
-      <c r="E33" s="1236" t="n"/>
-      <c r="F33" s="1239">
-        <f>D33*E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="1051">
-      <c r="A34" s="529" t="n"/>
-      <c r="B34" s="510" t="n"/>
-      <c r="C34" s="527" t="inlineStr">
-        <is>
-          <t>SUBTOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="D34" s="510" t="n"/>
-      <c r="E34" s="510" t="n"/>
-      <c r="F34" s="1240">
-        <f>SUM(F28:F33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="1051">
-      <c r="A35" s="67" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B35" s="361" t="inlineStr">
-        <is>
-          <t>EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="C35" s="523" t="n"/>
-      <c r="D35" s="510" t="n"/>
-      <c r="E35" s="510" t="n"/>
-      <c r="F35" s="524" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="1051">
-      <c r="A36" s="70" t="n"/>
-      <c r="B36" s="52" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C36" s="52" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="D36" s="52" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="E36" s="52" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="F36" s="69" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="1051">
-      <c r="A37" s="509" t="n"/>
-      <c r="B37" s="510" t="n"/>
-      <c r="C37" s="118" t="n"/>
-      <c r="D37" s="1238" t="n"/>
-      <c r="E37" s="1234" t="n"/>
-      <c r="F37" s="1239">
-        <f>D37*E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="1051">
-      <c r="A38" s="509" t="n"/>
-      <c r="B38" s="510" t="n"/>
-      <c r="C38" s="118" t="n"/>
-      <c r="D38" s="1238" t="n"/>
-      <c r="E38" s="1234" t="n"/>
-      <c r="F38" s="1239">
-        <f>D38*E38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="1051">
-      <c r="A39" s="509" t="n"/>
-      <c r="B39" s="510" t="n"/>
-      <c r="C39" s="118" t="n"/>
-      <c r="D39" s="1238" t="n"/>
-      <c r="E39" s="1234" t="n"/>
-      <c r="F39" s="1239">
-        <f>D39*E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="1051">
-      <c r="A40" s="509" t="n"/>
-      <c r="B40" s="510" t="n"/>
-      <c r="C40" s="118" t="n"/>
-      <c r="D40" s="1238" t="n"/>
-      <c r="E40" s="1234" t="n"/>
-      <c r="F40" s="1239">
-        <f>D40*E40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="1051">
-      <c r="A41" s="509" t="n"/>
-      <c r="B41" s="510" t="n"/>
-      <c r="C41" s="118" t="n"/>
-      <c r="D41" s="1238" t="n"/>
-      <c r="E41" s="1234" t="n"/>
-      <c r="F41" s="1239">
-        <f>D41*E41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="1051">
-      <c r="A42" s="509" t="n"/>
-      <c r="B42" s="510" t="n"/>
-      <c r="C42" s="118" t="n"/>
-      <c r="D42" s="1238" t="n"/>
-      <c r="E42" s="1234" t="n"/>
-      <c r="F42" s="1239">
-        <f>D42*E42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="1051">
-      <c r="A43" s="529" t="n"/>
-      <c r="B43" s="510" t="n"/>
-      <c r="C43" s="527" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="D43" s="510" t="n"/>
-      <c r="E43" s="510" t="n"/>
-      <c r="F43" s="1240">
-        <f>SUM(F37:F42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="24.75" customHeight="1" s="1051">
-      <c r="A44" s="511" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Materiales</t>
-        </is>
-      </c>
-      <c r="B44" s="510" t="n"/>
-      <c r="C44" s="510" t="n"/>
-      <c r="D44" s="510" t="n"/>
-      <c r="E44" s="510" t="n"/>
-      <c r="F44" s="1241">
-        <f>F25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="24.75" customHeight="1" s="1051">
-      <c r="A45" s="511" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Mano de Obra</t>
-        </is>
-      </c>
-      <c r="B45" s="510" t="n"/>
-      <c r="C45" s="510" t="n"/>
-      <c r="D45" s="510" t="n"/>
-      <c r="E45" s="510" t="n"/>
-      <c r="F45" s="1241">
-        <f>F34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="24.75" customHeight="1" s="1051">
-      <c r="A46" s="511" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Equipos y herramientas</t>
-        </is>
-      </c>
-      <c r="B46" s="510" t="n"/>
-      <c r="C46" s="510" t="n"/>
-      <c r="D46" s="510" t="n"/>
-      <c r="E46" s="510" t="n"/>
-      <c r="F46" s="1241">
-        <f>F43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="19.95" customHeight="1" s="1051">
-      <c r="A47" s="538" t="inlineStr">
-        <is>
-          <t>TOTAL DIRECTO UNITARIO</t>
-        </is>
-      </c>
-      <c r="B47" s="1242" t="n"/>
-      <c r="C47" s="1242" t="n"/>
-      <c r="D47" s="1242" t="n"/>
-      <c r="E47" s="1242" t="n"/>
-      <c r="F47" s="1243">
-        <f>SUM(F44:F46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="4.5" customHeight="1" s="1051">
-      <c r="A48" s="71" t="n"/>
-      <c r="B48" s="51" t="n"/>
-      <c r="C48" s="51" t="n"/>
-      <c r="D48" s="51" t="n"/>
-      <c r="E48" s="51" t="n"/>
-      <c r="F48" s="72" t="n"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="1051">
-      <c r="A49" s="546" t="inlineStr">
-        <is>
-          <t>ELABORADO POR</t>
-        </is>
-      </c>
-      <c r="B49" s="547" t="n"/>
-      <c r="C49" s="221" t="n"/>
-      <c r="D49" s="549" t="inlineStr">
-        <is>
-          <t>Vo. Bo. INTERVENTORÍA:</t>
-        </is>
-      </c>
-      <c r="E49" s="547" t="n"/>
-      <c r="F49" s="550" t="n"/>
-    </row>
-    <row r="50" ht="42" customHeight="1" s="1051">
-      <c r="A50" s="463" t="inlineStr">
-        <is>
-          <t>FIRMA:</t>
-        </is>
-      </c>
-      <c r="B50" s="504" t="n"/>
-      <c r="C50" s="870" t="n"/>
-      <c r="D50" s="464" t="inlineStr">
-        <is>
-          <t>FIRMA:</t>
-        </is>
-      </c>
-      <c r="E50" s="548" t="n"/>
-      <c r="F50" s="907" t="n"/>
-    </row>
-    <row r="51" ht="24.75" customHeight="1" s="1051">
-      <c r="A51" s="463" t="inlineStr">
-        <is>
-          <t>NOMBRE:</t>
-        </is>
-      </c>
-      <c r="B51" s="504" t="n"/>
-      <c r="C51" s="870" t="n"/>
-      <c r="D51" s="464" t="inlineStr">
-        <is>
-          <t>NOMBRE:</t>
-        </is>
-      </c>
-      <c r="E51" s="535" t="n"/>
-      <c r="F51" s="907" t="n"/>
-    </row>
-    <row r="52" ht="24.75" customHeight="1" s="1051">
-      <c r="A52" s="463" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="B52" s="504" t="n"/>
-      <c r="C52" s="870" t="n"/>
-      <c r="D52" s="464" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="E52" s="535" t="n"/>
-      <c r="F52" s="907" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="1051">
-      <c r="A53" s="232" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="F53" s="1122">
-        <f>F5</f>
-        <v/>
+    <row r="143">
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A1:B8"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A40:B40"/>
+  <mergeCells count="55">
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="F53:J53"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="A1:C8"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="E39:J39"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="169" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="164">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1194,45 +1194,8 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF17365D"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF17365D"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF17365D"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF17365D"/>
-      <sz val="16"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF17365D"/>
-      <sz val="16"/>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="77">
@@ -1689,7 +1652,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="410">
+  <borders count="400">
     <border>
       <left/>
       <right/>
@@ -3247,6 +3210,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB7C3D0"/>
       </left>
@@ -3626,6 +3600,80 @@
       <right/>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -4011,6 +4059,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="3" tint="0.5999633777886288"/>
@@ -6024,229 +6087,17 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
         <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF17365D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF17365D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF17365D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF17365D"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF17365D"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF17365D"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -6375,6 +6226,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="medium">
         <color theme="4" tint="0.5999633777886288"/>
@@ -6389,17 +6251,6 @@
       </right>
       <top style="medium">
         <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C2CC"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -6491,6 +6342,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -6512,17 +6374,6 @@
       <bottom style="thin">
         <color rgb="FF17365D"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </left>
-      <right style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -6570,7 +6421,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1415">
+  <cellXfs count="1366">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -6702,6 +6553,9 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="39" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6916,6 +6770,9 @@
     <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="105" fillId="44" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6967,7 +6824,7 @@
     <xf numFmtId="0" fontId="20" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6991,7 +6848,7 @@
     <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7000,37 +6857,37 @@
     <xf numFmtId="0" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7044,32 +6901,32 @@
     <xf numFmtId="0" fontId="113" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="92" fillId="20" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="20" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7101,6 +6958,18 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="5" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="112" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
@@ -7177,38 +7046,38 @@
     <xf numFmtId="0" fontId="125" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="54" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
@@ -7224,15 +7093,15 @@
     <xf numFmtId="0" fontId="59" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="69" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="70" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="70" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7250,46 +7119,46 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="140" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="150" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="61" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="61" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7330,10 +7199,10 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7373,19 +7242,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="41" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -7449,31 +7318,34 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="26" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="26" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7484,64 +7356,67 @@
     <xf numFmtId="0" fontId="156" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="25" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="74" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="28" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="75" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="17" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="16" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="75" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="17" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="16" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="25" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="25" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="74" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="17" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="16" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="28" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="75" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="17" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="16" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="75" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="17" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="16" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="25" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7556,25 +7431,25 @@
     <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7603,11 +7478,11 @@
     </xf>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7646,10 +7521,10 @@
     <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7658,28 +7533,28 @@
     <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7701,7 +7576,7 @@
     <xf numFmtId="165" fontId="35" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="18" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="33" fillId="18" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="56" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7716,11 +7591,11 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7729,7 +7604,7 @@
     <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7739,6 +7614,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7757,22 +7635,22 @@
     <xf numFmtId="0" fontId="54" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7781,33 +7659,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="37" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="42" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="149" fillId="42" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7826,147 +7704,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="37" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="161" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7988,38 +7748,20 @@
     <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="85" fillId="52" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8027,31 +7769,59 @@
     <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="116" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="149" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="87" fillId="49" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="28" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="117" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="205" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8063,24 +7833,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="102" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8101,9 +7871,6 @@
     </xf>
     <xf numFmtId="0" fontId="115" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="94" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8112,138 +7879,128 @@
     <xf numFmtId="0" fontId="93" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="280" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="61" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="62" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="72" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="61" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="61" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="62" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="72" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="61" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="135" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="62" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="135" fillId="62" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
@@ -8268,44 +8025,44 @@
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="25" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="76" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="71" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="131" fillId="71" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="110" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="61" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8318,18 +8075,34 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="111" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="111" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="3" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="155" fillId="3" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="49" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -8337,96 +8110,80 @@
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="49" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="34" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="34" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="20" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="110" fillId="20" borderId="200" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="201" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="42" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="42" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="20" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8442,22 +8199,22 @@
     <xf numFmtId="0" fontId="82" fillId="59" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="51" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8471,10 +8228,10 @@
     <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="104" fillId="28" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8522,35 +8279,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="210" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="211" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="207" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -8564,9 +8307,31 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="218" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="219" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8574,16 +8339,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8596,7 +8365,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -8610,10 +8379,10 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="105" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8629,7 +8398,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8640,141 +8409,129 @@
     <xf numFmtId="0" fontId="109" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="106" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="124" fillId="57" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="57" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="28" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="126" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="229" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="28" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="28" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="28" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="54" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="41" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="227" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="28" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="55" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="228" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="55" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8825,7 +8582,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8839,8 +8596,8 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -8853,13 +8610,55 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="25" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8869,92 +8668,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="236" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="228" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8964,75 +8687,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="224" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="232" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="96" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="227" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="59" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="229" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="69" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9045,8 +8769,8 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="57" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9065,967 +8789,969 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="260" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="261" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="14" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="50" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="16" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="167" fontId="38" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="14" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="60" fillId="58" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="157" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="37" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="37" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="37" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="139" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="140" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="54" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="54" fillId="20" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="54" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="54" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="129" fillId="56" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="126" fillId="55" borderId="189" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="126" fillId="55" borderId="190" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="16" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="47" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="58" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="48" fillId="3" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="29" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="58" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="16" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="25" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="50" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="167" fontId="38" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="22" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="339" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="55" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="49" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="25" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="25" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="25" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="28" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="28" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="28" borderId="375" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="28" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="28" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="28" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="37" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="159" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="157" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="139" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="140" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="47" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="54" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="61" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="54" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="54" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="54" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="43" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="42" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="184" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="129" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="126" fillId="55" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="126" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="52" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="408" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="46" fillId="16" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="47" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="47" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="43" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="48" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="58" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="48" fillId="3" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="50" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="50" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="37" fillId="16" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="37" fillId="16" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="405" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="396" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="52" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -10051,10 +9777,10 @@
     <xf numFmtId="165" fontId="35" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="18" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="33" fillId="18" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="35" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -10069,7 +9795,7 @@
     <xf numFmtId="167" fontId="57" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -10085,7 +9811,7 @@
     <xf numFmtId="165" fontId="34" fillId="16" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="406" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="394" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10683,13 +10409,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>237075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10723,13 +10449,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>110085</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>256680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>493125</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>33120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10767,9 +10493,9 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2556750</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2747250</xdr:colOff>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>141525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10803,13 +10529,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>49468</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>27346</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>553468</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>8088</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10834,206 +10560,6 @@
         </a:prstGeom>
         <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2118075</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>49050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 5" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2981325" y="3800475"/>
-          <a:ext cx="756000" cy="792000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>455083</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>34926</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>959083</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>466926</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Imagen 9"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="455083" y="3971926"/>
-          <a:ext cx="504000" cy="432000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1485900</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>324150</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Imagen 19"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6781800" y="3895725"/>
-          <a:ext cx="648000" cy="648000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1239675</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>551625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 23"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9553575" y="3962400"/>
-          <a:ext cx="792000" cy="504000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1458900</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>5625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Imagen 25"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="11449050" y="3829050"/>
-          <a:ext cx="1116000" cy="720000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
@@ -11227,3374 +10753,801 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB143"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20.77734375" customWidth="1" style="1062" min="1" max="1"/>
-    <col width="2.77734375" customWidth="1" style="1062" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="1062" min="3" max="3"/>
-    <col width="2.77734375" customWidth="1" style="1062" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="1062" min="5" max="6"/>
-    <col width="2.77734375" customWidth="1" style="1062" min="7" max="7"/>
-    <col width="26.33203125" customWidth="1" style="1062" min="8" max="8"/>
-    <col width="2.77734375" customWidth="1" style="1062" min="9" max="9"/>
-    <col width="26" customWidth="1" style="1062" min="10" max="10"/>
-    <col width="4.77734375" customWidth="1" style="1062" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" style="1062" min="25" max="25"/>
-    <col hidden="1" width="13" customWidth="1" style="1062" min="26" max="26"/>
-    <col hidden="1" width="13" customWidth="1" style="1062" min="27" max="27"/>
-    <col hidden="1" width="13" customWidth="1" style="1062" min="28" max="28"/>
+    <col width="20.77734375" customWidth="1" style="1051" min="1" max="1"/>
+    <col width="50.77734375" customWidth="1" style="1051" min="2" max="2"/>
+    <col width="26.33203125" customWidth="1" style="1051" min="3" max="5"/>
+    <col width="26" customWidth="1" style="1051" min="6" max="6"/>
+    <col width="4.77734375" customWidth="1" style="1051" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="1062">
-      <c r="E1" s="548" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="1051">
+      <c r="C1" s="513" t="inlineStr">
         <is>
           <t>ANÁLISIS DE PRECIOS UNITARIOS</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Actividad</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Rendimiento</t>
-        </is>
-      </c>
     </row>
-    <row r="2" ht="4.95" customHeight="1" s="1062">
-      <c r="E2" s="553" t="n"/>
-      <c r="J2" s="554" t="n"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Replanteo general de ejes y niveles</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>1 Topógrafo + 1 Cadenero</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>150</v>
-      </c>
+    <row r="2" ht="4.95" customHeight="1" s="1051">
+      <c r="C2" s="518" t="n"/>
+      <c r="F2" s="519" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="1062">
-      <c r="E3" s="288" t="n"/>
-      <c r="F3" s="288" t="n"/>
-      <c r="G3" s="288" t="n"/>
-      <c r="H3" s="563" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="1051">
+      <c r="C3" s="294" t="n"/>
+      <c r="D3" s="294" t="n"/>
+      <c r="E3" s="520" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="I3" s="694" t="n"/>
-      <c r="J3" s="564" t="n"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Cerramiento provisional de obra</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>40</v>
-      </c>
+      <c r="F3" s="521" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="1062">
-      <c r="E4" s="288" t="n"/>
-      <c r="F4" s="288" t="n"/>
-      <c r="G4" s="288" t="n"/>
-      <c r="H4" s="10" t="inlineStr">
+    <row r="4" hidden="1" ht="15" customHeight="1" s="1051">
+      <c r="C4" s="294" t="n"/>
+      <c r="D4" s="294" t="n"/>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="82" t="n"/>
-      <c r="K4" s="119" t="n"/>
-      <c r="M4" s="119" t="n"/>
-      <c r="P4" s="119">
-        <f>IFERROR(VLOOKUP($A$10,$Y$2:$AB$143,2,0),"")</f>
-        <v/>
+      <c r="F4" s="83" t="n"/>
+      <c r="G4" s="120" t="n"/>
+      <c r="I4" s="120" t="n"/>
+      <c r="L4" s="120" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
       </c>
-      <c r="Q4" s="119" t="n"/>
-      <c r="R4" s="120" t="n"/>
-      <c r="S4" s="121">
-        <f>IFERROR(IF(VLOOKUP($A$10,$Y$2:$AB$143,3,0)=0,"",VLOOKUP($A$10,$Y$2:$AB$143,3,0)),"")</f>
-        <v/>
+      <c r="M4" s="120" t="n"/>
+      <c r="N4" s="121" t="n"/>
+      <c r="O4" s="122" t="inlineStr">
+        <is>
+          <t>1 Topógrafo + 1 Cadenero 1o</t>
+        </is>
       </c>
-      <c r="T4" s="120" t="n"/>
-      <c r="U4" s="600" t="n">
+      <c r="P4" s="121" t="n"/>
+      <c r="Q4" s="122" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="121">
-        <f>IFERROR(IF(VLOOKUP($A$10,$Y$2:$AB$143,4,0)=0,"",VLOOKUP($A$10,$Y$2:$AB$143,4,0)),"")</f>
-        <v/>
+      <c r="R4" s="122" t="n">
+        <v>100</v>
       </c>
-      <c r="W4" s="121">
-        <f>IF(P4="","",P4&amp;"/jornada")</f>
-        <v/>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="S4" s="122" t="inlineStr">
         <is>
-          <t>Instalación de campamento y oficinas provisionales</t>
+          <t>m2/jornada</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="1062">
-      <c r="E5" s="565" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="1051">
+      <c r="C5" s="522" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="H5" s="124" t="inlineStr">
+      <c r="E5" s="125" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="I5" s="814" t="n"/>
-      <c r="J5" s="202" t="inlineStr">
+      <c r="F5" s="208" t="inlineStr">
         <is>
           <t>RYR-AP-001</t>
         </is>
       </c>
-      <c r="K5" s="119" t="n"/>
-      <c r="M5" s="119" t="n"/>
-      <c r="P5" s="119" t="n"/>
-      <c r="Q5" s="119" t="n"/>
-      <c r="R5" s="120" t="n"/>
-      <c r="S5" s="121" t="n"/>
-      <c r="T5" s="120" t="n"/>
-      <c r="U5" s="121" t="n"/>
-      <c r="V5" s="121" t="n"/>
-      <c r="W5" s="121" t="n"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Adecuación de área de almacenamiento</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>25</v>
-      </c>
+      <c r="G5" s="120" t="n"/>
+      <c r="I5" s="120" t="n"/>
+      <c r="L5" s="120" t="n"/>
+      <c r="M5" s="120" t="n"/>
+      <c r="N5" s="121" t="n"/>
+      <c r="O5" s="122" t="n"/>
+      <c r="P5" s="121" t="n"/>
+      <c r="Q5" s="122" t="n"/>
+      <c r="R5" s="122" t="n"/>
+      <c r="S5" s="122" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="1062">
-      <c r="E6" s="356" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="1051">
+      <c r="C6" s="363" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="F6" s="288" t="n"/>
-      <c r="G6" s="288" t="n"/>
-      <c r="H6" s="216" t="inlineStr">
+      <c r="D6" s="294" t="n"/>
+      <c r="E6" s="222" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="I6" s="823" t="n"/>
-      <c r="J6" s="202" t="n">
+      <c r="F6" s="208" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="119" t="n"/>
-      <c r="M6" s="119" t="n"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Señalización preventiva e informativa de obra</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
+      <c r="G6" s="120" t="n"/>
+      <c r="I6" s="120" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="1062">
-      <c r="E7" s="201" t="n"/>
-      <c r="F7" s="288" t="n"/>
-      <c r="G7" s="288" t="n"/>
-      <c r="H7" s="124" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="1051">
+      <c r="C7" s="207" t="n"/>
+      <c r="D7" s="294" t="n"/>
+      <c r="E7" s="125" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="I7" s="814" t="n"/>
-      <c r="J7" s="202" t="inlineStr">
+      <c r="F7" s="208" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="K7" s="119" t="n"/>
-      <c r="M7" s="119" t="n"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Instalaciones provisionales de agua y energía</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
+      <c r="G7" s="120" t="n"/>
+      <c r="I7" s="120" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1062">
-      <c r="E8" s="288" t="n"/>
-      <c r="F8" s="288" t="n"/>
-      <c r="G8" s="288" t="n"/>
-      <c r="H8" s="124" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="1051">
+      <c r="C8" s="294" t="n"/>
+      <c r="D8" s="294" t="n"/>
+      <c r="E8" s="125" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="I8" s="814" t="n"/>
-      <c r="J8" s="202" t="inlineStr">
+      <c r="F8" s="208" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="K8" s="119" t="n"/>
-      <c r="M8" s="119" t="n"/>
-      <c r="Y8" t="inlineStr">
+      <c r="G8" s="120" t="n"/>
+      <c r="I8" s="120" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1051">
+      <c r="A9" s="294">
+        <f>"Cuadrilla: "&amp;O4&amp;"   |   Unidad: "&amp;L4&amp;"   |   Jornada: "&amp;Q4&amp;" h   |   Rendimiento: "&amp;R4&amp;" "&amp;S4&amp;"   |   Consumo M.O.: "&amp;IFERROR(TEXT(Q4/R4,"0.00"),"—")&amp;" h/"&amp;L4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="25.05" customHeight="1" s="1051">
+      <c r="A10" s="542" t="inlineStr">
         <is>
-          <t>Protección de elementos existentes</t>
+          <t>LOCALIZACIÓN Y REPLANTEO</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>30</v>
-      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1062">
-      <c r="A9" s="288" t="n"/>
-      <c r="B9" s="288" t="n"/>
-      <c r="C9" s="288" t="n"/>
-      <c r="D9" s="288" t="n"/>
-      <c r="E9" s="288" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Desmonte y limpieza inicial</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>80</v>
-      </c>
+    <row r="11" ht="15" customHeight="1" s="1051">
+      <c r="A11" s="528" t="n"/>
     </row>
-    <row r="10" ht="25.05" customHeight="1" s="1062">
-      <c r="A10" s="573" t="n"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Demoliciones preliminares</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="1062">
-      <c r="A11" s="566" t="n"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Excavación manual en material común</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="1062">
-      <c r="A12" s="550" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="1051">
+      <c r="A12" s="515" t="inlineStr">
         <is>
           <t>IDENTIFICACIÓN DEL PROYECTO</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Excavación mecánica</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1 Operador retroexcavadora + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>60</v>
-      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1062">
-      <c r="A13" s="535" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="1051">
+      <c r="A13" s="364" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B13" s="529" t="n"/>
-      <c r="C13" s="1283" t="n"/>
-      <c r="D13" s="558" t="n"/>
-      <c r="E13" s="558" t="n"/>
-      <c r="F13" s="558" t="n"/>
-      <c r="G13" s="558" t="n"/>
-      <c r="H13" s="558" t="n"/>
-      <c r="I13" s="558" t="n"/>
-      <c r="J13" s="562" t="n"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Excavación en roca</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>1 Operador + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>15</v>
-      </c>
+      <c r="B13" s="533" t="n"/>
+      <c r="C13" s="534" t="n"/>
+      <c r="D13" s="534" t="n"/>
+      <c r="E13" s="534" t="n"/>
+      <c r="F13" s="526" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1062">
-      <c r="A14" s="535" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="1051">
+      <c r="A14" s="364" t="inlineStr">
         <is>
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B14" s="529" t="n"/>
-      <c r="C14" s="567" t="n"/>
-      <c r="D14" s="558" t="n"/>
-      <c r="E14" s="558" t="n"/>
-      <c r="F14" s="530" t="n"/>
-      <c r="G14" s="530" t="n"/>
-      <c r="H14" s="529" t="inlineStr">
+      <c r="B14" s="530" t="n"/>
+      <c r="C14" s="526" t="n"/>
+      <c r="D14" s="206" t="n"/>
+      <c r="E14" s="364" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="I14" s="529" t="n"/>
-      <c r="J14" s="536" t="n"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Perfilado y conformación de excavaciones</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>40</v>
-      </c>
+      <c r="F14" s="460" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="1062">
-      <c r="A15" s="535" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="1051">
+      <c r="A15" s="364" t="inlineStr">
         <is>
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B15" s="529" t="n"/>
-      <c r="C15" s="557" t="inlineStr">
+      <c r="B15" s="525" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="D15" s="558" t="n"/>
-      <c r="E15" s="558" t="n"/>
-      <c r="F15" s="530" t="n"/>
-      <c r="G15" s="530" t="n"/>
-      <c r="H15" s="529" t="inlineStr">
+      <c r="C15" s="526" t="n"/>
+      <c r="D15" s="206" t="n"/>
+      <c r="E15" s="364" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I15" s="529" t="n"/>
-      <c r="J15" s="536" t="n"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Relleno con material seleccionado compactado</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>25</v>
-      </c>
+      <c r="F15" s="460" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="1062" thickBot="1">
-      <c r="A16" s="1244" t="n"/>
-      <c r="B16" s="640" t="n"/>
-      <c r="C16" s="640" t="n"/>
-      <c r="D16" s="640" t="n"/>
-      <c r="E16" s="640" t="n"/>
-      <c r="F16" s="640" t="n"/>
-      <c r="G16" s="640" t="n"/>
-      <c r="H16" s="640" t="n"/>
-      <c r="I16" s="640" t="n"/>
-      <c r="J16" s="640" t="n"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Relleno con material proveniente de excavación</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>30</v>
-      </c>
+    <row r="16" ht="15" customHeight="1" s="1051">
+      <c r="A16" s="540" t="n"/>
+      <c r="B16" s="541" t="n"/>
+      <c r="C16" s="541" t="n"/>
+      <c r="D16" s="541" t="n"/>
+      <c r="E16" s="541" t="n"/>
+      <c r="F16" s="541" t="n"/>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="1062" thickTop="1">
-      <c r="A17" s="1269" t="inlineStr">
-        <is>
-          <t>UNIDAD</t>
-        </is>
-      </c>
-      <c r="B17" s="1278" t="n"/>
-      <c r="C17" s="1269" t="inlineStr">
-        <is>
-          <t>CUADRILLA</t>
-        </is>
-      </c>
-      <c r="D17" s="1260" t="n"/>
-      <c r="E17" s="1269" t="inlineStr">
-        <is>
-          <t>JORNADA</t>
-        </is>
-      </c>
-      <c r="F17" s="1284" t="n"/>
-      <c r="G17" s="1260" t="n"/>
-      <c r="H17" s="1269" t="inlineStr">
-        <is>
-          <t>RENDIMIENTO</t>
-        </is>
-      </c>
-      <c r="I17" s="1277" t="n"/>
-      <c r="J17" s="1269" t="inlineStr">
-        <is>
-          <t>CONSUMO M.O.</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Suministro, extendido y compactación de subbase</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" ht="25.05" customFormat="1" customHeight="1" s="1276">
-      <c r="A18" s="1279">
-        <f>P4</f>
-        <v/>
-      </c>
-      <c r="B18" s="1278" t="n"/>
-      <c r="C18" s="1279">
-        <f>S4</f>
-        <v/>
-      </c>
-      <c r="D18" s="1285" t="n"/>
-      <c r="E18" s="1279">
-        <f>U4</f>
-        <v/>
-      </c>
-      <c r="F18" s="1286" t="n"/>
-      <c r="G18" s="1285" t="n"/>
-      <c r="H18" s="1279">
-        <f>IF(V4="","",V4&amp;" "&amp;W4)</f>
-        <v/>
-      </c>
-      <c r="J18" s="1282">
-        <f>IFERROR(U4/V4,"")</f>
-        <v/>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Suministro, extendido y compactación de base granular</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" ht="49.95" customFormat="1" customHeight="1" s="1276" thickBot="1">
-      <c r="A19" s="1272" t="n"/>
-      <c r="B19" s="1261" t="n"/>
-      <c r="C19" s="1273" t="n"/>
-      <c r="D19" s="1285" t="n"/>
-      <c r="E19" s="1272" t="n"/>
-      <c r="F19" s="1287" t="n"/>
-      <c r="G19" s="1285" t="n"/>
-      <c r="H19" s="1272" t="n"/>
-      <c r="J19" s="1272" t="n"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Cargue de material sobrante</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="528" thickTop="1">
-      <c r="A20" s="1245" t="n"/>
-      <c r="B20" s="711" t="n"/>
-      <c r="C20" s="711" t="n"/>
-      <c r="D20" s="711" t="n"/>
-      <c r="E20" s="711" t="n"/>
-      <c r="F20" s="711" t="n"/>
-      <c r="G20" s="711" t="n"/>
-      <c r="H20" s="711" t="n"/>
-      <c r="I20" s="711" t="n"/>
-      <c r="J20" s="711" t="n"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Transporte de material sobrante</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1062">
-      <c r="A21" s="537" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="1051">
+      <c r="A17" s="203" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B21" s="1246" t="n"/>
-      <c r="C21" s="538" t="inlineStr">
+      <c r="B17" s="359" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="D21" s="1262" t="n"/>
-      <c r="E21" s="574" t="n"/>
-      <c r="F21" s="575" t="n"/>
-      <c r="G21" s="575" t="n"/>
-      <c r="H21" s="575" t="n"/>
-      <c r="I21" s="575" t="n"/>
-      <c r="J21" s="1288" t="n"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Disposición final de sobrantes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+      <c r="C17" s="543" t="n"/>
+      <c r="D17" s="544" t="n"/>
+      <c r="E17" s="544" t="n"/>
+      <c r="F17" s="545" t="n"/>
     </row>
-    <row r="22" ht="15" customFormat="1" customHeight="1" s="665">
-      <c r="A22" s="531" t="n"/>
-      <c r="B22" s="1247" t="n"/>
-      <c r="C22" s="532" t="inlineStr">
+    <row r="18" ht="15" customFormat="1" customHeight="1" s="629">
+      <c r="A18" s="204" t="n"/>
+      <c r="B18" s="132" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D22" s="533" t="n"/>
-      <c r="E22" s="533" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F22" s="533" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G22" s="533" t="n"/>
-      <c r="H22" s="533" t="inlineStr">
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I22" s="533" t="n"/>
-      <c r="J22" s="534" t="inlineStr">
+      <c r="F18" s="205" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Concreto de limpieza / solado</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB22" t="n">
-        <v>12</v>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="1051">
+      <c r="A19" s="514" t="n"/>
+      <c r="B19" s="510" t="n"/>
+      <c r="C19" s="118" t="n"/>
+      <c r="D19" s="119" t="n"/>
+      <c r="E19" s="1234" t="n"/>
+      <c r="F19" s="1235">
+        <f>D19*E19</f>
+        <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="1062">
-      <c r="A23" s="549" t="n"/>
-      <c r="B23" s="545" t="n"/>
-      <c r="C23" s="545" t="n"/>
-      <c r="D23" s="545" t="n"/>
-      <c r="E23" s="117" t="n"/>
-      <c r="F23" s="118" t="n"/>
-      <c r="G23" s="118" t="n"/>
-      <c r="H23" s="1289" t="n"/>
-      <c r="I23" s="1289" t="n"/>
-      <c r="J23" s="1290">
-        <f>F23*H23</f>
+    <row r="20" ht="15" customHeight="1" s="1051">
+      <c r="A20" s="514" t="n"/>
+      <c r="B20" s="510" t="n"/>
+      <c r="C20" s="118" t="n"/>
+      <c r="D20" s="119" t="n"/>
+      <c r="E20" s="1234" t="n"/>
+      <c r="F20" s="1235">
+        <f>D20*E20</f>
         <v/>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Concreto para zapatas</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB23" t="n">
-        <v>10</v>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="1051">
+      <c r="A21" s="514" t="n"/>
+      <c r="B21" s="510" t="n"/>
+      <c r="C21" s="118" t="n"/>
+      <c r="D21" s="119" t="n"/>
+      <c r="E21" s="1234" t="n"/>
+      <c r="F21" s="1235">
+        <f>D21*E21</f>
+        <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="1062">
-      <c r="A24" s="549" t="n"/>
-      <c r="B24" s="545" t="n"/>
-      <c r="C24" s="545" t="n"/>
-      <c r="D24" s="545" t="n"/>
-      <c r="E24" s="117" t="n"/>
-      <c r="F24" s="118" t="n"/>
-      <c r="G24" s="118" t="n"/>
-      <c r="H24" s="1289" t="n"/>
-      <c r="I24" s="1289" t="n"/>
-      <c r="J24" s="1290">
-        <f>F24*H24</f>
+    <row r="22" ht="15" customHeight="1" s="1051">
+      <c r="A22" s="514" t="n"/>
+      <c r="B22" s="510" t="n"/>
+      <c r="C22" s="118" t="n"/>
+      <c r="D22" s="119" t="n"/>
+      <c r="E22" s="1234" t="n"/>
+      <c r="F22" s="1235">
+        <f>D22*E22</f>
         <v/>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Concreto para vigas de cimentación</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB24" t="n">
-        <v>8</v>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="1051">
+      <c r="A23" s="514" t="n"/>
+      <c r="B23" s="510" t="n"/>
+      <c r="C23" s="118" t="n"/>
+      <c r="D23" s="119" t="n"/>
+      <c r="E23" s="1234" t="n"/>
+      <c r="F23" s="1235">
+        <f>D23*E23</f>
+        <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="1062">
-      <c r="A25" s="549" t="n"/>
-      <c r="B25" s="545" t="n"/>
-      <c r="C25" s="545" t="n"/>
-      <c r="D25" s="545" t="n"/>
-      <c r="E25" s="117" t="n"/>
-      <c r="F25" s="118" t="n"/>
-      <c r="G25" s="118" t="n"/>
-      <c r="H25" s="1289" t="n"/>
-      <c r="I25" s="1289" t="n"/>
-      <c r="J25" s="1290">
-        <f>F25*H25</f>
+    <row r="24" ht="15" customHeight="1" s="1051">
+      <c r="A24" s="514" t="n"/>
+      <c r="B24" s="510" t="n"/>
+      <c r="C24" s="118" t="n"/>
+      <c r="D24" s="119" t="n"/>
+      <c r="E24" s="1236" t="n"/>
+      <c r="F24" s="1235">
+        <f>D24*E24</f>
         <v/>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Concreto para losas de cimentación</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>1 Oficial + 4 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB25" t="n">
-        <v>15</v>
-      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="1062">
-      <c r="A26" s="549" t="n"/>
-      <c r="B26" s="545" t="n"/>
-      <c r="C26" s="545" t="n"/>
-      <c r="D26" s="545" t="n"/>
-      <c r="E26" s="117" t="n"/>
-      <c r="F26" s="118" t="n"/>
-      <c r="G26" s="118" t="n"/>
-      <c r="H26" s="1289" t="n"/>
-      <c r="I26" s="1289" t="n"/>
-      <c r="J26" s="1290">
-        <f>F26*H26</f>
-        <v/>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Concreto para pedestales</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB26" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="1062">
-      <c r="A27" s="549" t="n"/>
-      <c r="B27" s="545" t="n"/>
-      <c r="C27" s="545" t="n"/>
-      <c r="D27" s="545" t="n"/>
-      <c r="E27" s="117" t="n"/>
-      <c r="F27" s="118" t="n"/>
-      <c r="G27" s="118" t="n"/>
-      <c r="H27" s="1289" t="n"/>
-      <c r="I27" s="1289" t="n"/>
-      <c r="J27" s="1290">
-        <f>F27*H27</f>
-        <v/>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Acero de refuerzo en cimentación</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB27" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="1062">
-      <c r="A28" s="549" t="n"/>
-      <c r="B28" s="545" t="n"/>
-      <c r="C28" s="545" t="n"/>
-      <c r="D28" s="545" t="n"/>
-      <c r="E28" s="117" t="n"/>
-      <c r="F28" s="118" t="n"/>
-      <c r="G28" s="118" t="n"/>
-      <c r="H28" s="1291" t="n"/>
-      <c r="I28" s="1291" t="n"/>
-      <c r="J28" s="1290">
-        <f>F28*H28</f>
-        <v/>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Formaleta para elementos de cimentación</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB28" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1062">
-      <c r="A29" s="551" t="n"/>
-      <c r="B29" s="552" t="n"/>
-      <c r="C29" s="552" t="n"/>
-      <c r="D29" s="552" t="n"/>
-      <c r="E29" s="582" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="1051">
+      <c r="A25" s="516" t="n"/>
+      <c r="B25" s="517" t="n"/>
+      <c r="C25" s="532" t="inlineStr">
         <is>
           <t>SUBTOTAL MATERIALES</t>
         </is>
       </c>
-      <c r="F29" s="552" t="n"/>
-      <c r="G29" s="552" t="n"/>
-      <c r="H29" s="552" t="n"/>
-      <c r="I29" s="552" t="n"/>
-      <c r="J29" s="1292">
-        <f>SUM(J23:J28)</f>
+      <c r="D25" s="517" t="n"/>
+      <c r="E25" s="517" t="n"/>
+      <c r="F25" s="1237">
+        <f>SUM(F19:F24)</f>
         <v/>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Concreto para columnas</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB29" t="n">
-        <v>6</v>
-      </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="1062">
-      <c r="A30" s="200" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="1051">
+      <c r="A26" s="202" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B30" s="1250" t="n"/>
-      <c r="C30" s="353" t="inlineStr">
+      <c r="B26" s="360" t="inlineStr">
         <is>
           <t>MANO DE OBRA</t>
         </is>
       </c>
-      <c r="D30" s="353" t="n"/>
-      <c r="E30" s="541" t="n"/>
-      <c r="F30" s="542" t="n"/>
-      <c r="G30" s="542" t="n"/>
-      <c r="H30" s="542" t="n"/>
-      <c r="I30" s="542" t="n"/>
-      <c r="J30" s="543" t="n"/>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Concreto para vigas</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB30" t="n">
-        <v>8</v>
-      </c>
+      <c r="C26" s="506" t="n"/>
+      <c r="D26" s="507" t="n"/>
+      <c r="E26" s="507" t="n"/>
+      <c r="F26" s="508" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="1062">
-      <c r="A31" s="67" t="n"/>
-      <c r="B31" s="1251" t="n"/>
-      <c r="C31" s="51" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="1051">
+      <c r="A27" s="68" t="n"/>
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D31" s="51" t="n"/>
-      <c r="E31" s="51" t="inlineStr">
+      <c r="C27" s="52" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F31" s="51" t="inlineStr">
+      <c r="D27" s="52" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G31" s="51" t="n"/>
-      <c r="H31" s="51" t="inlineStr">
+      <c r="E27" s="52" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I31" s="51" t="n"/>
-      <c r="J31" s="68" t="inlineStr">
+      <c r="F27" s="69" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Concreto para losas</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>1 Oficial + 4 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB31" t="n">
-        <v>15</v>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1051">
+      <c r="A28" s="509" t="n"/>
+      <c r="B28" s="510" t="n"/>
+      <c r="C28" s="118" t="n"/>
+      <c r="D28" s="1238" t="n"/>
+      <c r="E28" s="1234" t="n"/>
+      <c r="F28" s="1239">
+        <f>D28*E28</f>
+        <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="1062">
-      <c r="A32" s="544" t="n"/>
-      <c r="B32" s="545" t="n"/>
-      <c r="C32" s="545" t="n"/>
-      <c r="D32" s="545" t="n"/>
-      <c r="E32" s="117" t="n"/>
-      <c r="F32" s="1293" t="n"/>
-      <c r="G32" s="1293" t="n"/>
-      <c r="H32" s="1289" t="n"/>
-      <c r="I32" s="1289" t="n"/>
-      <c r="J32" s="1294">
-        <f>F32*H32</f>
+    <row r="29" ht="15" customHeight="1" s="1051">
+      <c r="A29" s="509" t="n"/>
+      <c r="B29" s="510" t="n"/>
+      <c r="C29" s="118" t="n"/>
+      <c r="D29" s="1238" t="n"/>
+      <c r="E29" s="1234" t="n"/>
+      <c r="F29" s="1239">
+        <f>D29*E29</f>
         <v/>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Concreto para escaleras</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB32" t="n">
-        <v>4</v>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="1051">
+      <c r="A30" s="509" t="n"/>
+      <c r="B30" s="510" t="n"/>
+      <c r="C30" s="118" t="n"/>
+      <c r="D30" s="1238" t="n"/>
+      <c r="E30" s="1234" t="n"/>
+      <c r="F30" s="1239">
+        <f>D30*E30</f>
+        <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="1062">
-      <c r="A33" s="544" t="n"/>
-      <c r="B33" s="545" t="n"/>
-      <c r="C33" s="545" t="n"/>
-      <c r="D33" s="545" t="n"/>
-      <c r="E33" s="117" t="n"/>
-      <c r="F33" s="1293" t="n"/>
-      <c r="G33" s="1293" t="n"/>
-      <c r="H33" s="1289" t="n"/>
-      <c r="I33" s="1289" t="n"/>
-      <c r="J33" s="1294">
-        <f>F33*H33</f>
+    <row r="31" ht="15" customHeight="1" s="1051">
+      <c r="A31" s="509" t="n"/>
+      <c r="B31" s="510" t="n"/>
+      <c r="C31" s="118" t="n"/>
+      <c r="D31" s="1238" t="n"/>
+      <c r="E31" s="1234" t="n"/>
+      <c r="F31" s="1239">
+        <f>D31*E31</f>
         <v/>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Concreto para muros estructurales</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB33" t="n">
-        <v>8</v>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="1051">
+      <c r="A32" s="509" t="n"/>
+      <c r="B32" s="510" t="n"/>
+      <c r="C32" s="118" t="n"/>
+      <c r="D32" s="1238" t="n"/>
+      <c r="E32" s="1234" t="n"/>
+      <c r="F32" s="1239">
+        <f>D32*E32</f>
+        <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="1062">
-      <c r="A34" s="544" t="n"/>
-      <c r="B34" s="545" t="n"/>
-      <c r="C34" s="545" t="n"/>
-      <c r="D34" s="545" t="n"/>
-      <c r="E34" s="117" t="n"/>
-      <c r="F34" s="1293" t="n"/>
-      <c r="G34" s="1293" t="n"/>
-      <c r="H34" s="1289" t="n"/>
-      <c r="I34" s="1289" t="n"/>
-      <c r="J34" s="1294">
-        <f>F34*H34</f>
+    <row r="33" ht="15" customHeight="1" s="1051">
+      <c r="A33" s="509" t="n"/>
+      <c r="B33" s="510" t="n"/>
+      <c r="C33" s="118" t="n"/>
+      <c r="D33" s="1238" t="n"/>
+      <c r="E33" s="1236" t="n"/>
+      <c r="F33" s="1239">
+        <f>D33*E33</f>
         <v/>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Acero de refuerzo de columnas</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB34" t="n">
-        <v>220</v>
-      </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="1062">
-      <c r="A35" s="544" t="n"/>
-      <c r="B35" s="545" t="n"/>
-      <c r="C35" s="545" t="n"/>
-      <c r="D35" s="545" t="n"/>
-      <c r="E35" s="117" t="n"/>
-      <c r="F35" s="1293" t="n"/>
-      <c r="G35" s="1293" t="n"/>
-      <c r="H35" s="1289" t="n"/>
-      <c r="I35" s="1289" t="n"/>
-      <c r="J35" s="1294">
-        <f>F35*H35</f>
-        <v/>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Acero de refuerzo de vigas</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB35" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="1062">
-      <c r="A36" s="544" t="n"/>
-      <c r="B36" s="545" t="n"/>
-      <c r="C36" s="545" t="n"/>
-      <c r="D36" s="545" t="n"/>
-      <c r="E36" s="117" t="n"/>
-      <c r="F36" s="1293" t="n"/>
-      <c r="G36" s="1293" t="n"/>
-      <c r="H36" s="1289" t="n"/>
-      <c r="I36" s="1289" t="n"/>
-      <c r="J36" s="1294">
-        <f>F36*H36</f>
-        <v/>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Acero de refuerzo de losas</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB36" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="1062">
-      <c r="A37" s="544" t="n"/>
-      <c r="B37" s="545" t="n"/>
-      <c r="C37" s="545" t="n"/>
-      <c r="D37" s="545" t="n"/>
-      <c r="E37" s="117" t="n"/>
-      <c r="F37" s="1293" t="n"/>
-      <c r="G37" s="1293" t="n"/>
-      <c r="H37" s="1291" t="n"/>
-      <c r="I37" s="1291" t="n"/>
-      <c r="J37" s="1294">
-        <f>F37*H37</f>
-        <v/>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Formaleta de columnas</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="1062">
-      <c r="A38" s="560" t="n"/>
-      <c r="B38" s="545" t="n"/>
-      <c r="C38" s="545" t="n"/>
-      <c r="D38" s="545" t="n"/>
-      <c r="E38" s="559" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="1051">
+      <c r="A34" s="529" t="n"/>
+      <c r="B34" s="510" t="n"/>
+      <c r="C34" s="527" t="inlineStr">
         <is>
           <t>SUBTOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="F38" s="545" t="n"/>
-      <c r="G38" s="545" t="n"/>
-      <c r="H38" s="545" t="n"/>
-      <c r="I38" s="545" t="n"/>
-      <c r="J38" s="1295">
-        <f>SUM(J32:J37)</f>
+      <c r="D34" s="510" t="n"/>
+      <c r="E34" s="510" t="n"/>
+      <c r="F34" s="1240">
+        <f>SUM(F28:F33)</f>
         <v/>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Formaleta de vigas</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB38" t="n">
-        <v>8</v>
-      </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="1062">
-      <c r="A39" s="66" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="1051">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B39" s="1253" t="n"/>
-      <c r="C39" s="354" t="inlineStr">
+      <c r="B35" s="361" t="inlineStr">
         <is>
           <t>EQUIPOS Y HERRAMIENTAS</t>
         </is>
       </c>
-      <c r="D39" s="354" t="n"/>
-      <c r="E39" s="555" t="n"/>
-      <c r="F39" s="545" t="n"/>
-      <c r="G39" s="545" t="n"/>
-      <c r="H39" s="545" t="n"/>
-      <c r="I39" s="545" t="n"/>
-      <c r="J39" s="556" t="n"/>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Formaleta de losas</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>1 Oficial + 3 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB39" t="n">
-        <v>12</v>
-      </c>
+      <c r="C35" s="523" t="n"/>
+      <c r="D35" s="510" t="n"/>
+      <c r="E35" s="510" t="n"/>
+      <c r="F35" s="524" t="n"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="1062">
-      <c r="A40" s="69" t="n"/>
-      <c r="B40" s="354" t="n"/>
-      <c r="C40" s="51" t="inlineStr">
+    <row r="36" ht="15.75" customHeight="1" s="1051">
+      <c r="A36" s="70" t="n"/>
+      <c r="B36" s="52" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D40" s="51" t="n"/>
-      <c r="E40" s="51" t="inlineStr">
+      <c r="C36" s="52" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F40" s="51" t="inlineStr">
+      <c r="D36" s="52" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G40" s="51" t="n"/>
-      <c r="H40" s="51" t="inlineStr">
+      <c r="E36" s="52" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I40" s="51" t="n"/>
-      <c r="J40" s="68" t="inlineStr">
+      <c r="F36" s="69" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Formaleta de escaleras</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB40" t="n">
-        <v>5</v>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="1051">
+      <c r="A37" s="509" t="n"/>
+      <c r="B37" s="510" t="n"/>
+      <c r="C37" s="118" t="n"/>
+      <c r="D37" s="1238" t="n"/>
+      <c r="E37" s="1234" t="n"/>
+      <c r="F37" s="1239">
+        <f>D37*E37</f>
+        <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="1062">
-      <c r="A41" s="544" t="n"/>
-      <c r="B41" s="545" t="n"/>
-      <c r="C41" s="545" t="n"/>
-      <c r="D41" s="545" t="n"/>
-      <c r="E41" s="117" t="n"/>
-      <c r="F41" s="1293" t="n"/>
-      <c r="G41" s="1293" t="n"/>
-      <c r="H41" s="1289" t="n"/>
-      <c r="I41" s="1289" t="n"/>
-      <c r="J41" s="1294">
-        <f>F41*H41</f>
+    <row r="38" ht="15" customHeight="1" s="1051">
+      <c r="A38" s="509" t="n"/>
+      <c r="B38" s="510" t="n"/>
+      <c r="C38" s="118" t="n"/>
+      <c r="D38" s="1238" t="n"/>
+      <c r="E38" s="1234" t="n"/>
+      <c r="F38" s="1239">
+        <f>D38*E38</f>
         <v/>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="1051">
+      <c r="A39" s="509" t="n"/>
+      <c r="B39" s="510" t="n"/>
+      <c r="C39" s="118" t="n"/>
+      <c r="D39" s="1238" t="n"/>
+      <c r="E39" s="1234" t="n"/>
+      <c r="F39" s="1239">
+        <f>D39*E39</f>
+        <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="1062">
-      <c r="A42" s="544" t="n"/>
-      <c r="B42" s="1248" t="n"/>
-      <c r="C42" s="1248" t="n"/>
-      <c r="D42" s="1248" t="n"/>
-      <c r="E42" s="117" t="n"/>
-      <c r="F42" s="1293" t="n"/>
-      <c r="G42" s="1293" t="n"/>
-      <c r="H42" s="1289" t="n"/>
-      <c r="I42" s="1289" t="n"/>
-      <c r="J42" s="1294">
-        <f>F42*H42</f>
+    <row r="40" ht="15" customHeight="1" s="1051">
+      <c r="A40" s="509" t="n"/>
+      <c r="B40" s="510" t="n"/>
+      <c r="C40" s="118" t="n"/>
+      <c r="D40" s="1238" t="n"/>
+      <c r="E40" s="1234" t="n"/>
+      <c r="F40" s="1239">
+        <f>D40*E40</f>
         <v/>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Placas, pernos y conexiones metálicas</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="1051">
+      <c r="A41" s="509" t="n"/>
+      <c r="B41" s="510" t="n"/>
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="1238" t="n"/>
+      <c r="E41" s="1234" t="n"/>
+      <c r="F41" s="1239">
+        <f>D41*E41</f>
+        <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="1062">
-      <c r="A43" s="544" t="n"/>
-      <c r="B43" s="1248" t="n"/>
-      <c r="C43" s="1248" t="n"/>
-      <c r="D43" s="1248" t="n"/>
-      <c r="E43" s="117" t="n"/>
-      <c r="F43" s="1293" t="n"/>
-      <c r="G43" s="1293" t="n"/>
-      <c r="H43" s="1289" t="n"/>
-      <c r="I43" s="1289" t="n"/>
-      <c r="J43" s="1294">
-        <f>F43*H43</f>
+    <row r="42" ht="15" customHeight="1" s="1051">
+      <c r="A42" s="509" t="n"/>
+      <c r="B42" s="510" t="n"/>
+      <c r="C42" s="118" t="n"/>
+      <c r="D42" s="1238" t="n"/>
+      <c r="E42" s="1234" t="n"/>
+      <c r="F42" s="1239">
+        <f>D42*E42</f>
         <v/>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Mampostería en bloque de concreto</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB43" t="n">
-        <v>12</v>
-      </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="1062">
-      <c r="A44" s="544" t="n"/>
-      <c r="B44" s="1248" t="n"/>
-      <c r="C44" s="1248" t="n"/>
-      <c r="D44" s="1248" t="n"/>
-      <c r="E44" s="117" t="n"/>
-      <c r="F44" s="1293" t="n"/>
-      <c r="G44" s="1293" t="n"/>
-      <c r="H44" s="1289" t="n"/>
-      <c r="I44" s="1289" t="n"/>
-      <c r="J44" s="1294">
-        <f>F44*H44</f>
-        <v/>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Mampostería en ladrillo</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB44" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="1062">
-      <c r="A45" s="544" t="n"/>
-      <c r="B45" s="545" t="n"/>
-      <c r="C45" s="545" t="n"/>
-      <c r="D45" s="545" t="n"/>
-      <c r="E45" s="117" t="n"/>
-      <c r="F45" s="1293" t="n"/>
-      <c r="G45" s="1293" t="n"/>
-      <c r="H45" s="1289" t="n"/>
-      <c r="I45" s="1289" t="n"/>
-      <c r="J45" s="1294">
-        <f>F45*H45</f>
-        <v/>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Mampostería estructural</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB45" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="1062">
-      <c r="A46" s="544" t="n"/>
-      <c r="B46" s="545" t="n"/>
-      <c r="C46" s="545" t="n"/>
-      <c r="D46" s="545" t="n"/>
-      <c r="E46" s="117" t="n"/>
-      <c r="F46" s="1293" t="n"/>
-      <c r="G46" s="1293" t="n"/>
-      <c r="H46" s="1289" t="n"/>
-      <c r="I46" s="1289" t="n"/>
-      <c r="J46" s="1294">
-        <f>F46*H46</f>
-        <v/>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Muros en sistema liviano / drywall</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="1062">
-      <c r="A47" s="560" t="n"/>
-      <c r="B47" s="545" t="n"/>
-      <c r="C47" s="545" t="n"/>
-      <c r="D47" s="545" t="n"/>
-      <c r="E47" s="559" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="1051">
+      <c r="A43" s="529" t="n"/>
+      <c r="B43" s="510" t="n"/>
+      <c r="C43" s="527" t="inlineStr">
         <is>
           <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
         </is>
       </c>
-      <c r="F47" s="545" t="n"/>
-      <c r="G47" s="545" t="n"/>
-      <c r="H47" s="545" t="n"/>
-      <c r="I47" s="545" t="n"/>
-      <c r="J47" s="1295">
-        <f>SUM(J41:J46)</f>
+      <c r="D43" s="510" t="n"/>
+      <c r="E43" s="510" t="n"/>
+      <c r="F43" s="1240">
+        <f>SUM(F37:F42)</f>
         <v/>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Dinteles sobre vanos</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB47" t="n">
-        <v>15</v>
-      </c>
     </row>
-    <row r="48" ht="24.75" customHeight="1" s="1062">
-      <c r="A48" s="546" t="inlineStr">
+    <row r="44" ht="24.75" customHeight="1" s="1051">
+      <c r="A44" s="511" t="inlineStr">
         <is>
           <t xml:space="preserve">                Materiales</t>
         </is>
       </c>
-      <c r="B48" s="545" t="n"/>
-      <c r="C48" s="545" t="n"/>
-      <c r="D48" s="545" t="n"/>
-      <c r="E48" s="545" t="n"/>
-      <c r="F48" s="545" t="n"/>
-      <c r="G48" s="545" t="n"/>
-      <c r="H48" s="545" t="n"/>
-      <c r="I48" s="547" t="n"/>
-      <c r="J48" s="1296">
-        <f>J29</f>
+      <c r="B44" s="510" t="n"/>
+      <c r="C44" s="510" t="n"/>
+      <c r="D44" s="510" t="n"/>
+      <c r="E44" s="510" t="n"/>
+      <c r="F44" s="1241">
+        <f>F25</f>
         <v/>
       </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Alfajías y remates</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB48" t="n">
-        <v>20</v>
-      </c>
     </row>
-    <row r="49" ht="24.75" customHeight="1" s="1062">
-      <c r="A49" s="546" t="inlineStr">
+    <row r="45" ht="24.75" customHeight="1" s="1051">
+      <c r="A45" s="511" t="inlineStr">
         <is>
           <t xml:space="preserve">                Mano de Obra</t>
         </is>
       </c>
-      <c r="B49" s="545" t="n"/>
-      <c r="C49" s="545" t="n"/>
-      <c r="D49" s="545" t="n"/>
-      <c r="E49" s="545" t="n"/>
-      <c r="F49" s="545" t="n"/>
-      <c r="G49" s="545" t="n"/>
-      <c r="H49" s="545" t="n"/>
-      <c r="I49" s="547" t="n"/>
-      <c r="J49" s="1296">
-        <f>J38</f>
+      <c r="B45" s="510" t="n"/>
+      <c r="C45" s="510" t="n"/>
+      <c r="D45" s="510" t="n"/>
+      <c r="E45" s="510" t="n"/>
+      <c r="F45" s="1241">
+        <f>F34</f>
         <v/>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Anclajes y refuerzos de mampostería</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
     </row>
-    <row r="50" ht="24.75" customHeight="1" s="1062">
-      <c r="A50" s="546" t="inlineStr">
+    <row r="46" ht="24.75" customHeight="1" s="1051">
+      <c r="A46" s="511" t="inlineStr">
         <is>
           <t xml:space="preserve">                Equipos y herramientas</t>
         </is>
       </c>
-      <c r="B50" s="545" t="n"/>
-      <c r="C50" s="545" t="n"/>
-      <c r="D50" s="545" t="n"/>
-      <c r="E50" s="545" t="n"/>
-      <c r="F50" s="545" t="n"/>
-      <c r="G50" s="545" t="n"/>
-      <c r="H50" s="545" t="n"/>
-      <c r="I50" s="547" t="n"/>
-      <c r="J50" s="1296">
-        <f>J47</f>
+      <c r="B46" s="510" t="n"/>
+      <c r="C46" s="510" t="n"/>
+      <c r="D46" s="510" t="n"/>
+      <c r="E46" s="510" t="n"/>
+      <c r="F46" s="1241">
+        <f>F43</f>
         <v/>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>1 Oficial soldador + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB50" t="n">
-        <v>80</v>
-      </c>
     </row>
-    <row r="51" ht="19.95" customHeight="1" s="1062">
-      <c r="A51" s="571" t="inlineStr">
+    <row r="47" ht="19.95" customHeight="1" s="1051">
+      <c r="A47" s="538" t="inlineStr">
         <is>
           <t>TOTAL DIRECTO UNITARIO</t>
         </is>
       </c>
-      <c r="B51" s="1297" t="n"/>
-      <c r="C51" s="1297" t="n"/>
-      <c r="D51" s="1297" t="n"/>
-      <c r="E51" s="1297" t="n"/>
-      <c r="F51" s="1297" t="n"/>
-      <c r="G51" s="1297" t="n"/>
-      <c r="H51" s="1297" t="n"/>
-      <c r="I51" s="572" t="n"/>
-      <c r="J51" s="1298">
-        <f>SUM(J48:J50)</f>
+      <c r="B47" s="1242" t="n"/>
+      <c r="C47" s="1242" t="n"/>
+      <c r="D47" s="1242" t="n"/>
+      <c r="E47" s="1242" t="n"/>
+      <c r="F47" s="1243">
+        <f>SUM(F44:F46)</f>
         <v/>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Cerchas y elementos estructurales</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
     </row>
-    <row r="52" ht="4.5" customHeight="1" s="1062">
-      <c r="A52" s="70" t="n"/>
-      <c r="B52" s="1256" t="n"/>
-      <c r="C52" s="1256" t="n"/>
-      <c r="D52" s="1256" t="n"/>
-      <c r="E52" s="1256" t="n"/>
-      <c r="F52" s="1256" t="n"/>
-      <c r="G52" s="1256" t="n"/>
-      <c r="H52" s="1256" t="n"/>
-      <c r="I52" s="1256" t="n"/>
-      <c r="J52" s="71" t="n"/>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de teja</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB52" t="n">
-        <v>25</v>
-      </c>
+    <row r="48" ht="4.5" customHeight="1" s="1051">
+      <c r="A48" s="71" t="n"/>
+      <c r="B48" s="51" t="n"/>
+      <c r="C48" s="51" t="n"/>
+      <c r="D48" s="51" t="n"/>
+      <c r="E48" s="51" t="n"/>
+      <c r="F48" s="72" t="n"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="1062">
-      <c r="A53" s="577" t="inlineStr">
+    <row r="49" ht="15.75" customHeight="1" s="1051">
+      <c r="A49" s="546" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="B53" s="578" t="n"/>
-      <c r="C53" s="578" t="n"/>
-      <c r="D53" s="578" t="n"/>
-      <c r="E53" s="1257" t="n"/>
-      <c r="F53" s="580" t="inlineStr">
+      <c r="B49" s="547" t="n"/>
+      <c r="C49" s="221" t="n"/>
+      <c r="D49" s="549" t="inlineStr">
         <is>
           <t>Vo. Bo. INTERVENTORÍA:</t>
         </is>
       </c>
-      <c r="G53" s="578" t="n"/>
-      <c r="H53" s="578" t="n"/>
-      <c r="I53" s="578" t="n"/>
-      <c r="J53" s="581" t="n"/>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Impermeabilización de cubierta</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB53" t="n">
-        <v>20</v>
-      </c>
+      <c r="E49" s="547" t="n"/>
+      <c r="F49" s="550" t="n"/>
     </row>
-    <row r="54" ht="42" customHeight="1" s="1062">
-      <c r="A54" s="454" t="inlineStr">
+    <row r="50" ht="42" customHeight="1" s="1051">
+      <c r="A50" s="463" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="B54" s="1258" t="n"/>
-      <c r="C54" s="539" t="n"/>
-      <c r="D54" s="906" t="n"/>
-      <c r="E54" s="906" t="n"/>
-      <c r="F54" s="455" t="inlineStr">
+      <c r="B50" s="504" t="n"/>
+      <c r="C50" s="870" t="n"/>
+      <c r="D50" s="464" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="G54" s="455" t="n"/>
-      <c r="H54" s="579" t="n"/>
-      <c r="I54" s="906" t="n"/>
-      <c r="J54" s="930" t="n"/>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Aislamiento térmico/acústico</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="E50" s="548" t="n"/>
+      <c r="F50" s="907" t="n"/>
     </row>
-    <row r="55" ht="24.75" customHeight="1" s="1062">
-      <c r="A55" s="454" t="inlineStr">
+    <row r="51" ht="24.75" customHeight="1" s="1051">
+      <c r="A51" s="463" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="B55" s="1258" t="n"/>
-      <c r="C55" s="539" t="n"/>
-      <c r="D55" s="906" t="n"/>
-      <c r="E55" s="906" t="n"/>
-      <c r="F55" s="455" t="inlineStr">
+      <c r="B51" s="504" t="n"/>
+      <c r="C51" s="870" t="n"/>
+      <c r="D51" s="464" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="G55" s="455" t="n"/>
-      <c r="H55" s="569" t="n"/>
-      <c r="I55" s="906" t="n"/>
-      <c r="J55" s="930" t="n"/>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Canales de aguas lluvias</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB55" t="n">
-        <v>20</v>
-      </c>
+      <c r="E51" s="535" t="n"/>
+      <c r="F51" s="907" t="n"/>
     </row>
-    <row r="56" ht="24.75" customHeight="1" s="1062">
-      <c r="A56" s="454" t="inlineStr">
+    <row r="52" ht="24.75" customHeight="1" s="1051">
+      <c r="A52" s="463" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="B56" s="1258" t="n"/>
-      <c r="C56" s="539" t="n"/>
-      <c r="D56" s="906" t="n"/>
-      <c r="E56" s="906" t="n"/>
-      <c r="F56" s="455" t="inlineStr">
+      <c r="B52" s="504" t="n"/>
+      <c r="C52" s="870" t="n"/>
+      <c r="D52" s="464" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="G56" s="455" t="n"/>
-      <c r="H56" s="569" t="n"/>
-      <c r="I56" s="906" t="n"/>
-      <c r="J56" s="930" t="n"/>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Bajantes de aguas lluvias</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB56" t="n">
-        <v>25</v>
-      </c>
+      <c r="E52" s="535" t="n"/>
+      <c r="F52" s="907" t="n"/>
     </row>
-    <row r="57" ht="15" customHeight="1" s="1062">
-      <c r="A57" s="226" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="1051">
+      <c r="A53" s="232" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B57" s="1259" t="n"/>
-      <c r="J57" s="496">
-        <f>J5</f>
+      <c r="F53" s="1122">
+        <f>F5</f>
         <v/>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB57" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB58" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Impermeabilización de zonas húmedas</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB59" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB60" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Pañete / revoque exterior</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB61" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Pañete impermeabilizado</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB62" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Estuco plástico o tradicional</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB63" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Mortero de nivelación</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB64" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Piso cerámico</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB65" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>Piso en porcelanato</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB66" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Piso vinílico</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB67" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Piso laminado</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB68" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Enchape cerámico en muros</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB69" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Guardaescoba</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>1 Oficial</t>
-        </is>
-      </c>
-      <c r="AB70" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Pintura vinílica interior</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB72" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Pintura exterior</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB73" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB74" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Pintura anticorrosiva</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB75" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Sellador / imprimante</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>1 Oficial</t>
-        </is>
-      </c>
-      <c r="AB76" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Muebles fijos de madera</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Puertas metálicas</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Ventanas de aluminio</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB82" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Divisiones de aluminio</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB83" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB84" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Vidrio laminado</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>1 Oficial + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB85" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Espejos</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>Sellos y silicona</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Tubería de agua fría</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB88" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>Tubería de agua caliente</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB89" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Válvulas y accesorios</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Tubería sanitaria</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB91" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>Tubería de aguas lluvias</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB92" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>Cajas de inspección</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>Aparatos sanitarios</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB94" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Lavamanos</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB95" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Griferías</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario</t>
-        </is>
-      </c>
-      <c r="AB96" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>Duchas</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>1 Oficial hidrosanitario + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB97" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Tubería/conduit eléctrica</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>1 Electricista + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB99" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>Bandejas portacables</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Cajas eléctricas</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>Cableado de fuerza</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>1 Electricista + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB102" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>Cableado de iluminación</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>1 Electricista + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB103" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Tableros eléctricos</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>Tomacorrientes</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>1 Electricista</t>
-        </is>
-      </c>
-      <c r="AB105" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>Interruptores</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>1 Electricista</t>
-        </is>
-      </c>
-      <c r="AB106" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>Luminarias</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>1 Electricista + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB107" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Sistema de puesta a tierra</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>Pruebas y certificaciones</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>Rack de comunicaciones</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>Cámaras y sistema CCTV</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>Control de acceso</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>Sistema de citofonía</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>Sistema de detección de incendios</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>Ductos de ventilación</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Tubería de refrigerante</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>Red interna de gas</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>Válvulas y accesorios</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>Pruebas y certificación</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>Construcción de andenes</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB123" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>Placas de concreto exteriores</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>Pavimento en adoquín</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>Sardineles y bordillos</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>1 Oficial + 2 Ayudantes</t>
-        </is>
-      </c>
-      <c r="AB126" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>Sumideros exteriores</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>Suministro y extendido de tierra vegetal</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>Siembra y jardinería</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>1 Jardinero + 1 Ayudante</t>
-        </is>
-      </c>
-      <c r="AB129" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>Escaleras metálicas</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>Elementos metálicos especiales</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>Mobiliario fijo de obra</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2 Aseadores</t>
-        </is>
-      </c>
-      <c r="AB134" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>Limpieza final para entrega</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>2 Aseadores</t>
-        </is>
-      </c>
-      <c r="AB135" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>Actualización de planos récord / as-built</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>Entrega, manuales y acta de recibo</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="F53:J53"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="A1:C8"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="E39:J39"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="E18:F18"/>
+  <mergeCells count="52">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A1:B8"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -9943,464 +9943,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1228,6 +1228,11 @@
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="76">
@@ -6573,7 +6578,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9798,6 +9803,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10019,7 +10027,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10215,7 +10223,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10306,7 +10314,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10339,7 +10347,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1233,6 +1233,10 @@
       <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="76">
@@ -6578,7 +6582,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9807,6 +9811,7 @@
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -23,6 +23,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1688,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6573,6 +6574,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6582,7 +6597,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9812,6 +9827,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10627,7 +10654,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W56"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -10401,31 +10401,6 @@
     </a:ln>
   </spPr>
 </chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Apu's" sheetId="1" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apu's" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -9970,440 +9971,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10625,10 +10193,11 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W56"/>
@@ -10978,7 +10547,10 @@
         <f>A1&amp;" "&amp;A18&amp;"/jornada"</f>
         <v/>
       </c>
-      <c r="J18" s="390" t="n"/>
+      <c r="J18" s="390">
+        <f>IFERROR(1/V4,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="358" thickTop="1">
       <c r="A19" s="542" t="n"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -10197,7 +10197,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W56"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -6598,7 +6598,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1313">
+  <cellXfs count="1314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9839,6 +9839,9 @@
     </xf>
     <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9972,32 +9975,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1944750</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>49500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1944750</colOff>
+      <row>8</row>
+      <rowOff>49500</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1764000"/>
@@ -10009,11 +10012,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10449,13 +10452,12 @@
       <c r="E14" s="567" t="n"/>
       <c r="F14" s="360" t="n"/>
       <c r="G14" s="360" t="n"/>
-      <c r="H14" s="359" t="inlineStr">
+      <c r="H14" s="1313" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="I14" s="359" t="n"/>
-      <c r="J14" s="366" t="n"/>
+      <c r="I14" s="575" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="1223">
       <c r="A15" s="365" t="inlineStr">
@@ -10473,13 +10475,12 @@
       <c r="E15" s="567" t="n"/>
       <c r="F15" s="360" t="n"/>
       <c r="G15" s="360" t="n"/>
-      <c r="H15" s="359" t="inlineStr">
+      <c r="H15" s="1313" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I15" s="359" t="n"/>
-      <c r="J15" s="366" t="n"/>
+      <c r="I15" s="575" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="1223" thickBot="1">
       <c r="A16" s="562" t="n"/>
@@ -11227,7 +11228,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="55">
     <mergeCell ref="C54:E54"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A48:H48"/>
@@ -11275,9 +11276,11 @@
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="H55:J55"/>
+    <mergeCell ref="H15:I15"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="E46:H46"/>
     <mergeCell ref="C13:J13"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E38:J38"/>
     <mergeCell ref="E29:J29"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Apu's" sheetId="1" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apu's" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -10409,7 +10410,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10631,7 +10632,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -11204,7 +11205,11 @@
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G30" s="48" t="n"/>
+      <c r="G30" s="48" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="H30" s="48" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
@@ -11228,7 +11233,7 @@
       <c r="H31" s="1288" t="n"/>
       <c r="I31" s="1288" t="n"/>
       <c r="J31" s="1294">
-        <f>F31*H31</f>
+        <f>F31*IF(G31=0,1,G31)*H31</f>
         <v/>
       </c>
     </row>
@@ -11243,7 +11248,7 @@
       <c r="H32" s="1288" t="n"/>
       <c r="I32" s="1288" t="n"/>
       <c r="J32" s="1294">
-        <f>F32*H32</f>
+        <f>F32*IF(G32=0,1,G32)*H32</f>
         <v/>
       </c>
     </row>
@@ -11258,7 +11263,7 @@
       <c r="H33" s="1288" t="n"/>
       <c r="I33" s="1288" t="n"/>
       <c r="J33" s="1294">
-        <f>F33*H33</f>
+        <f>F33*IF(G33=0,1,G33)*H33</f>
         <v/>
       </c>
     </row>
@@ -11273,7 +11278,7 @@
       <c r="H34" s="1288" t="n"/>
       <c r="I34" s="1288" t="n"/>
       <c r="J34" s="1294">
-        <f>F34*H34</f>
+        <f>F34*IF(G34=0,1,G34)*H34</f>
         <v/>
       </c>
     </row>
@@ -11288,7 +11293,7 @@
       <c r="H35" s="1288" t="n"/>
       <c r="I35" s="1288" t="n"/>
       <c r="J35" s="1294">
-        <f>F35*H35</f>
+        <f>F35*IF(G35=0,1,G35)*H35</f>
         <v/>
       </c>
     </row>
@@ -11303,7 +11308,7 @@
       <c r="H36" s="1290" t="n"/>
       <c r="I36" s="1290" t="n"/>
       <c r="J36" s="1294">
-        <f>F36*H36</f>
+        <f>F36*IF(G36=0,1,G36)*H36</f>
         <v/>
       </c>
     </row>
@@ -11365,7 +11370,11 @@
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G39" s="48" t="n"/>
+      <c r="G39" s="48" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="H39" s="48" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
@@ -11389,7 +11398,7 @@
       <c r="H40" s="1288" t="n"/>
       <c r="I40" s="1288" t="n"/>
       <c r="J40" s="1294">
-        <f>F40*H40</f>
+        <f>F40*IF(G40=0,1,G40)*H40</f>
         <v/>
       </c>
     </row>
@@ -11404,7 +11413,7 @@
       <c r="H41" s="1288" t="n"/>
       <c r="I41" s="1288" t="n"/>
       <c r="J41" s="1294">
-        <f>F41*H41</f>
+        <f>F41*IF(G41=0,1,G41)*H41</f>
         <v/>
       </c>
     </row>
@@ -11419,7 +11428,7 @@
       <c r="H42" s="1288" t="n"/>
       <c r="I42" s="1288" t="n"/>
       <c r="J42" s="1294">
-        <f>F42*H42</f>
+        <f>F42*IF(G42=0,1,G42)*H42</f>
         <v/>
       </c>
     </row>
@@ -11434,7 +11443,7 @@
       <c r="H43" s="1288" t="n"/>
       <c r="I43" s="1288" t="n"/>
       <c r="J43" s="1294">
-        <f>F43*H43</f>
+        <f>F43*IF(G43=0,1,G43)*H43</f>
         <v/>
       </c>
     </row>
@@ -11449,7 +11458,7 @@
       <c r="H44" s="1288" t="n"/>
       <c r="I44" s="1288" t="n"/>
       <c r="J44" s="1294">
-        <f>F44*H44</f>
+        <f>F44*IF(G44=0,1,G44)*H44</f>
         <v/>
       </c>
     </row>
@@ -11464,7 +11473,7 @@
       <c r="H45" s="1288" t="n"/>
       <c r="I45" s="1288" t="n"/>
       <c r="J45" s="1294">
-        <f>F45*H45</f>
+        <f>F45*IF(G45=0,1,G45)*H45</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -11044,7 +11044,11 @@
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G21" s="358" t="n"/>
+      <c r="G21" s="358" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
       <c r="H21" s="358" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
@@ -11068,7 +11072,7 @@
       <c r="H22" s="1288" t="n"/>
       <c r="I22" s="1288" t="n"/>
       <c r="J22" s="1289">
-        <f>F22*H22</f>
+        <f>F22*IF(G22=0,1,G22)*H22</f>
         <v/>
       </c>
     </row>
@@ -11083,7 +11087,7 @@
       <c r="H23" s="1288" t="n"/>
       <c r="I23" s="1288" t="n"/>
       <c r="J23" s="1289">
-        <f>F23*H23</f>
+        <f>F23*IF(G23=0,1,G23)*H23</f>
         <v/>
       </c>
     </row>
@@ -11098,7 +11102,7 @@
       <c r="H24" s="1288" t="n"/>
       <c r="I24" s="1288" t="n"/>
       <c r="J24" s="1289">
-        <f>F24*H24</f>
+        <f>F24*IF(G24=0,1,G24)*H24</f>
         <v/>
       </c>
     </row>
@@ -11113,7 +11117,7 @@
       <c r="H25" s="1288" t="n"/>
       <c r="I25" s="1288" t="n"/>
       <c r="J25" s="1289">
-        <f>F25*H25</f>
+        <f>F25*IF(G25=0,1,G25)*H25</f>
         <v/>
       </c>
     </row>
@@ -11128,7 +11132,7 @@
       <c r="H26" s="1288" t="n"/>
       <c r="I26" s="1288" t="n"/>
       <c r="J26" s="1289">
-        <f>F26*H26</f>
+        <f>F26*IF(G26=0,1,G26)*H26</f>
         <v/>
       </c>
     </row>
@@ -11143,7 +11147,7 @@
       <c r="H27" s="1290" t="n"/>
       <c r="I27" s="1290" t="n"/>
       <c r="J27" s="1289">
-        <f>F27*H27</f>
+        <f>F27*IF(G27=0,1,G27)*H27</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -6680,7 +6680,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1446">
+  <cellXfs count="1447">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10279,6 +10279,7 @@
     <xf numFmtId="2" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10638,7 +10639,7 @@
     <tabColor theme="9" tint="-0.499984740745262"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.77734375" customWidth="1" style="550" min="1" max="1"/>
@@ -11151,213 +11152,183 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="550">
-      <c r="A28" s="587" t="n"/>
-      <c r="B28" s="1291" t="n"/>
-      <c r="C28" s="1291" t="n"/>
-      <c r="D28" s="1291" t="n"/>
-      <c r="E28" s="596" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="566" t="n"/>
+      <c r="B28" s="1446" t="n"/>
+      <c r="C28" s="1446" t="n"/>
+      <c r="D28" s="1446" t="n"/>
+      <c r="E28" s="111" t="n"/>
+      <c r="F28" s="112" t="n"/>
+      <c r="G28" s="112" t="n"/>
+      <c r="H28" s="1288" t="n"/>
+      <c r="I28" s="1288" t="n"/>
+      <c r="J28" s="1289">
+        <f>F28*IF(G28=0,1,G28)*H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="566" t="n"/>
+      <c r="B29" s="1446" t="n"/>
+      <c r="C29" s="1446" t="n"/>
+      <c r="D29" s="1446" t="n"/>
+      <c r="E29" s="111" t="n"/>
+      <c r="F29" s="112" t="n"/>
+      <c r="G29" s="112" t="n"/>
+      <c r="H29" s="1288" t="n"/>
+      <c r="I29" s="1288" t="n"/>
+      <c r="J29" s="1289">
+        <f>F29*IF(G29=0,1,G29)*H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="566" t="n"/>
+      <c r="B30" s="1446" t="n"/>
+      <c r="C30" s="1446" t="n"/>
+      <c r="D30" s="1446" t="n"/>
+      <c r="E30" s="111" t="n"/>
+      <c r="F30" s="112" t="n"/>
+      <c r="G30" s="112" t="n"/>
+      <c r="H30" s="1288" t="n"/>
+      <c r="I30" s="1288" t="n"/>
+      <c r="J30" s="1289">
+        <f>F30*IF(G30=0,1,G30)*H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="566" t="n"/>
+      <c r="B31" s="1446" t="n"/>
+      <c r="C31" s="1446" t="n"/>
+      <c r="D31" s="1446" t="n"/>
+      <c r="E31" s="111" t="n"/>
+      <c r="F31" s="112" t="n"/>
+      <c r="G31" s="112" t="n"/>
+      <c r="H31" s="1288" t="n"/>
+      <c r="I31" s="1288" t="n"/>
+      <c r="J31" s="1289">
+        <f>F31*IF(G31=0,1,G31)*H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="566" t="n"/>
+      <c r="B32" s="1446" t="n"/>
+      <c r="C32" s="1446" t="n"/>
+      <c r="D32" s="1446" t="n"/>
+      <c r="E32" s="111" t="n"/>
+      <c r="F32" s="112" t="n"/>
+      <c r="G32" s="112" t="n"/>
+      <c r="H32" s="1288" t="n"/>
+      <c r="I32" s="1288" t="n"/>
+      <c r="J32" s="1289">
+        <f>F32*IF(G32=0,1,G32)*H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="566" t="n"/>
+      <c r="B33" s="1446" t="n"/>
+      <c r="C33" s="1446" t="n"/>
+      <c r="D33" s="1446" t="n"/>
+      <c r="E33" s="111" t="n"/>
+      <c r="F33" s="112" t="n"/>
+      <c r="G33" s="112" t="n"/>
+      <c r="H33" s="1288" t="n"/>
+      <c r="I33" s="1288" t="n"/>
+      <c r="J33" s="1289">
+        <f>F33*IF(G33=0,1,G33)*H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="566" t="n"/>
+      <c r="B34" s="1446" t="n"/>
+      <c r="C34" s="1446" t="n"/>
+      <c r="D34" s="1446" t="n"/>
+      <c r="E34" s="111" t="n"/>
+      <c r="F34" s="112" t="n"/>
+      <c r="G34" s="112" t="n"/>
+      <c r="H34" s="1288" t="n"/>
+      <c r="I34" s="1288" t="n"/>
+      <c r="J34" s="1289">
+        <f>F34*IF(G34=0,1,G34)*H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="566" t="n"/>
+      <c r="B35" s="1446" t="n"/>
+      <c r="C35" s="1446" t="n"/>
+      <c r="D35" s="1446" t="n"/>
+      <c r="E35" s="111" t="n"/>
+      <c r="F35" s="112" t="n"/>
+      <c r="G35" s="112" t="n"/>
+      <c r="H35" s="1288" t="n"/>
+      <c r="I35" s="1288" t="n"/>
+      <c r="J35" s="1289">
+        <f>F35*IF(G35=0,1,G35)*H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="566" t="n"/>
+      <c r="B36" s="1446" t="n"/>
+      <c r="C36" s="1446" t="n"/>
+      <c r="D36" s="1446" t="n"/>
+      <c r="E36" s="111" t="n"/>
+      <c r="F36" s="112" t="n"/>
+      <c r="G36" s="112" t="n"/>
+      <c r="H36" s="1288" t="n"/>
+      <c r="I36" s="1288" t="n"/>
+      <c r="J36" s="1289">
+        <f>F36*IF(G36=0,1,G36)*H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="550">
+      <c r="A37" s="587" t="n"/>
+      <c r="B37" s="1291" t="n"/>
+      <c r="C37" s="1291" t="n"/>
+      <c r="D37" s="1291" t="n"/>
+      <c r="E37" s="596" t="inlineStr">
         <is>
           <t>SUBTOTAL MATERIALES</t>
         </is>
       </c>
-      <c r="F28" s="1291" t="n"/>
-      <c r="G28" s="1291" t="n"/>
-      <c r="H28" s="1291" t="n"/>
-      <c r="I28" s="1291" t="n"/>
-      <c r="J28" s="1292">
-        <f>SUM(J22:J27)</f>
+      <c r="F37" s="1291" t="n"/>
+      <c r="G37" s="1291" t="n"/>
+      <c r="H37" s="1291" t="n"/>
+      <c r="I37" s="1291" t="n"/>
+      <c r="J37" s="1292">
+        <f>SUM(J22:J36)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="550">
-      <c r="A29" s="187" t="inlineStr">
+    <row r="38" ht="15" customHeight="1" s="550">
+      <c r="A38" s="187" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B29" s="368" t="n"/>
-      <c r="C29" s="275" t="inlineStr">
+      <c r="B38" s="368" t="n"/>
+      <c r="C38" s="275" t="inlineStr">
         <is>
           <t>MANO DE OBRA</t>
         </is>
       </c>
-      <c r="D29" s="275" t="n"/>
-      <c r="E29" s="608" t="n"/>
-      <c r="F29" s="609" t="n"/>
-      <c r="G29" s="609" t="n"/>
-      <c r="H29" s="609" t="n"/>
-      <c r="I29" s="609" t="n"/>
-      <c r="J29" s="610" t="n"/>
+      <c r="D38" s="275" t="n"/>
+      <c r="E38" s="608" t="n"/>
+      <c r="F38" s="609" t="n"/>
+      <c r="G38" s="609" t="n"/>
+      <c r="H38" s="609" t="n"/>
+      <c r="I38" s="609" t="n"/>
+      <c r="J38" s="610" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="550">
-      <c r="A30" s="64" t="n"/>
-      <c r="B30" s="369" t="n"/>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="D30" s="48" t="n"/>
-      <c r="E30" s="48" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="F30" s="48" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="G30" s="48" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="H30" s="48" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="I30" s="48" t="n"/>
-      <c r="J30" s="65" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="550">
-      <c r="A31" s="580" t="n"/>
-      <c r="B31" s="567" t="n"/>
-      <c r="C31" s="567" t="n"/>
-      <c r="D31" s="567" t="n"/>
-      <c r="E31" s="111" t="n"/>
-      <c r="F31" s="1437" t="n"/>
-      <c r="G31" s="1437" t="n"/>
-      <c r="H31" s="1288" t="n"/>
-      <c r="I31" s="1288" t="n"/>
-      <c r="J31" s="1294">
-        <f>F31*IF(G31=0,1,G31)*H31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="550">
-      <c r="A32" s="580" t="n"/>
-      <c r="B32" s="567" t="n"/>
-      <c r="C32" s="567" t="n"/>
-      <c r="D32" s="567" t="n"/>
-      <c r="E32" s="111" t="n"/>
-      <c r="F32" s="1437" t="n"/>
-      <c r="G32" s="1437" t="n"/>
-      <c r="H32" s="1288" t="n"/>
-      <c r="I32" s="1288" t="n"/>
-      <c r="J32" s="1294">
-        <f>F32*IF(G32=0,1,G32)*H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="550">
-      <c r="A33" s="580" t="n"/>
-      <c r="B33" s="567" t="n"/>
-      <c r="C33" s="567" t="n"/>
-      <c r="D33" s="567" t="n"/>
-      <c r="E33" s="111" t="n"/>
-      <c r="F33" s="1437" t="n"/>
-      <c r="G33" s="1437" t="n"/>
-      <c r="H33" s="1288" t="n"/>
-      <c r="I33" s="1288" t="n"/>
-      <c r="J33" s="1294">
-        <f>F33*IF(G33=0,1,G33)*H33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="550">
-      <c r="A34" s="580" t="n"/>
-      <c r="B34" s="567" t="n"/>
-      <c r="C34" s="567" t="n"/>
-      <c r="D34" s="567" t="n"/>
-      <c r="E34" s="111" t="n"/>
-      <c r="F34" s="1437" t="n"/>
-      <c r="G34" s="1437" t="n"/>
-      <c r="H34" s="1288" t="n"/>
-      <c r="I34" s="1288" t="n"/>
-      <c r="J34" s="1294">
-        <f>F34*IF(G34=0,1,G34)*H34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="550">
-      <c r="A35" s="580" t="n"/>
-      <c r="B35" s="567" t="n"/>
-      <c r="C35" s="567" t="n"/>
-      <c r="D35" s="567" t="n"/>
-      <c r="E35" s="111" t="n"/>
-      <c r="F35" s="1437" t="n"/>
-      <c r="G35" s="1437" t="n"/>
-      <c r="H35" s="1288" t="n"/>
-      <c r="I35" s="1288" t="n"/>
-      <c r="J35" s="1294">
-        <f>F35*IF(G35=0,1,G35)*H35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="550">
-      <c r="A36" s="580" t="n"/>
-      <c r="B36" s="567" t="n"/>
-      <c r="C36" s="567" t="n"/>
-      <c r="D36" s="567" t="n"/>
-      <c r="E36" s="111" t="n"/>
-      <c r="F36" s="1437" t="n"/>
-      <c r="G36" s="1437" t="n"/>
-      <c r="H36" s="1290" t="n"/>
-      <c r="I36" s="1290" t="n"/>
-      <c r="J36" s="1294">
-        <f>F36*IF(G36=0,1,G36)*H36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="550">
-      <c r="A37" s="572" t="n"/>
-      <c r="B37" s="567" t="n"/>
-      <c r="C37" s="567" t="n"/>
-      <c r="D37" s="567" t="n"/>
-      <c r="E37" s="577" t="inlineStr">
-        <is>
-          <t>SUBTOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="F37" s="567" t="n"/>
-      <c r="G37" s="567" t="n"/>
-      <c r="H37" s="567" t="n"/>
-      <c r="I37" s="567" t="n"/>
-      <c r="J37" s="1295">
-        <f>SUM(J31:J36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="550">
-      <c r="A38" s="63" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B38" s="370" t="n"/>
-      <c r="C38" s="276" t="inlineStr">
-        <is>
-          <t>EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="D38" s="276" t="n"/>
-      <c r="E38" s="606" t="n"/>
-      <c r="F38" s="567" t="n"/>
-      <c r="G38" s="567" t="n"/>
-      <c r="H38" s="567" t="n"/>
-      <c r="I38" s="567" t="n"/>
-      <c r="J38" s="607" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" s="550">
-      <c r="A39" s="66" t="n"/>
-      <c r="B39" s="276" t="n"/>
+    <row r="39" ht="15" customHeight="1" s="550">
+      <c r="A39" s="64" t="n"/>
+      <c r="B39" s="369" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
           <t>Descripción</t>
@@ -11474,215 +11445,650 @@
       <c r="E45" s="111" t="n"/>
       <c r="F45" s="1437" t="n"/>
       <c r="G45" s="1437" t="n"/>
-      <c r="H45" s="1288" t="n"/>
-      <c r="I45" s="1288" t="n"/>
+      <c r="H45" s="1290" t="n"/>
+      <c r="I45" s="1290" t="n"/>
       <c r="J45" s="1294">
         <f>F45*IF(G45=0,1,G45)*H45</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="550">
-      <c r="A46" s="572" t="n"/>
-      <c r="B46" s="567" t="n"/>
-      <c r="C46" s="567" t="n"/>
-      <c r="D46" s="567" t="n"/>
-      <c r="E46" s="577" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="580" t="n"/>
+      <c r="B46" s="1446" t="n"/>
+      <c r="C46" s="1446" t="n"/>
+      <c r="D46" s="1446" t="n"/>
+      <c r="E46" s="111" t="n"/>
+      <c r="F46" s="1437" t="n"/>
+      <c r="G46" s="1437" t="n"/>
+      <c r="H46" s="1288" t="n"/>
+      <c r="I46" s="1288" t="n"/>
+      <c r="J46" s="1294">
+        <f>F46*IF(G46=0,1,G46)*H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="580" t="n"/>
+      <c r="B47" s="1446" t="n"/>
+      <c r="C47" s="1446" t="n"/>
+      <c r="D47" s="1446" t="n"/>
+      <c r="E47" s="111" t="n"/>
+      <c r="F47" s="1437" t="n"/>
+      <c r="G47" s="1437" t="n"/>
+      <c r="H47" s="1288" t="n"/>
+      <c r="I47" s="1288" t="n"/>
+      <c r="J47" s="1294">
+        <f>F47*IF(G47=0,1,G47)*H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="580" t="n"/>
+      <c r="B48" s="1446" t="n"/>
+      <c r="C48" s="1446" t="n"/>
+      <c r="D48" s="1446" t="n"/>
+      <c r="E48" s="111" t="n"/>
+      <c r="F48" s="1437" t="n"/>
+      <c r="G48" s="1437" t="n"/>
+      <c r="H48" s="1288" t="n"/>
+      <c r="I48" s="1288" t="n"/>
+      <c r="J48" s="1294">
+        <f>F48*IF(G48=0,1,G48)*H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="580" t="n"/>
+      <c r="B49" s="1446" t="n"/>
+      <c r="C49" s="1446" t="n"/>
+      <c r="D49" s="1446" t="n"/>
+      <c r="E49" s="111" t="n"/>
+      <c r="F49" s="1437" t="n"/>
+      <c r="G49" s="1437" t="n"/>
+      <c r="H49" s="1288" t="n"/>
+      <c r="I49" s="1288" t="n"/>
+      <c r="J49" s="1294">
+        <f>F49*IF(G49=0,1,G49)*H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="580" t="n"/>
+      <c r="B50" s="1446" t="n"/>
+      <c r="C50" s="1446" t="n"/>
+      <c r="D50" s="1446" t="n"/>
+      <c r="E50" s="111" t="n"/>
+      <c r="F50" s="1437" t="n"/>
+      <c r="G50" s="1437" t="n"/>
+      <c r="H50" s="1288" t="n"/>
+      <c r="I50" s="1288" t="n"/>
+      <c r="J50" s="1294">
+        <f>F50*IF(G50=0,1,G50)*H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="580" t="n"/>
+      <c r="B51" s="1446" t="n"/>
+      <c r="C51" s="1446" t="n"/>
+      <c r="D51" s="1446" t="n"/>
+      <c r="E51" s="111" t="n"/>
+      <c r="F51" s="1437" t="n"/>
+      <c r="G51" s="1437" t="n"/>
+      <c r="H51" s="1288" t="n"/>
+      <c r="I51" s="1288" t="n"/>
+      <c r="J51" s="1294">
+        <f>F51*IF(G51=0,1,G51)*H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="580" t="n"/>
+      <c r="B52" s="1446" t="n"/>
+      <c r="C52" s="1446" t="n"/>
+      <c r="D52" s="1446" t="n"/>
+      <c r="E52" s="111" t="n"/>
+      <c r="F52" s="1437" t="n"/>
+      <c r="G52" s="1437" t="n"/>
+      <c r="H52" s="1288" t="n"/>
+      <c r="I52" s="1288" t="n"/>
+      <c r="J52" s="1294">
+        <f>F52*IF(G52=0,1,G52)*H52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="580" t="n"/>
+      <c r="B53" s="1446" t="n"/>
+      <c r="C53" s="1446" t="n"/>
+      <c r="D53" s="1446" t="n"/>
+      <c r="E53" s="111" t="n"/>
+      <c r="F53" s="1437" t="n"/>
+      <c r="G53" s="1437" t="n"/>
+      <c r="H53" s="1288" t="n"/>
+      <c r="I53" s="1288" t="n"/>
+      <c r="J53" s="1294">
+        <f>F53*IF(G53=0,1,G53)*H53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="580" t="n"/>
+      <c r="B54" s="1446" t="n"/>
+      <c r="C54" s="1446" t="n"/>
+      <c r="D54" s="1446" t="n"/>
+      <c r="E54" s="111" t="n"/>
+      <c r="F54" s="1437" t="n"/>
+      <c r="G54" s="1437" t="n"/>
+      <c r="H54" s="1288" t="n"/>
+      <c r="I54" s="1288" t="n"/>
+      <c r="J54" s="1294">
+        <f>F54*IF(G54=0,1,G54)*H54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="550">
+      <c r="A55" s="572" t="n"/>
+      <c r="B55" s="567" t="n"/>
+      <c r="C55" s="567" t="n"/>
+      <c r="D55" s="567" t="n"/>
+      <c r="E55" s="577" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="F55" s="567" t="n"/>
+      <c r="G55" s="567" t="n"/>
+      <c r="H55" s="567" t="n"/>
+      <c r="I55" s="567" t="n"/>
+      <c r="J55" s="1295">
+        <f>SUM(J40:J54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="550">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B56" s="370" t="n"/>
+      <c r="C56" s="276" t="inlineStr">
+        <is>
+          <t>EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="D56" s="276" t="n"/>
+      <c r="E56" s="606" t="n"/>
+      <c r="F56" s="567" t="n"/>
+      <c r="G56" s="567" t="n"/>
+      <c r="H56" s="567" t="n"/>
+      <c r="I56" s="567" t="n"/>
+      <c r="J56" s="607" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="550">
+      <c r="A57" s="66" t="n"/>
+      <c r="B57" s="276" t="n"/>
+      <c r="C57" s="48" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="48" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F57" s="48" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G57" s="48" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H57" s="48" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="I57" s="48" t="n"/>
+      <c r="J57" s="65" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="550">
+      <c r="A58" s="580" t="n"/>
+      <c r="B58" s="567" t="n"/>
+      <c r="C58" s="567" t="n"/>
+      <c r="D58" s="567" t="n"/>
+      <c r="E58" s="111" t="n"/>
+      <c r="F58" s="1437" t="n"/>
+      <c r="G58" s="1437" t="n"/>
+      <c r="H58" s="1288" t="n"/>
+      <c r="I58" s="1288" t="n"/>
+      <c r="J58" s="1294">
+        <f>F58*IF(G58=0,1,G58)*H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="550">
+      <c r="A59" s="580" t="n"/>
+      <c r="B59" s="567" t="n"/>
+      <c r="C59" s="567" t="n"/>
+      <c r="D59" s="567" t="n"/>
+      <c r="E59" s="111" t="n"/>
+      <c r="F59" s="1437" t="n"/>
+      <c r="G59" s="1437" t="n"/>
+      <c r="H59" s="1288" t="n"/>
+      <c r="I59" s="1288" t="n"/>
+      <c r="J59" s="1294">
+        <f>F59*IF(G59=0,1,G59)*H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="550">
+      <c r="A60" s="580" t="n"/>
+      <c r="B60" s="567" t="n"/>
+      <c r="C60" s="567" t="n"/>
+      <c r="D60" s="567" t="n"/>
+      <c r="E60" s="111" t="n"/>
+      <c r="F60" s="1437" t="n"/>
+      <c r="G60" s="1437" t="n"/>
+      <c r="H60" s="1288" t="n"/>
+      <c r="I60" s="1288" t="n"/>
+      <c r="J60" s="1294">
+        <f>F60*IF(G60=0,1,G60)*H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="550">
+      <c r="A61" s="580" t="n"/>
+      <c r="B61" s="567" t="n"/>
+      <c r="C61" s="567" t="n"/>
+      <c r="D61" s="567" t="n"/>
+      <c r="E61" s="111" t="n"/>
+      <c r="F61" s="1437" t="n"/>
+      <c r="G61" s="1437" t="n"/>
+      <c r="H61" s="1288" t="n"/>
+      <c r="I61" s="1288" t="n"/>
+      <c r="J61" s="1294">
+        <f>F61*IF(G61=0,1,G61)*H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="550">
+      <c r="A62" s="580" t="n"/>
+      <c r="B62" s="567" t="n"/>
+      <c r="C62" s="567" t="n"/>
+      <c r="D62" s="567" t="n"/>
+      <c r="E62" s="111" t="n"/>
+      <c r="F62" s="1437" t="n"/>
+      <c r="G62" s="1437" t="n"/>
+      <c r="H62" s="1288" t="n"/>
+      <c r="I62" s="1288" t="n"/>
+      <c r="J62" s="1294">
+        <f>F62*IF(G62=0,1,G62)*H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="550">
+      <c r="A63" s="580" t="n"/>
+      <c r="B63" s="567" t="n"/>
+      <c r="C63" s="567" t="n"/>
+      <c r="D63" s="567" t="n"/>
+      <c r="E63" s="111" t="n"/>
+      <c r="F63" s="1437" t="n"/>
+      <c r="G63" s="1437" t="n"/>
+      <c r="H63" s="1288" t="n"/>
+      <c r="I63" s="1288" t="n"/>
+      <c r="J63" s="1294">
+        <f>F63*IF(G63=0,1,G63)*H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="580" t="n"/>
+      <c r="B64" s="1446" t="n"/>
+      <c r="C64" s="1446" t="n"/>
+      <c r="D64" s="1446" t="n"/>
+      <c r="E64" s="111" t="n"/>
+      <c r="F64" s="1437" t="n"/>
+      <c r="G64" s="1437" t="n"/>
+      <c r="H64" s="1288" t="n"/>
+      <c r="I64" s="1288" t="n"/>
+      <c r="J64" s="1294">
+        <f>F64*IF(G64=0,1,G64)*H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="580" t="n"/>
+      <c r="B65" s="1446" t="n"/>
+      <c r="C65" s="1446" t="n"/>
+      <c r="D65" s="1446" t="n"/>
+      <c r="E65" s="111" t="n"/>
+      <c r="F65" s="1437" t="n"/>
+      <c r="G65" s="1437" t="n"/>
+      <c r="H65" s="1288" t="n"/>
+      <c r="I65" s="1288" t="n"/>
+      <c r="J65" s="1294">
+        <f>F65*IF(G65=0,1,G65)*H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="580" t="n"/>
+      <c r="B66" s="1446" t="n"/>
+      <c r="C66" s="1446" t="n"/>
+      <c r="D66" s="1446" t="n"/>
+      <c r="E66" s="111" t="n"/>
+      <c r="F66" s="1437" t="n"/>
+      <c r="G66" s="1437" t="n"/>
+      <c r="H66" s="1288" t="n"/>
+      <c r="I66" s="1288" t="n"/>
+      <c r="J66" s="1294">
+        <f>F66*IF(G66=0,1,G66)*H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="580" t="n"/>
+      <c r="B67" s="1446" t="n"/>
+      <c r="C67" s="1446" t="n"/>
+      <c r="D67" s="1446" t="n"/>
+      <c r="E67" s="111" t="n"/>
+      <c r="F67" s="1437" t="n"/>
+      <c r="G67" s="1437" t="n"/>
+      <c r="H67" s="1288" t="n"/>
+      <c r="I67" s="1288" t="n"/>
+      <c r="J67" s="1294">
+        <f>F67*IF(G67=0,1,G67)*H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="580" t="n"/>
+      <c r="B68" s="1446" t="n"/>
+      <c r="C68" s="1446" t="n"/>
+      <c r="D68" s="1446" t="n"/>
+      <c r="E68" s="111" t="n"/>
+      <c r="F68" s="1437" t="n"/>
+      <c r="G68" s="1437" t="n"/>
+      <c r="H68" s="1288" t="n"/>
+      <c r="I68" s="1288" t="n"/>
+      <c r="J68" s="1294">
+        <f>F68*IF(G68=0,1,G68)*H68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="580" t="n"/>
+      <c r="B69" s="1446" t="n"/>
+      <c r="C69" s="1446" t="n"/>
+      <c r="D69" s="1446" t="n"/>
+      <c r="E69" s="111" t="n"/>
+      <c r="F69" s="1437" t="n"/>
+      <c r="G69" s="1437" t="n"/>
+      <c r="H69" s="1288" t="n"/>
+      <c r="I69" s="1288" t="n"/>
+      <c r="J69" s="1294">
+        <f>F69*IF(G69=0,1,G69)*H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="580" t="n"/>
+      <c r="B70" s="1446" t="n"/>
+      <c r="C70" s="1446" t="n"/>
+      <c r="D70" s="1446" t="n"/>
+      <c r="E70" s="111" t="n"/>
+      <c r="F70" s="1437" t="n"/>
+      <c r="G70" s="1437" t="n"/>
+      <c r="H70" s="1288" t="n"/>
+      <c r="I70" s="1288" t="n"/>
+      <c r="J70" s="1294">
+        <f>F70*IF(G70=0,1,G70)*H70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="580" t="n"/>
+      <c r="B71" s="1446" t="n"/>
+      <c r="C71" s="1446" t="n"/>
+      <c r="D71" s="1446" t="n"/>
+      <c r="E71" s="111" t="n"/>
+      <c r="F71" s="1437" t="n"/>
+      <c r="G71" s="1437" t="n"/>
+      <c r="H71" s="1288" t="n"/>
+      <c r="I71" s="1288" t="n"/>
+      <c r="J71" s="1294">
+        <f>F71*IF(G71=0,1,G71)*H71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="580" t="n"/>
+      <c r="B72" s="1446" t="n"/>
+      <c r="C72" s="1446" t="n"/>
+      <c r="D72" s="1446" t="n"/>
+      <c r="E72" s="111" t="n"/>
+      <c r="F72" s="1437" t="n"/>
+      <c r="G72" s="1437" t="n"/>
+      <c r="H72" s="1288" t="n"/>
+      <c r="I72" s="1288" t="n"/>
+      <c r="J72" s="1294">
+        <f>F72*IF(G72=0,1,G72)*H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="550">
+      <c r="A73" s="572" t="n"/>
+      <c r="B73" s="567" t="n"/>
+      <c r="C73" s="567" t="n"/>
+      <c r="D73" s="567" t="n"/>
+      <c r="E73" s="577" t="inlineStr">
         <is>
           <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
         </is>
       </c>
-      <c r="F46" s="567" t="n"/>
-      <c r="G46" s="567" t="n"/>
-      <c r="H46" s="567" t="n"/>
-      <c r="I46" s="567" t="n"/>
-      <c r="J46" s="1295">
-        <f>SUM(J40:J45)</f>
+      <c r="F73" s="567" t="n"/>
+      <c r="G73" s="567" t="n"/>
+      <c r="H73" s="567" t="n"/>
+      <c r="I73" s="567" t="n"/>
+      <c r="J73" s="1295">
+        <f>SUM(J58:J72)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="24.75" customHeight="1" s="550">
-      <c r="A47" s="568" t="inlineStr">
+    <row r="74" ht="24.75" customHeight="1" s="550">
+      <c r="A74" s="568" t="inlineStr">
         <is>
           <t xml:space="preserve">                Materiales</t>
         </is>
       </c>
-      <c r="B47" s="567" t="n"/>
-      <c r="C47" s="567" t="n"/>
-      <c r="D47" s="567" t="n"/>
-      <c r="E47" s="567" t="n"/>
-      <c r="F47" s="567" t="n"/>
-      <c r="G47" s="567" t="n"/>
-      <c r="H47" s="567" t="n"/>
-      <c r="I47" s="567" t="n"/>
-      <c r="J47" s="1296">
-        <f>J28</f>
+      <c r="B74" s="567" t="n"/>
+      <c r="C74" s="567" t="n"/>
+      <c r="D74" s="567" t="n"/>
+      <c r="E74" s="567" t="n"/>
+      <c r="F74" s="567" t="n"/>
+      <c r="G74" s="567" t="n"/>
+      <c r="H74" s="567" t="n"/>
+      <c r="I74" s="567" t="n"/>
+      <c r="J74" s="1296">
+        <f>J37</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="24.75" customHeight="1" s="550">
-      <c r="A48" s="568" t="inlineStr">
+    <row r="75" ht="24.75" customHeight="1" s="550">
+      <c r="A75" s="568" t="inlineStr">
         <is>
           <t xml:space="preserve">                Mano de Obra</t>
         </is>
       </c>
-      <c r="B48" s="567" t="n"/>
-      <c r="C48" s="567" t="n"/>
-      <c r="D48" s="567" t="n"/>
-      <c r="E48" s="567" t="n"/>
-      <c r="F48" s="567" t="n"/>
-      <c r="G48" s="567" t="n"/>
-      <c r="H48" s="567" t="n"/>
-      <c r="I48" s="567" t="n"/>
-      <c r="J48" s="1296">
-        <f>J37</f>
+      <c r="B75" s="567" t="n"/>
+      <c r="C75" s="567" t="n"/>
+      <c r="D75" s="567" t="n"/>
+      <c r="E75" s="567" t="n"/>
+      <c r="F75" s="567" t="n"/>
+      <c r="G75" s="567" t="n"/>
+      <c r="H75" s="567" t="n"/>
+      <c r="I75" s="567" t="n"/>
+      <c r="J75" s="1296">
+        <f>J55</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="24.75" customHeight="1" s="550">
-      <c r="A49" s="568" t="inlineStr">
+    <row r="76" ht="24.75" customHeight="1" s="550">
+      <c r="A76" s="568" t="inlineStr">
         <is>
           <t xml:space="preserve">                Equipos y herramientas</t>
         </is>
       </c>
-      <c r="B49" s="567" t="n"/>
-      <c r="C49" s="567" t="n"/>
-      <c r="D49" s="567" t="n"/>
-      <c r="E49" s="567" t="n"/>
-      <c r="F49" s="567" t="n"/>
-      <c r="G49" s="567" t="n"/>
-      <c r="H49" s="567" t="n"/>
-      <c r="I49" s="567" t="n"/>
-      <c r="J49" s="1296">
-        <f>J46</f>
+      <c r="B76" s="567" t="n"/>
+      <c r="C76" s="567" t="n"/>
+      <c r="D76" s="567" t="n"/>
+      <c r="E76" s="567" t="n"/>
+      <c r="F76" s="567" t="n"/>
+      <c r="G76" s="567" t="n"/>
+      <c r="H76" s="567" t="n"/>
+      <c r="I76" s="567" t="n"/>
+      <c r="J76" s="1296">
+        <f>J73</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="19.95" customHeight="1" s="550">
-      <c r="A50" s="1276" t="inlineStr">
+    <row r="77" ht="19.95" customHeight="1" s="550">
+      <c r="A77" s="1276" t="inlineStr">
         <is>
           <t>TOTAL DIRECTO UNITARIO</t>
         </is>
       </c>
-      <c r="B50" s="1217" t="n"/>
-      <c r="C50" s="1217" t="n"/>
-      <c r="D50" s="1217" t="n"/>
-      <c r="E50" s="1217" t="n"/>
-      <c r="F50" s="1217" t="n"/>
-      <c r="G50" s="1217" t="n"/>
-      <c r="H50" s="1217" t="n"/>
-      <c r="I50" s="1217" t="n"/>
-      <c r="J50" s="1297">
-        <f>SUM(J47:J49)</f>
+      <c r="B77" s="1217" t="n"/>
+      <c r="C77" s="1217" t="n"/>
+      <c r="D77" s="1217" t="n"/>
+      <c r="E77" s="1217" t="n"/>
+      <c r="F77" s="1217" t="n"/>
+      <c r="G77" s="1217" t="n"/>
+      <c r="H77" s="1217" t="n"/>
+      <c r="I77" s="1217" t="n"/>
+      <c r="J77" s="1297">
+        <f>SUM(J74:J76)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="4.5" customHeight="1" s="550">
-      <c r="A51" s="67" t="n"/>
-      <c r="B51" s="371" t="n"/>
-      <c r="C51" s="371" t="n"/>
-      <c r="D51" s="371" t="n"/>
-      <c r="E51" s="371" t="n"/>
-      <c r="F51" s="371" t="n"/>
-      <c r="G51" s="371" t="n"/>
-      <c r="H51" s="371" t="n"/>
-      <c r="I51" s="371" t="n"/>
-      <c r="J51" s="68" t="n"/>
+    <row r="78" ht="4.5" customHeight="1" s="550">
+      <c r="A78" s="67" t="n"/>
+      <c r="B78" s="371" t="n"/>
+      <c r="C78" s="371" t="n"/>
+      <c r="D78" s="371" t="n"/>
+      <c r="E78" s="371" t="n"/>
+      <c r="F78" s="371" t="n"/>
+      <c r="G78" s="371" t="n"/>
+      <c r="H78" s="371" t="n"/>
+      <c r="I78" s="371" t="n"/>
+      <c r="J78" s="68" t="n"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="550">
-      <c r="A52" s="584" t="inlineStr">
+    <row r="79" ht="15.75" customHeight="1" s="550">
+      <c r="A79" s="584" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="B52" s="585" t="n"/>
-      <c r="C52" s="585" t="n"/>
-      <c r="D52" s="585" t="n"/>
-      <c r="E52" s="372" t="n"/>
-      <c r="F52" s="597" t="inlineStr">
+      <c r="B79" s="585" t="n"/>
+      <c r="C79" s="585" t="n"/>
+      <c r="D79" s="585" t="n"/>
+      <c r="E79" s="372" t="n"/>
+      <c r="F79" s="597" t="inlineStr">
         <is>
           <t>Vo. Bo. INTERVENTORÍA:</t>
         </is>
       </c>
-      <c r="G52" s="585" t="n"/>
-      <c r="H52" s="585" t="n"/>
-      <c r="I52" s="585" t="n"/>
-      <c r="J52" s="598" t="n"/>
+      <c r="G79" s="585" t="n"/>
+      <c r="H79" s="585" t="n"/>
+      <c r="I79" s="585" t="n"/>
+      <c r="J79" s="598" t="n"/>
     </row>
-    <row r="53" ht="42" customHeight="1" s="550">
-      <c r="A53" s="298" t="inlineStr">
+    <row r="80" ht="42" customHeight="1" s="550">
+      <c r="A80" s="298" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="B53" s="1267" t="n"/>
-      <c r="C53" s="565" t="n"/>
-      <c r="D53" s="565" t="n"/>
-      <c r="E53" s="565" t="n"/>
-      <c r="F53" s="1268" t="inlineStr">
+      <c r="B80" s="1267" t="n"/>
+      <c r="C80" s="565" t="n"/>
+      <c r="D80" s="565" t="n"/>
+      <c r="E80" s="565" t="n"/>
+      <c r="F80" s="1268" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="G53" s="1269" t="n"/>
-      <c r="H53" s="565" t="n"/>
-      <c r="I53" s="565" t="n"/>
-      <c r="J53" s="593" t="n"/>
+      <c r="G80" s="1269" t="n"/>
+      <c r="H80" s="565" t="n"/>
+      <c r="I80" s="565" t="n"/>
+      <c r="J80" s="593" t="n"/>
     </row>
-    <row r="54" ht="24.75" customHeight="1" s="550">
-      <c r="A54" s="298" t="inlineStr">
+    <row r="81" ht="24.75" customHeight="1" s="550">
+      <c r="A81" s="298" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="B54" s="1267" t="n"/>
-      <c r="C54" s="565" t="n"/>
-      <c r="D54" s="565" t="n"/>
-      <c r="E54" s="565" t="n"/>
-      <c r="F54" s="1268" t="inlineStr">
+      <c r="B81" s="1267" t="n"/>
+      <c r="C81" s="565" t="n"/>
+      <c r="D81" s="565" t="n"/>
+      <c r="E81" s="565" t="n"/>
+      <c r="F81" s="1268" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="G54" s="1269" t="n"/>
-      <c r="H54" s="565" t="n"/>
-      <c r="I54" s="565" t="n"/>
-      <c r="J54" s="593" t="n"/>
+      <c r="G81" s="1269" t="n"/>
+      <c r="H81" s="565" t="n"/>
+      <c r="I81" s="565" t="n"/>
+      <c r="J81" s="593" t="n"/>
     </row>
-    <row r="55" ht="24.75" customHeight="1" s="550">
-      <c r="A55" s="298" t="inlineStr">
+    <row r="82" ht="24.75" customHeight="1" s="550">
+      <c r="A82" s="298" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="B55" s="1267" t="n"/>
-      <c r="C55" s="565" t="n"/>
-      <c r="D55" s="565" t="n"/>
-      <c r="E55" s="565" t="n"/>
-      <c r="F55" s="1268" t="inlineStr">
+      <c r="B82" s="1267" t="n"/>
+      <c r="C82" s="565" t="n"/>
+      <c r="D82" s="565" t="n"/>
+      <c r="E82" s="565" t="n"/>
+      <c r="F82" s="1268" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="G55" s="1269" t="n"/>
-      <c r="H55" s="565" t="n"/>
-      <c r="I55" s="565" t="n"/>
-      <c r="J55" s="593" t="n"/>
+      <c r="G82" s="1269" t="n"/>
+      <c r="H82" s="565" t="n"/>
+      <c r="I82" s="565" t="n"/>
+      <c r="J82" s="593" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1" s="550">
-      <c r="A56" s="204" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="550">
+      <c r="A83" s="204" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B56" s="1278" t="n"/>
-      <c r="C56" s="583" t="n"/>
-      <c r="D56" s="583" t="n"/>
-      <c r="E56" s="583" t="n"/>
-      <c r="F56" s="583" t="n"/>
-      <c r="G56" s="583" t="n"/>
-      <c r="H56" s="583" t="n"/>
-      <c r="I56" s="583" t="n"/>
-      <c r="J56" s="335">
+      <c r="B83" s="1278" t="n"/>
+      <c r="C83" s="583" t="n"/>
+      <c r="D83" s="583" t="n"/>
+      <c r="E83" s="583" t="n"/>
+      <c r="F83" s="583" t="n"/>
+      <c r="G83" s="583" t="n"/>
+      <c r="H83" s="583" t="n"/>
+      <c r="I83" s="583" t="n"/>
+      <c r="J83" s="335">
         <f>J5</f>
         <v/>
       </c>
@@ -11692,62 +12098,62 @@
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="E55:I55"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="G54:J54"/>
     <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="B56:I56"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="E73:I73"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="B81:E81"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="F79:J79"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E56:J56"/>
+    <mergeCell ref="G82:J82"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A48:I48"/>
     <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F52:J52"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="G53:J53"/>
     <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B82:E82"/>
     <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="C13:J13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E37:I37"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="E38:J38"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E29:J29"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -10412,32 +10412,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1944750</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>49500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1944750</colOff>
+      <row>8</row>
+      <rowOff>49500</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1764000"/>
@@ -10449,11 +10449,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10637,9 +10637,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.77734375" customWidth="1" style="550" min="1" max="1"/>
@@ -10647,7 +10648,7 @@
     <col width="50.77734375" customWidth="1" style="550" min="3" max="3"/>
     <col width="2.77734375" customWidth="1" style="550" min="4" max="4"/>
     <col width="26.33203125" customWidth="1" style="550" min="5" max="6"/>
-    <col width="2.77734375" customWidth="1" style="550" min="7" max="7"/>
+    <col width="13" customWidth="1" style="550" min="7" max="7"/>
     <col width="26.33203125" customWidth="1" style="550" min="8" max="8"/>
     <col width="2.77734375" customWidth="1" style="550" min="9" max="9"/>
     <col width="26" customWidth="1" style="550" min="10" max="10"/>
@@ -10697,16 +10698,22 @@
       <c r="B4" s="618" t="n"/>
       <c r="C4" s="516" t="n"/>
       <c r="D4" s="618" t="n"/>
-      <c r="E4" s="252" t="n"/>
-      <c r="F4" s="252" t="n"/>
-      <c r="G4" s="252" t="n"/>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="E4" s="573" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="H4" s="118" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="79" t="n"/>
+      <c r="I4" s="801" t="n"/>
+      <c r="J4" s="189" t="inlineStr">
+        <is>
+          <t>RYR-AP-001</t>
+        </is>
+      </c>
       <c r="K4" s="113" t="n"/>
       <c r="M4" s="113" t="n"/>
       <c r="P4" s="113" t="inlineStr">
@@ -10740,53 +10747,43 @@
       <c r="B5" s="618" t="n"/>
       <c r="C5" s="516" t="n"/>
       <c r="D5" s="618" t="n"/>
-      <c r="E5" s="573" t="inlineStr">
+      <c r="E5" s="278" t="inlineStr">
         <is>
-          <t>REFORMAS Y REMODELACIONES</t>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="H5" s="118" t="inlineStr">
+      <c r="F5" s="252" t="n"/>
+      <c r="G5" s="252" t="n"/>
+      <c r="H5" s="195" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Versión</t>
         </is>
       </c>
-      <c r="I5" s="801" t="n"/>
-      <c r="J5" s="189" t="inlineStr">
-        <is>
-          <t>RYR-AP-001</t>
-        </is>
+      <c r="I5" s="784" t="n"/>
+      <c r="J5" s="189" t="n">
+        <v>1</v>
       </c>
       <c r="K5" s="113" t="n"/>
       <c r="M5" s="113" t="n"/>
-      <c r="P5" s="113" t="n"/>
-      <c r="Q5" s="113" t="n"/>
-      <c r="R5" s="114" t="n"/>
-      <c r="S5" s="115" t="n"/>
-      <c r="T5" s="114" t="n"/>
-      <c r="U5" s="115" t="n"/>
-      <c r="V5" s="115" t="n"/>
-      <c r="W5" s="115" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="550">
       <c r="A6" s="618" t="n"/>
       <c r="B6" s="618" t="n"/>
       <c r="C6" s="516" t="n"/>
       <c r="D6" s="618" t="n"/>
-      <c r="E6" s="278" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
+      <c r="E6" s="188" t="n"/>
       <c r="F6" s="252" t="n"/>
       <c r="G6" s="252" t="n"/>
-      <c r="H6" s="195" t="inlineStr">
+      <c r="H6" s="118" t="inlineStr">
         <is>
-          <t>Versión</t>
+          <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="I6" s="784" t="n"/>
-      <c r="J6" s="189" t="n">
-        <v>1</v>
+      <c r="I6" s="801" t="n"/>
+      <c r="J6" s="189" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
       </c>
       <c r="K6" s="113" t="n"/>
       <c r="M6" s="113" t="n"/>
@@ -10796,270 +10793,263 @@
       <c r="B7" s="618" t="n"/>
       <c r="C7" s="516" t="n"/>
       <c r="D7" s="618" t="n"/>
-      <c r="E7" s="188" t="n"/>
+      <c r="E7" s="252" t="n"/>
       <c r="F7" s="252" t="n"/>
       <c r="G7" s="252" t="n"/>
       <c r="H7" s="118" t="inlineStr">
         <is>
-          <t>Fecha de Emisión</t>
+          <t>Página</t>
         </is>
       </c>
       <c r="I7" s="801" t="n"/>
       <c r="J7" s="189" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>1 de 1</t>
         </is>
       </c>
       <c r="K7" s="113" t="n"/>
       <c r="M7" s="113" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="550">
-      <c r="A8" s="618" t="n"/>
-      <c r="B8" s="618" t="n"/>
-      <c r="C8" s="516" t="n"/>
-      <c r="D8" s="618" t="n"/>
+      <c r="A8" s="252" t="n"/>
+      <c r="B8" s="252" t="n"/>
+      <c r="C8" s="252" t="n"/>
+      <c r="D8" s="515" t="n"/>
       <c r="E8" s="252" t="n"/>
-      <c r="F8" s="252" t="n"/>
-      <c r="G8" s="252" t="n"/>
-      <c r="H8" s="118" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="I8" s="801" t="n"/>
-      <c r="J8" s="189" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-      <c r="K8" s="113" t="n"/>
-      <c r="M8" s="113" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="550">
-      <c r="A9" s="252" t="n"/>
-      <c r="B9" s="252" t="n"/>
-      <c r="C9" s="252" t="n"/>
-      <c r="D9" s="515" t="n"/>
-      <c r="E9" s="252" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="25.05" customHeight="1" s="550">
-      <c r="A10" s="576" t="inlineStr">
+    <row r="9" ht="25.05" customHeight="1" s="550">
+      <c r="A9" s="576" t="inlineStr">
         <is>
           <t>LOCALIZACIÓN Y REPLANTEO</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="15" customHeight="1" s="550">
+      <c r="A10" s="586" t="n"/>
+    </row>
     <row r="11" ht="15" customHeight="1" s="550">
-      <c r="A11" s="586" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="550">
-      <c r="A12" s="602" t="inlineStr">
+      <c r="A11" s="602" t="inlineStr">
         <is>
           <t>IDENTIFICACIÓN DEL PROYECTO</t>
         </is>
       </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="550">
+      <c r="A12" s="360" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B12" s="354" t="n"/>
+      <c r="C12" s="603" t="n"/>
+      <c r="D12" s="595" t="n"/>
+      <c r="E12" s="595" t="n"/>
+      <c r="F12" s="595" t="n"/>
+      <c r="G12" s="595" t="n"/>
+      <c r="H12" s="595" t="n"/>
+      <c r="I12" s="595" t="n"/>
+      <c r="J12" s="601" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="550">
       <c r="A13" s="360" t="inlineStr">
         <is>
-          <t>Proyecto</t>
+          <t>No de Contrato</t>
         </is>
       </c>
       <c r="B13" s="354" t="n"/>
-      <c r="C13" s="603" t="n"/>
+      <c r="C13" s="599" t="n"/>
       <c r="D13" s="595" t="n"/>
       <c r="E13" s="595" t="n"/>
-      <c r="F13" s="595" t="n"/>
-      <c r="G13" s="595" t="n"/>
-      <c r="H13" s="595" t="n"/>
-      <c r="I13" s="595" t="n"/>
+      <c r="F13" s="355" t="n"/>
+      <c r="G13" s="355" t="n"/>
+      <c r="H13" s="600" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="I13" s="601" t="n"/>
       <c r="J13" s="601" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="550">
       <c r="A14" s="360" t="inlineStr">
         <is>
-          <t>No de Contrato</t>
+          <t>Contratista</t>
         </is>
       </c>
       <c r="B14" s="354" t="n"/>
-      <c r="C14" s="599" t="n"/>
+      <c r="C14" s="594" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
       <c r="D14" s="595" t="n"/>
       <c r="E14" s="595" t="n"/>
       <c r="F14" s="355" t="n"/>
       <c r="G14" s="355" t="n"/>
       <c r="H14" s="600" t="inlineStr">
         <is>
-          <t>Fecha de Emisión</t>
+          <t>Ubicación</t>
         </is>
       </c>
       <c r="I14" s="601" t="n"/>
       <c r="J14" s="601" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="550">
-      <c r="A15" s="360" t="inlineStr">
-        <is>
-          <t>Contratista</t>
-        </is>
-      </c>
-      <c r="B15" s="354" t="n"/>
-      <c r="C15" s="594" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="D15" s="595" t="n"/>
-      <c r="E15" s="595" t="n"/>
-      <c r="F15" s="355" t="n"/>
-      <c r="G15" s="355" t="n"/>
-      <c r="H15" s="600" t="inlineStr">
-        <is>
-          <t>Ubicación</t>
-        </is>
-      </c>
-      <c r="I15" s="601" t="n"/>
-      <c r="J15" s="601" t="n"/>
+      <c r="A15" s="591" t="n"/>
+      <c r="B15" s="592" t="n"/>
+      <c r="C15" s="592" t="n"/>
+      <c r="D15" s="592" t="n"/>
+      <c r="E15" s="592" t="n"/>
+      <c r="F15" s="592" t="n"/>
+      <c r="G15" s="592" t="n"/>
+      <c r="H15" s="592" t="n"/>
+      <c r="I15" s="592" t="n"/>
+      <c r="J15" s="592" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="550" thickBot="1">
-      <c r="A16" s="591" t="n"/>
-      <c r="B16" s="592" t="n"/>
-      <c r="C16" s="592" t="n"/>
-      <c r="D16" s="592" t="n"/>
-      <c r="E16" s="592" t="n"/>
-      <c r="F16" s="592" t="n"/>
-      <c r="G16" s="592" t="n"/>
-      <c r="H16" s="592" t="n"/>
-      <c r="I16" s="592" t="n"/>
-      <c r="J16" s="592" t="n"/>
-    </row>
-    <row r="17" ht="19.95" customHeight="1" s="550" thickTop="1">
-      <c r="A17" s="574" t="inlineStr">
+    <row r="16" ht="19.95" customHeight="1" s="550" thickBot="1">
+      <c r="A16" s="574" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="B17" s="376" t="n"/>
-      <c r="C17" s="574" t="inlineStr">
+      <c r="B16" s="376" t="n"/>
+      <c r="C16" s="574" t="inlineStr">
         <is>
           <t>CUADRILLA</t>
         </is>
       </c>
-      <c r="D17" s="570" t="n"/>
-      <c r="E17" s="574" t="inlineStr">
+      <c r="D16" s="570" t="n"/>
+      <c r="E16" s="574" t="inlineStr">
         <is>
           <t>JORNADA</t>
         </is>
       </c>
-      <c r="F17" s="575" t="n"/>
-      <c r="G17" s="570" t="n"/>
-      <c r="H17" s="574" t="inlineStr">
+      <c r="F16" s="575" t="n"/>
+      <c r="G16" s="570" t="n"/>
+      <c r="H16" s="574" t="inlineStr">
         <is>
           <t>RENDIMIENTO</t>
         </is>
       </c>
-      <c r="I17" s="581" t="n"/>
-      <c r="J17" s="574" t="inlineStr">
+      <c r="I16" s="581" t="n"/>
+      <c r="J16" s="574" t="inlineStr">
         <is>
           <t>CONSUMO M.O.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.05" customFormat="1" customHeight="1" s="582" thickBot="1">
-      <c r="A18" s="604">
+    <row r="17" ht="25.05" customHeight="1" s="550" thickTop="1">
+      <c r="A17" s="604">
         <f>P4</f>
         <v/>
       </c>
-      <c r="B18" s="376" t="n"/>
-      <c r="C18" s="604">
+      <c r="B17" s="376" t="n"/>
+      <c r="C17" s="604">
         <f>S4</f>
         <v/>
       </c>
-      <c r="D18" s="571" t="n"/>
-      <c r="E18" s="604">
+      <c r="D17" s="571" t="n"/>
+      <c r="E17" s="604">
         <f>U4</f>
         <v/>
       </c>
-      <c r="F18" s="605" t="n"/>
-      <c r="G18" s="571" t="n"/>
-      <c r="H18" s="604">
-        <f>A1&amp;" "&amp;A18&amp;"/jornada"</f>
+      <c r="F17" s="605" t="n"/>
+      <c r="G17" s="571" t="n"/>
+      <c r="H17" s="604">
+        <f>A1&amp;" "&amp;A17&amp;"/jornada"</f>
         <v/>
       </c>
-      <c r="J18" s="377">
+      <c r="J17" s="377">
         <f>IFERROR(1/V4,0)</f>
         <v/>
       </c>
     </row>
+    <row r="18" ht="15" customFormat="1" customHeight="1" s="582" thickBot="1">
+      <c r="A18" s="578" t="n"/>
+      <c r="B18" s="579" t="n"/>
+      <c r="C18" s="579" t="n"/>
+      <c r="D18" s="579" t="n"/>
+      <c r="E18" s="579" t="n"/>
+      <c r="F18" s="579" t="n"/>
+      <c r="G18" s="579" t="n"/>
+      <c r="H18" s="579" t="n"/>
+      <c r="I18" s="579" t="n"/>
+      <c r="J18" s="579" t="n"/>
+    </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="353" thickTop="1">
-      <c r="A19" s="578" t="n"/>
-      <c r="B19" s="579" t="n"/>
-      <c r="C19" s="579" t="n"/>
-      <c r="D19" s="579" t="n"/>
-      <c r="E19" s="579" t="n"/>
-      <c r="F19" s="579" t="n"/>
-      <c r="G19" s="579" t="n"/>
-      <c r="H19" s="579" t="n"/>
-      <c r="I19" s="579" t="n"/>
-      <c r="J19" s="579" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="550">
-      <c r="A20" s="361" t="inlineStr">
+      <c r="A19" s="361" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B20" s="366" t="n"/>
-      <c r="C20" s="1286" t="inlineStr">
+      <c r="B19" s="366" t="n"/>
+      <c r="C19" s="1286" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="D20" s="1287" t="n"/>
-      <c r="E20" s="588" t="n"/>
-      <c r="F20" s="589" t="n"/>
-      <c r="G20" s="589" t="n"/>
-      <c r="H20" s="589" t="n"/>
-      <c r="I20" s="589" t="n"/>
-      <c r="J20" s="590" t="n"/>
+      <c r="D19" s="1287" t="n"/>
+      <c r="E19" s="588" t="n"/>
+      <c r="F19" s="589" t="n"/>
+      <c r="G19" s="589" t="n"/>
+      <c r="H19" s="589" t="n"/>
+      <c r="I19" s="589" t="n"/>
+      <c r="J19" s="590" t="n"/>
     </row>
-    <row r="21" ht="15" customFormat="1" customHeight="1" s="690">
-      <c r="A21" s="356" t="n"/>
-      <c r="B21" s="367" t="n"/>
-      <c r="C21" s="357" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="550">
+      <c r="A20" s="356" t="n"/>
+      <c r="B20" s="367" t="n"/>
+      <c r="C20" s="357" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D21" s="358" t="n"/>
-      <c r="E21" s="358" t="inlineStr">
+      <c r="D20" s="358" t="n"/>
+      <c r="E20" s="358" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F21" s="358" t="inlineStr">
+      <c r="F20" s="358" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="G20" s="358" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="H21" s="358" t="inlineStr">
+      <c r="H20" s="358" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I21" s="358" t="n"/>
-      <c r="J21" s="359" t="inlineStr">
+      <c r="I20" s="358" t="n"/>
+      <c r="J20" s="359" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customFormat="1" customHeight="1" s="690">
+      <c r="A21" s="566" t="n"/>
+      <c r="B21" s="567" t="n"/>
+      <c r="C21" s="567" t="n"/>
+      <c r="D21" s="567" t="n"/>
+      <c r="E21" s="111" t="n"/>
+      <c r="F21" s="112" t="n"/>
+      <c r="G21" s="112" t="n"/>
+      <c r="H21" s="1288" t="n"/>
+      <c r="I21" s="1288" t="n"/>
+      <c r="J21" s="1289">
+        <f>F21*IF(G21=0,1,G21)*H21</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="550">
@@ -11130,8 +11120,8 @@
       <c r="E26" s="111" t="n"/>
       <c r="F26" s="112" t="n"/>
       <c r="G26" s="112" t="n"/>
-      <c r="H26" s="1288" t="n"/>
-      <c r="I26" s="1288" t="n"/>
+      <c r="H26" s="1290" t="n"/>
+      <c r="I26" s="1290" t="n"/>
       <c r="J26" s="1289">
         <f>F26*IF(G26=0,1,G26)*H26</f>
         <v/>
@@ -11139,14 +11129,14 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="550">
       <c r="A27" s="566" t="n"/>
-      <c r="B27" s="567" t="n"/>
-      <c r="C27" s="567" t="n"/>
-      <c r="D27" s="567" t="n"/>
+      <c r="B27" s="1446" t="n"/>
+      <c r="C27" s="1446" t="n"/>
+      <c r="D27" s="1446" t="n"/>
       <c r="E27" s="111" t="n"/>
       <c r="F27" s="112" t="n"/>
       <c r="G27" s="112" t="n"/>
-      <c r="H27" s="1290" t="n"/>
-      <c r="I27" s="1290" t="n"/>
+      <c r="H27" s="1288" t="n"/>
+      <c r="I27" s="1288" t="n"/>
       <c r="J27" s="1289">
         <f>F27*IF(G27=0,1,G27)*H27</f>
         <v/>
@@ -11272,94 +11262,94 @@
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="566" t="n"/>
-      <c r="B36" s="1446" t="n"/>
-      <c r="C36" s="1446" t="n"/>
-      <c r="D36" s="1446" t="n"/>
-      <c r="E36" s="111" t="n"/>
-      <c r="F36" s="112" t="n"/>
-      <c r="G36" s="112" t="n"/>
-      <c r="H36" s="1288" t="n"/>
-      <c r="I36" s="1288" t="n"/>
-      <c r="J36" s="1289">
-        <f>F36*IF(G36=0,1,G36)*H36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="550">
-      <c r="A37" s="587" t="n"/>
-      <c r="B37" s="1291" t="n"/>
-      <c r="C37" s="1291" t="n"/>
-      <c r="D37" s="1291" t="n"/>
-      <c r="E37" s="596" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="550">
+      <c r="A36" s="587" t="n"/>
+      <c r="B36" s="1291" t="n"/>
+      <c r="C36" s="1291" t="n"/>
+      <c r="D36" s="1291" t="n"/>
+      <c r="E36" s="596" t="inlineStr">
         <is>
           <t>SUBTOTAL MATERIALES</t>
         </is>
       </c>
-      <c r="F37" s="1291" t="n"/>
-      <c r="G37" s="1291" t="n"/>
-      <c r="H37" s="1291" t="n"/>
-      <c r="I37" s="1291" t="n"/>
-      <c r="J37" s="1292">
-        <f>SUM(J22:J36)</f>
+      <c r="F36" s="1291" t="n"/>
+      <c r="G36" s="1291" t="n"/>
+      <c r="H36" s="1291" t="n"/>
+      <c r="I36" s="1291" t="n"/>
+      <c r="J36" s="1292">
+        <f>SUM(J21:J35)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="550">
-      <c r="A38" s="187" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="550">
+      <c r="A37" s="187" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B38" s="368" t="n"/>
-      <c r="C38" s="275" t="inlineStr">
+      <c r="B37" s="368" t="n"/>
+      <c r="C37" s="275" t="inlineStr">
         <is>
           <t>MANO DE OBRA</t>
         </is>
       </c>
-      <c r="D38" s="275" t="n"/>
-      <c r="E38" s="608" t="n"/>
-      <c r="F38" s="609" t="n"/>
-      <c r="G38" s="609" t="n"/>
-      <c r="H38" s="609" t="n"/>
-      <c r="I38" s="609" t="n"/>
-      <c r="J38" s="610" t="n"/>
+      <c r="D37" s="275" t="n"/>
+      <c r="E37" s="608" t="n"/>
+      <c r="F37" s="609" t="n"/>
+      <c r="G37" s="609" t="n"/>
+      <c r="H37" s="609" t="n"/>
+      <c r="I37" s="609" t="n"/>
+      <c r="J37" s="610" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="550">
-      <c r="A39" s="64" t="n"/>
-      <c r="B39" s="369" t="n"/>
-      <c r="C39" s="48" t="inlineStr">
+    <row r="38" ht="15" customHeight="1" s="550">
+      <c r="A38" s="64" t="n"/>
+      <c r="B38" s="369" t="n"/>
+      <c r="C38" s="48" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="48" t="inlineStr">
+      <c r="D38" s="48" t="n"/>
+      <c r="E38" s="48" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F39" s="48" t="inlineStr">
+      <c r="F38" s="48" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G39" s="48" t="inlineStr">
+      <c r="G38" s="48" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="H39" s="48" t="inlineStr">
+      <c r="H38" s="48" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I39" s="48" t="n"/>
-      <c r="J39" s="65" t="inlineStr">
+      <c r="I38" s="48" t="n"/>
+      <c r="J38" s="65" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="550">
+      <c r="A39" s="580" t="n"/>
+      <c r="B39" s="567" t="n"/>
+      <c r="C39" s="567" t="n"/>
+      <c r="D39" s="567" t="n"/>
+      <c r="E39" s="111" t="n"/>
+      <c r="F39" s="1437" t="n"/>
+      <c r="G39" s="1437" t="n"/>
+      <c r="H39" s="1288" t="n"/>
+      <c r="I39" s="1288" t="n"/>
+      <c r="J39" s="1294">
+        <f>F39*IF(G39=0,1,G39)*H39</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="550">
@@ -11430,8 +11420,8 @@
       <c r="E44" s="111" t="n"/>
       <c r="F44" s="1437" t="n"/>
       <c r="G44" s="1437" t="n"/>
-      <c r="H44" s="1288" t="n"/>
-      <c r="I44" s="1288" t="n"/>
+      <c r="H44" s="1290" t="n"/>
+      <c r="I44" s="1290" t="n"/>
       <c r="J44" s="1294">
         <f>F44*IF(G44=0,1,G44)*H44</f>
         <v/>
@@ -11439,14 +11429,14 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="550">
       <c r="A45" s="580" t="n"/>
-      <c r="B45" s="567" t="n"/>
-      <c r="C45" s="567" t="n"/>
-      <c r="D45" s="567" t="n"/>
+      <c r="B45" s="1446" t="n"/>
+      <c r="C45" s="1446" t="n"/>
+      <c r="D45" s="1446" t="n"/>
       <c r="E45" s="111" t="n"/>
       <c r="F45" s="1437" t="n"/>
       <c r="G45" s="1437" t="n"/>
-      <c r="H45" s="1290" t="n"/>
-      <c r="I45" s="1290" t="n"/>
+      <c r="H45" s="1288" t="n"/>
+      <c r="I45" s="1288" t="n"/>
       <c r="J45" s="1294">
         <f>F45*IF(G45=0,1,G45)*H45</f>
         <v/>
@@ -11572,94 +11562,94 @@
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="580" t="n"/>
-      <c r="B54" s="1446" t="n"/>
-      <c r="C54" s="1446" t="n"/>
-      <c r="D54" s="1446" t="n"/>
-      <c r="E54" s="111" t="n"/>
-      <c r="F54" s="1437" t="n"/>
-      <c r="G54" s="1437" t="n"/>
-      <c r="H54" s="1288" t="n"/>
-      <c r="I54" s="1288" t="n"/>
-      <c r="J54" s="1294">
-        <f>F54*IF(G54=0,1,G54)*H54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="550">
-      <c r="A55" s="572" t="n"/>
-      <c r="B55" s="567" t="n"/>
-      <c r="C55" s="567" t="n"/>
-      <c r="D55" s="567" t="n"/>
-      <c r="E55" s="577" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="550">
+      <c r="A54" s="572" t="n"/>
+      <c r="B54" s="567" t="n"/>
+      <c r="C54" s="567" t="n"/>
+      <c r="D54" s="567" t="n"/>
+      <c r="E54" s="577" t="inlineStr">
         <is>
           <t>SUBTOTAL MANO DE OBRA</t>
         </is>
       </c>
+      <c r="F54" s="567" t="n"/>
+      <c r="G54" s="567" t="n"/>
+      <c r="H54" s="567" t="n"/>
+      <c r="I54" s="567" t="n"/>
+      <c r="J54" s="1295">
+        <f>SUM(J39:J53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="550">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B55" s="370" t="n"/>
+      <c r="C55" s="276" t="inlineStr">
+        <is>
+          <t>EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="D55" s="276" t="n"/>
+      <c r="E55" s="606" t="n"/>
       <c r="F55" s="567" t="n"/>
       <c r="G55" s="567" t="n"/>
       <c r="H55" s="567" t="n"/>
       <c r="I55" s="567" t="n"/>
-      <c r="J55" s="1295">
-        <f>SUM(J40:J54)</f>
-        <v/>
-      </c>
+      <c r="J55" s="607" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1" s="550">
-      <c r="A56" s="63" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B56" s="370" t="n"/>
-      <c r="C56" s="276" t="inlineStr">
-        <is>
-          <t>EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="D56" s="276" t="n"/>
-      <c r="E56" s="606" t="n"/>
-      <c r="F56" s="567" t="n"/>
-      <c r="G56" s="567" t="n"/>
-      <c r="H56" s="567" t="n"/>
-      <c r="I56" s="567" t="n"/>
-      <c r="J56" s="607" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="550">
-      <c r="A57" s="66" t="n"/>
-      <c r="B57" s="276" t="n"/>
-      <c r="C57" s="48" t="inlineStr">
+    <row r="56" ht="15.75" customHeight="1" s="550">
+      <c r="A56" s="66" t="n"/>
+      <c r="B56" s="276" t="n"/>
+      <c r="C56" s="48" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="48" t="inlineStr">
+      <c r="D56" s="48" t="n"/>
+      <c r="E56" s="48" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F57" s="48" t="inlineStr">
+      <c r="F56" s="48" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G57" s="48" t="inlineStr">
+      <c r="G56" s="48" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="H57" s="48" t="inlineStr">
+      <c r="H56" s="48" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="I57" s="48" t="n"/>
-      <c r="J57" s="65" t="inlineStr">
+      <c r="I56" s="48" t="n"/>
+      <c r="J56" s="65" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="550">
+      <c r="A57" s="580" t="n"/>
+      <c r="B57" s="567" t="n"/>
+      <c r="C57" s="567" t="n"/>
+      <c r="D57" s="567" t="n"/>
+      <c r="E57" s="111" t="n"/>
+      <c r="F57" s="1437" t="n"/>
+      <c r="G57" s="1437" t="n"/>
+      <c r="H57" s="1288" t="n"/>
+      <c r="I57" s="1288" t="n"/>
+      <c r="J57" s="1294">
+        <f>F57*IF(G57=0,1,G57)*H57</f>
+        <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="550">
@@ -11739,9 +11729,9 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="550">
       <c r="A63" s="580" t="n"/>
-      <c r="B63" s="567" t="n"/>
-      <c r="C63" s="567" t="n"/>
-      <c r="D63" s="567" t="n"/>
+      <c r="B63" s="1446" t="n"/>
+      <c r="C63" s="1446" t="n"/>
+      <c r="D63" s="1446" t="n"/>
       <c r="E63" s="111" t="n"/>
       <c r="F63" s="1437" t="n"/>
       <c r="G63" s="1437" t="n"/>
@@ -11872,44 +11862,48 @@
         <v/>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="580" t="n"/>
-      <c r="B72" s="1446" t="n"/>
-      <c r="C72" s="1446" t="n"/>
-      <c r="D72" s="1446" t="n"/>
-      <c r="E72" s="111" t="n"/>
-      <c r="F72" s="1437" t="n"/>
-      <c r="G72" s="1437" t="n"/>
-      <c r="H72" s="1288" t="n"/>
-      <c r="I72" s="1288" t="n"/>
-      <c r="J72" s="1294">
-        <f>F72*IF(G72=0,1,G72)*H72</f>
+    <row r="72" ht="15" customHeight="1" s="550">
+      <c r="A72" s="572" t="n"/>
+      <c r="B72" s="567" t="n"/>
+      <c r="C72" s="567" t="n"/>
+      <c r="D72" s="567" t="n"/>
+      <c r="E72" s="577" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="F72" s="567" t="n"/>
+      <c r="G72" s="567" t="n"/>
+      <c r="H72" s="567" t="n"/>
+      <c r="I72" s="567" t="n"/>
+      <c r="J72" s="1295">
+        <f>SUM(J57:J71)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="550">
-      <c r="A73" s="572" t="n"/>
+    <row r="73" ht="24.75" customHeight="1" s="550">
+      <c r="A73" s="568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Materiales</t>
+        </is>
+      </c>
       <c r="B73" s="567" t="n"/>
       <c r="C73" s="567" t="n"/>
       <c r="D73" s="567" t="n"/>
-      <c r="E73" s="577" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
+      <c r="E73" s="567" t="n"/>
       <c r="F73" s="567" t="n"/>
       <c r="G73" s="567" t="n"/>
       <c r="H73" s="567" t="n"/>
       <c r="I73" s="567" t="n"/>
-      <c r="J73" s="1295">
-        <f>SUM(J58:J72)</f>
+      <c r="J73" s="1296">
+        <f>J36</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="24.75" customHeight="1" s="550">
       <c r="A74" s="568" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Materiales</t>
+          <t xml:space="preserve">                Mano de Obra</t>
         </is>
       </c>
       <c r="B74" s="567" t="n"/>
@@ -11921,14 +11915,14 @@
       <c r="H74" s="567" t="n"/>
       <c r="I74" s="567" t="n"/>
       <c r="J74" s="1296">
-        <f>J37</f>
+        <f>J54</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="24.75" customHeight="1" s="550">
       <c r="A75" s="568" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Mano de Obra</t>
+          <t xml:space="preserve">                Equipos y herramientas</t>
         </is>
       </c>
       <c r="B75" s="567" t="n"/>
@@ -11940,84 +11934,85 @@
       <c r="H75" s="567" t="n"/>
       <c r="I75" s="567" t="n"/>
       <c r="J75" s="1296">
-        <f>J55</f>
+        <f>J72</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="24.75" customHeight="1" s="550">
-      <c r="A76" s="568" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Equipos y herramientas</t>
-        </is>
-      </c>
-      <c r="B76" s="567" t="n"/>
-      <c r="C76" s="567" t="n"/>
-      <c r="D76" s="567" t="n"/>
-      <c r="E76" s="567" t="n"/>
-      <c r="F76" s="567" t="n"/>
-      <c r="G76" s="567" t="n"/>
-      <c r="H76" s="567" t="n"/>
-      <c r="I76" s="567" t="n"/>
-      <c r="J76" s="1296">
-        <f>J73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="19.95" customHeight="1" s="550">
-      <c r="A77" s="1276" t="inlineStr">
+    <row r="76" ht="19.95" customHeight="1" s="550">
+      <c r="A76" s="1276" t="inlineStr">
         <is>
           <t>TOTAL DIRECTO UNITARIO</t>
         </is>
       </c>
-      <c r="B77" s="1217" t="n"/>
-      <c r="C77" s="1217" t="n"/>
-      <c r="D77" s="1217" t="n"/>
-      <c r="E77" s="1217" t="n"/>
-      <c r="F77" s="1217" t="n"/>
-      <c r="G77" s="1217" t="n"/>
-      <c r="H77" s="1217" t="n"/>
-      <c r="I77" s="1217" t="n"/>
-      <c r="J77" s="1297">
-        <f>SUM(J74:J76)</f>
+      <c r="B76" s="1217" t="n"/>
+      <c r="C76" s="1217" t="n"/>
+      <c r="D76" s="1217" t="n"/>
+      <c r="E76" s="1217" t="n"/>
+      <c r="F76" s="1217" t="n"/>
+      <c r="G76" s="1217" t="n"/>
+      <c r="H76" s="1217" t="n"/>
+      <c r="I76" s="1217" t="n"/>
+      <c r="J76" s="1297">
+        <f>SUM(J73:J75)</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="4.5" customHeight="1" s="550">
-      <c r="A78" s="67" t="n"/>
-      <c r="B78" s="371" t="n"/>
-      <c r="C78" s="371" t="n"/>
-      <c r="D78" s="371" t="n"/>
-      <c r="E78" s="371" t="n"/>
-      <c r="F78" s="371" t="n"/>
-      <c r="G78" s="371" t="n"/>
-      <c r="H78" s="371" t="n"/>
-      <c r="I78" s="371" t="n"/>
-      <c r="J78" s="68" t="n"/>
+    <row r="77" ht="4.5" customHeight="1" s="550">
+      <c r="A77" s="67" t="n"/>
+      <c r="B77" s="371" t="n"/>
+      <c r="C77" s="371" t="n"/>
+      <c r="D77" s="371" t="n"/>
+      <c r="E77" s="371" t="n"/>
+      <c r="F77" s="371" t="n"/>
+      <c r="G77" s="371" t="n"/>
+      <c r="H77" s="371" t="n"/>
+      <c r="I77" s="371" t="n"/>
+      <c r="J77" s="68" t="n"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="550">
-      <c r="A79" s="584" t="inlineStr">
+    <row r="78" ht="15.75" customHeight="1" s="550">
+      <c r="A78" s="584" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="B79" s="585" t="n"/>
-      <c r="C79" s="585" t="n"/>
-      <c r="D79" s="585" t="n"/>
-      <c r="E79" s="372" t="n"/>
-      <c r="F79" s="597" t="inlineStr">
+      <c r="B78" s="585" t="n"/>
+      <c r="C78" s="585" t="n"/>
+      <c r="D78" s="585" t="n"/>
+      <c r="E78" s="372" t="n"/>
+      <c r="F78" s="597" t="inlineStr">
         <is>
           <t>Vo. Bo. INTERVENTORÍA:</t>
         </is>
       </c>
-      <c r="G79" s="585" t="n"/>
-      <c r="H79" s="585" t="n"/>
-      <c r="I79" s="585" t="n"/>
-      <c r="J79" s="598" t="n"/>
+      <c r="G78" s="585" t="n"/>
+      <c r="H78" s="585" t="n"/>
+      <c r="I78" s="585" t="n"/>
+      <c r="J78" s="598" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1" s="550">
+    <row r="79" ht="42" customHeight="1" s="550">
+      <c r="A79" s="298" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="B79" s="1267" t="n"/>
+      <c r="C79" s="565" t="n"/>
+      <c r="D79" s="565" t="n"/>
+      <c r="E79" s="565" t="n"/>
+      <c r="F79" s="1268" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="G79" s="1269" t="n"/>
+      <c r="H79" s="565" t="n"/>
+      <c r="I79" s="565" t="n"/>
+      <c r="J79" s="593" t="n"/>
+    </row>
+    <row r="80" ht="24.75" customHeight="1" s="550">
       <c r="A80" s="298" t="inlineStr">
         <is>
-          <t>FIRMA:</t>
+          <t>NOMBRE:</t>
         </is>
       </c>
       <c r="B80" s="1267" t="n"/>
@@ -12026,7 +12021,7 @@
       <c r="E80" s="565" t="n"/>
       <c r="F80" s="1268" t="inlineStr">
         <is>
-          <t>FIRMA:</t>
+          <t>NOMBRE:</t>
         </is>
       </c>
       <c r="G80" s="1269" t="n"/>
@@ -12037,7 +12032,7 @@
     <row r="81" ht="24.75" customHeight="1" s="550">
       <c r="A81" s="298" t="inlineStr">
         <is>
-          <t>NOMBRE:</t>
+          <t>CARGO:</t>
         </is>
       </c>
       <c r="B81" s="1267" t="n"/>
@@ -12046,7 +12041,7 @@
       <c r="E81" s="565" t="n"/>
       <c r="F81" s="1268" t="inlineStr">
         <is>
-          <t>NOMBRE:</t>
+          <t>CARGO:</t>
         </is>
       </c>
       <c r="G81" s="1269" t="n"/>
@@ -12054,106 +12049,87 @@
       <c r="I81" s="565" t="n"/>
       <c r="J81" s="593" t="n"/>
     </row>
-    <row r="82" ht="24.75" customHeight="1" s="550">
-      <c r="A82" s="298" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="B82" s="1267" t="n"/>
-      <c r="C82" s="565" t="n"/>
-      <c r="D82" s="565" t="n"/>
-      <c r="E82" s="565" t="n"/>
-      <c r="F82" s="1268" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="G82" s="1269" t="n"/>
-      <c r="H82" s="565" t="n"/>
-      <c r="I82" s="565" t="n"/>
-      <c r="J82" s="593" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="550">
-      <c r="A83" s="204" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="550">
+      <c r="A82" s="204" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B83" s="1278" t="n"/>
-      <c r="C83" s="583" t="n"/>
-      <c r="D83" s="583" t="n"/>
-      <c r="E83" s="583" t="n"/>
-      <c r="F83" s="583" t="n"/>
-      <c r="G83" s="583" t="n"/>
-      <c r="H83" s="583" t="n"/>
-      <c r="I83" s="583" t="n"/>
-      <c r="J83" s="335">
-        <f>J5</f>
+      <c r="B82" s="1278" t="n"/>
+      <c r="C82" s="583" t="n"/>
+      <c r="D82" s="583" t="n"/>
+      <c r="E82" s="583" t="n"/>
+      <c r="F82" s="583" t="n"/>
+      <c r="G82" s="583" t="n"/>
+      <c r="H82" s="583" t="n"/>
+      <c r="I82" s="583" t="n"/>
+      <c r="J82" s="335">
+        <f>J4</f>
         <v/>
       </c>
     </row>
+    <row r="83" ht="15" customHeight="1" s="550"/>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F78:J78"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="A62:D62"/>
-    <mergeCell ref="E55:I55"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A43:D43"/>
-    <mergeCell ref="B80:E80"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E73:I73"/>
-    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A9:J9"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="B81:E81"/>
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F79:J79"/>
-    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="C12:J12"/>
     <mergeCell ref="A61:D61"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E56:J56"/>
-    <mergeCell ref="G82:J82"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="E37:J37"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="B83:I83"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="E36:I36"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E54:I54"/>
+    <mergeCell ref="A18:J18"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="E72:I72"/>
+    <mergeCell ref="A78:C78"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E38:J38"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -11022,7 +11022,7 @@
       </c>
       <c r="G20" s="358" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Factor de Desperdicio</t>
         </is>
       </c>
       <c r="H20" s="358" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="G38" s="48" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Rendimiento</t>
         </is>
       </c>
       <c r="H38" s="48" t="inlineStr">
@@ -11348,7 +11348,7 @@
       <c r="H39" s="1288" t="n"/>
       <c r="I39" s="1288" t="n"/>
       <c r="J39" s="1294">
-        <f>F39*IF(G39=0,1,G39)*H39</f>
+        <f>G39*H39</f>
         <v/>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       <c r="H40" s="1288" t="n"/>
       <c r="I40" s="1288" t="n"/>
       <c r="J40" s="1294">
-        <f>F40*IF(G40=0,1,G40)*H40</f>
+        <f>G40*H40</f>
         <v/>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       <c r="H41" s="1288" t="n"/>
       <c r="I41" s="1288" t="n"/>
       <c r="J41" s="1294">
-        <f>F41*IF(G41=0,1,G41)*H41</f>
+        <f>G41*H41</f>
         <v/>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       <c r="H42" s="1288" t="n"/>
       <c r="I42" s="1288" t="n"/>
       <c r="J42" s="1294">
-        <f>F42*IF(G42=0,1,G42)*H42</f>
+        <f>G42*H42</f>
         <v/>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       <c r="H43" s="1288" t="n"/>
       <c r="I43" s="1288" t="n"/>
       <c r="J43" s="1294">
-        <f>F43*IF(G43=0,1,G43)*H43</f>
+        <f>G43*H43</f>
         <v/>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       <c r="H44" s="1290" t="n"/>
       <c r="I44" s="1290" t="n"/>
       <c r="J44" s="1294">
-        <f>F44*IF(G44=0,1,G44)*H44</f>
+        <f>G44*H44</f>
         <v/>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       <c r="H45" s="1288" t="n"/>
       <c r="I45" s="1288" t="n"/>
       <c r="J45" s="1294">
-        <f>F45*IF(G45=0,1,G45)*H45</f>
+        <f>G45*H45</f>
         <v/>
       </c>
     </row>
@@ -11453,7 +11453,7 @@
       <c r="H46" s="1288" t="n"/>
       <c r="I46" s="1288" t="n"/>
       <c r="J46" s="1294">
-        <f>F46*IF(G46=0,1,G46)*H46</f>
+        <f>G46*H46</f>
         <v/>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       <c r="H47" s="1288" t="n"/>
       <c r="I47" s="1288" t="n"/>
       <c r="J47" s="1294">
-        <f>F47*IF(G47=0,1,G47)*H47</f>
+        <f>G47*H47</f>
         <v/>
       </c>
     </row>
@@ -11483,7 +11483,7 @@
       <c r="H48" s="1288" t="n"/>
       <c r="I48" s="1288" t="n"/>
       <c r="J48" s="1294">
-        <f>F48*IF(G48=0,1,G48)*H48</f>
+        <f>G48*H48</f>
         <v/>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       <c r="H49" s="1288" t="n"/>
       <c r="I49" s="1288" t="n"/>
       <c r="J49" s="1294">
-        <f>F49*IF(G49=0,1,G49)*H49</f>
+        <f>G49*H49</f>
         <v/>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       <c r="H50" s="1288" t="n"/>
       <c r="I50" s="1288" t="n"/>
       <c r="J50" s="1294">
-        <f>F50*IF(G50=0,1,G50)*H50</f>
+        <f>G50*H50</f>
         <v/>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       <c r="H51" s="1288" t="n"/>
       <c r="I51" s="1288" t="n"/>
       <c r="J51" s="1294">
-        <f>F51*IF(G51=0,1,G51)*H51</f>
+        <f>G51*H51</f>
         <v/>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       <c r="H52" s="1288" t="n"/>
       <c r="I52" s="1288" t="n"/>
       <c r="J52" s="1294">
-        <f>F52*IF(G52=0,1,G52)*H52</f>
+        <f>G52*H52</f>
         <v/>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       <c r="H53" s="1288" t="n"/>
       <c r="I53" s="1288" t="n"/>
       <c r="J53" s="1294">
-        <f>F53*IF(G53=0,1,G53)*H53</f>
+        <f>G53*H53</f>
         <v/>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="G56" s="48" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Rendimiento</t>
         </is>
       </c>
       <c r="H56" s="48" t="inlineStr">
@@ -11648,7 +11648,7 @@
       <c r="H57" s="1288" t="n"/>
       <c r="I57" s="1288" t="n"/>
       <c r="J57" s="1294">
-        <f>F57*IF(G57=0,1,G57)*H57</f>
+        <f>G57*H57</f>
         <v/>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       <c r="H58" s="1288" t="n"/>
       <c r="I58" s="1288" t="n"/>
       <c r="J58" s="1294">
-        <f>F58*IF(G58=0,1,G58)*H58</f>
+        <f>G58*H58</f>
         <v/>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       <c r="H59" s="1288" t="n"/>
       <c r="I59" s="1288" t="n"/>
       <c r="J59" s="1294">
-        <f>F59*IF(G59=0,1,G59)*H59</f>
+        <f>G59*H59</f>
         <v/>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       <c r="H60" s="1288" t="n"/>
       <c r="I60" s="1288" t="n"/>
       <c r="J60" s="1294">
-        <f>F60*IF(G60=0,1,G60)*H60</f>
+        <f>G60*H60</f>
         <v/>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       <c r="H61" s="1288" t="n"/>
       <c r="I61" s="1288" t="n"/>
       <c r="J61" s="1294">
-        <f>F61*IF(G61=0,1,G61)*H61</f>
+        <f>G61*H61</f>
         <v/>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       <c r="H62" s="1288" t="n"/>
       <c r="I62" s="1288" t="n"/>
       <c r="J62" s="1294">
-        <f>F62*IF(G62=0,1,G62)*H62</f>
+        <f>G62*H62</f>
         <v/>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       <c r="H63" s="1288" t="n"/>
       <c r="I63" s="1288" t="n"/>
       <c r="J63" s="1294">
-        <f>F63*IF(G63=0,1,G63)*H63</f>
+        <f>G63*H63</f>
         <v/>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       <c r="H64" s="1288" t="n"/>
       <c r="I64" s="1288" t="n"/>
       <c r="J64" s="1294">
-        <f>F64*IF(G64=0,1,G64)*H64</f>
+        <f>G64*H64</f>
         <v/>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       <c r="H65" s="1288" t="n"/>
       <c r="I65" s="1288" t="n"/>
       <c r="J65" s="1294">
-        <f>F65*IF(G65=0,1,G65)*H65</f>
+        <f>G65*H65</f>
         <v/>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       <c r="H66" s="1288" t="n"/>
       <c r="I66" s="1288" t="n"/>
       <c r="J66" s="1294">
-        <f>F66*IF(G66=0,1,G66)*H66</f>
+        <f>G66*H66</f>
         <v/>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       <c r="H67" s="1288" t="n"/>
       <c r="I67" s="1288" t="n"/>
       <c r="J67" s="1294">
-        <f>F67*IF(G67=0,1,G67)*H67</f>
+        <f>G67*H67</f>
         <v/>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       <c r="H68" s="1288" t="n"/>
       <c r="I68" s="1288" t="n"/>
       <c r="J68" s="1294">
-        <f>F68*IF(G68=0,1,G68)*H68</f>
+        <f>G68*H68</f>
         <v/>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       <c r="H69" s="1288" t="n"/>
       <c r="I69" s="1288" t="n"/>
       <c r="J69" s="1294">
-        <f>F69*IF(G69=0,1,G69)*H69</f>
+        <f>G69*H69</f>
         <v/>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       <c r="H70" s="1288" t="n"/>
       <c r="I70" s="1288" t="n"/>
       <c r="J70" s="1294">
-        <f>F70*IF(G70=0,1,G70)*H70</f>
+        <f>G70*H70</f>
         <v/>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       <c r="H71" s="1288" t="n"/>
       <c r="I71" s="1288" t="n"/>
       <c r="J71" s="1294">
-        <f>F71*IF(G71=0,1,G71)*H71</f>
+        <f>G71*H71</f>
         <v/>
       </c>
     </row>
@@ -12071,65 +12071,65 @@
     <row r="83" ht="15" customHeight="1" s="550"/>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="E19:J19"/>
+    <mergeCell ref="F78:J78"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="I16:I17"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="B80:E80"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="B79:E79"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A76:I76"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="D1:J1"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="C12:J12"/>
     <mergeCell ref="B82:I82"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="C13:E13"/>
     <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E36:I36"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="E55:J55"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F78:J78"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E36:I36"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E54:I54"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="E72:I72"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="G80:J80"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -11348,7 +11348,7 @@
       <c r="H39" s="1288" t="n"/>
       <c r="I39" s="1288" t="n"/>
       <c r="J39" s="1294">
-        <f>G39*H39</f>
+        <f>F39*IF(G39=0,1,G39)*H39</f>
         <v/>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       <c r="H40" s="1288" t="n"/>
       <c r="I40" s="1288" t="n"/>
       <c r="J40" s="1294">
-        <f>G40*H40</f>
+        <f>F40*IF(G40=0,1,G40)*H40</f>
         <v/>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       <c r="H41" s="1288" t="n"/>
       <c r="I41" s="1288" t="n"/>
       <c r="J41" s="1294">
-        <f>G41*H41</f>
+        <f>F41*IF(G41=0,1,G41)*H41</f>
         <v/>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       <c r="H42" s="1288" t="n"/>
       <c r="I42" s="1288" t="n"/>
       <c r="J42" s="1294">
-        <f>G42*H42</f>
+        <f>F42*IF(G42=0,1,G42)*H42</f>
         <v/>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       <c r="H43" s="1288" t="n"/>
       <c r="I43" s="1288" t="n"/>
       <c r="J43" s="1294">
-        <f>G43*H43</f>
+        <f>F43*IF(G43=0,1,G43)*H43</f>
         <v/>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       <c r="H44" s="1290" t="n"/>
       <c r="I44" s="1290" t="n"/>
       <c r="J44" s="1294">
-        <f>G44*H44</f>
+        <f>F44*IF(G44=0,1,G44)*H44</f>
         <v/>
       </c>
     </row>
@@ -11438,7 +11438,7 @@
       <c r="H45" s="1288" t="n"/>
       <c r="I45" s="1288" t="n"/>
       <c r="J45" s="1294">
-        <f>G45*H45</f>
+        <f>F45*IF(G45=0,1,G45)*H45</f>
         <v/>
       </c>
     </row>
@@ -11453,7 +11453,7 @@
       <c r="H46" s="1288" t="n"/>
       <c r="I46" s="1288" t="n"/>
       <c r="J46" s="1294">
-        <f>G46*H46</f>
+        <f>F46*IF(G46=0,1,G46)*H46</f>
         <v/>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       <c r="H47" s="1288" t="n"/>
       <c r="I47" s="1288" t="n"/>
       <c r="J47" s="1294">
-        <f>G47*H47</f>
+        <f>F47*IF(G47=0,1,G47)*H47</f>
         <v/>
       </c>
     </row>
@@ -11483,7 +11483,7 @@
       <c r="H48" s="1288" t="n"/>
       <c r="I48" s="1288" t="n"/>
       <c r="J48" s="1294">
-        <f>G48*H48</f>
+        <f>F48*IF(G48=0,1,G48)*H48</f>
         <v/>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       <c r="H49" s="1288" t="n"/>
       <c r="I49" s="1288" t="n"/>
       <c r="J49" s="1294">
-        <f>G49*H49</f>
+        <f>F49*IF(G49=0,1,G49)*H49</f>
         <v/>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       <c r="H50" s="1288" t="n"/>
       <c r="I50" s="1288" t="n"/>
       <c r="J50" s="1294">
-        <f>G50*H50</f>
+        <f>F50*IF(G50=0,1,G50)*H50</f>
         <v/>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       <c r="H51" s="1288" t="n"/>
       <c r="I51" s="1288" t="n"/>
       <c r="J51" s="1294">
-        <f>G51*H51</f>
+        <f>F51*IF(G51=0,1,G51)*H51</f>
         <v/>
       </c>
     </row>
@@ -11543,7 +11543,7 @@
       <c r="H52" s="1288" t="n"/>
       <c r="I52" s="1288" t="n"/>
       <c r="J52" s="1294">
-        <f>G52*H52</f>
+        <f>F52*IF(G52=0,1,G52)*H52</f>
         <v/>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       <c r="H53" s="1288" t="n"/>
       <c r="I53" s="1288" t="n"/>
       <c r="J53" s="1294">
-        <f>G53*H53</f>
+        <f>F53*IF(G53=0,1,G53)*H53</f>
         <v/>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
       <c r="H57" s="1288" t="n"/>
       <c r="I57" s="1288" t="n"/>
       <c r="J57" s="1294">
-        <f>G57*H57</f>
+        <f>F57*IF(G57=0,1,G57)*H57</f>
         <v/>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       <c r="H58" s="1288" t="n"/>
       <c r="I58" s="1288" t="n"/>
       <c r="J58" s="1294">
-        <f>G58*H58</f>
+        <f>F58*IF(G58=0,1,G58)*H58</f>
         <v/>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       <c r="H59" s="1288" t="n"/>
       <c r="I59" s="1288" t="n"/>
       <c r="J59" s="1294">
-        <f>G59*H59</f>
+        <f>F59*IF(G59=0,1,G59)*H59</f>
         <v/>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       <c r="H60" s="1288" t="n"/>
       <c r="I60" s="1288" t="n"/>
       <c r="J60" s="1294">
-        <f>G60*H60</f>
+        <f>F60*IF(G60=0,1,G60)*H60</f>
         <v/>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       <c r="H61" s="1288" t="n"/>
       <c r="I61" s="1288" t="n"/>
       <c r="J61" s="1294">
-        <f>G61*H61</f>
+        <f>F61*IF(G61=0,1,G61)*H61</f>
         <v/>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       <c r="H62" s="1288" t="n"/>
       <c r="I62" s="1288" t="n"/>
       <c r="J62" s="1294">
-        <f>G62*H62</f>
+        <f>F62*IF(G62=0,1,G62)*H62</f>
         <v/>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       <c r="H63" s="1288" t="n"/>
       <c r="I63" s="1288" t="n"/>
       <c r="J63" s="1294">
-        <f>G63*H63</f>
+        <f>F63*IF(G63=0,1,G63)*H63</f>
         <v/>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       <c r="H64" s="1288" t="n"/>
       <c r="I64" s="1288" t="n"/>
       <c r="J64" s="1294">
-        <f>G64*H64</f>
+        <f>F64*IF(G64=0,1,G64)*H64</f>
         <v/>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       <c r="H65" s="1288" t="n"/>
       <c r="I65" s="1288" t="n"/>
       <c r="J65" s="1294">
-        <f>G65*H65</f>
+        <f>F65*IF(G65=0,1,G65)*H65</f>
         <v/>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       <c r="H66" s="1288" t="n"/>
       <c r="I66" s="1288" t="n"/>
       <c r="J66" s="1294">
-        <f>G66*H66</f>
+        <f>F66*IF(G66=0,1,G66)*H66</f>
         <v/>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       <c r="H67" s="1288" t="n"/>
       <c r="I67" s="1288" t="n"/>
       <c r="J67" s="1294">
-        <f>G67*H67</f>
+        <f>F67*IF(G67=0,1,G67)*H67</f>
         <v/>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       <c r="H68" s="1288" t="n"/>
       <c r="I68" s="1288" t="n"/>
       <c r="J68" s="1294">
-        <f>G68*H68</f>
+        <f>F68*IF(G68=0,1,G68)*H68</f>
         <v/>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       <c r="H69" s="1288" t="n"/>
       <c r="I69" s="1288" t="n"/>
       <c r="J69" s="1294">
-        <f>G69*H69</f>
+        <f>F69*IF(G69=0,1,G69)*H69</f>
         <v/>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       <c r="H70" s="1288" t="n"/>
       <c r="I70" s="1288" t="n"/>
       <c r="J70" s="1294">
-        <f>G70*H70</f>
+        <f>F70*IF(G70=0,1,G70)*H70</f>
         <v/>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       <c r="H71" s="1288" t="n"/>
       <c r="I71" s="1288" t="n"/>
       <c r="J71" s="1294">
-        <f>G71*H71</f>
+        <f>F71*IF(G71=0,1,G71)*H71</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -10412,32 +10412,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1944750</colOff>
-      <row>8</row>
-      <rowOff>49500</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1944750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>49500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1764000"/>
@@ -10449,11 +10449,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10637,7 +10637,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W82"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -1563,34 +1563,34 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1944750</colOff>
-      <row>8</row>
-      <rowOff>49500</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Picture 1"/>
-        <cNvPicPr>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1944750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>49500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="0" cy="0"/>
@@ -1601,11 +1601,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1789,7 +1789,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X82"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -360,7 +360,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="67">
+  <borders count="68">
     <border>
       <left/>
       <right/>
@@ -870,17 +870,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1016,6 +1005,30 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1204,7 +1217,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1237,9 +1249,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1268,14 +1277,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1387,37 +1392,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1429,22 +1430,25 @@
     <xf numFmtId="0" fontId="25" fillId="11" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1453,16 +1457,28 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1475,17 +1491,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1794,31 +1811,31 @@
   <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
-    <col width="20.77734375" customWidth="1" style="66" min="1" max="1"/>
-    <col width="2.77734375" customWidth="1" style="66" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="66" min="3" max="3"/>
-    <col width="2.77734375" customWidth="1" style="66" min="4" max="4"/>
-    <col width="20.77734375" customWidth="1" style="66" min="5" max="5"/>
-    <col width="25.77734375" customWidth="1" style="66" min="6" max="6"/>
-    <col width="2.77734375" customWidth="1" style="66" min="7" max="7"/>
-    <col width="20.77734375" customWidth="1" style="66" min="8" max="8"/>
-    <col width="25.77734375" customWidth="1" style="66" min="9" max="9"/>
-    <col width="2.77734375" customWidth="1" style="66" min="10" max="10"/>
-    <col width="25.77734375" customWidth="1" style="66" min="11" max="11"/>
-    <col width="4.77734375" customWidth="1" style="66" min="15" max="15"/>
+    <col width="20.77734375" customWidth="1" style="62" min="1" max="1"/>
+    <col width="2.77734375" customWidth="1" style="62" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="62" min="3" max="3"/>
+    <col width="2.77734375" customWidth="1" style="62" min="4" max="4"/>
+    <col width="20.77734375" customWidth="1" style="62" min="5" max="5"/>
+    <col width="25.77734375" customWidth="1" style="62" min="6" max="6"/>
+    <col width="2.77734375" customWidth="1" style="62" min="7" max="7"/>
+    <col width="20.77734375" customWidth="1" style="62" min="8" max="8"/>
+    <col width="25.77734375" customWidth="1" style="62" min="9" max="9"/>
+    <col width="2.77734375" customWidth="1" style="62" min="10" max="10"/>
+    <col width="25.77734375" customWidth="1" style="62" min="11" max="11"/>
+    <col width="4.77734375" customWidth="1" style="62" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customFormat="1" customHeight="1" s="66">
+    <row r="1" ht="40.05" customFormat="1" customHeight="1" s="62">
       <c r="A1" s="2" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="n"/>
-      <c r="D1" s="65" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>ANÁLISIS DE PRECIOS UNITARIOS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="4.95" customFormat="1" customHeight="1" s="66">
+    <row r="2" ht="4.95" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="n"/>
@@ -1831,7 +1848,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="6" t="n"/>
     </row>
-    <row r="3" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="3" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="3" t="n"/>
@@ -1840,25 +1857,25 @@
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
-      <c r="I3" s="67" t="inlineStr">
+      <c r="I3" s="63" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="J3" s="139" t="n"/>
-      <c r="K3" s="140" t="n"/>
-    </row>
-    <row r="4" ht="15" customFormat="1" customHeight="1" s="66">
+      <c r="J3" s="138" t="n"/>
+      <c r="K3" s="139" t="n"/>
+    </row>
+    <row r="4" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="141" t="inlineStr">
+      <c r="E4" s="140" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="H4" s="142" t="n"/>
+      <c r="H4" s="141" t="n"/>
       <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Código</t>
@@ -1885,17 +1902,17 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="5" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="143" t="inlineStr">
+      <c r="E5" s="142" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="H5" s="142" t="n"/>
+      <c r="H5" s="141" t="n"/>
       <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Versión</t>
@@ -1908,7 +1925,7 @@
       <c r="L5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
     </row>
-    <row r="6" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="6" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="3" t="n"/>
@@ -1931,7 +1948,7 @@
       <c r="L6" s="11" t="n"/>
       <c r="N6" s="11" t="n"/>
     </row>
-    <row r="7" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="7" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="3" t="n"/>
@@ -1954,7 +1971,7 @@
       <c r="L7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
     </row>
-    <row r="8" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="8" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -1967,167 +1984,167 @@
       <c r="J8" s="20" t="n"/>
       <c r="K8" s="20" t="n"/>
     </row>
-    <row r="9" ht="25.05" customFormat="1" customHeight="1" s="66">
-      <c r="A9" s="71" t="n"/>
-    </row>
-    <row r="10" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A10" s="72" t="n"/>
-    </row>
-    <row r="11" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A11" s="73" t="inlineStr">
+    <row r="9" ht="25.05" customFormat="1" customHeight="1" s="62">
+      <c r="A9" s="67" t="n"/>
+    </row>
+    <row r="10" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A10" s="68" t="n"/>
+    </row>
+    <row r="11" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>IDENTIFICACIÓN DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customFormat="1" customHeight="1" s="66">
+    <row r="12" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="74" t="n"/>
-      <c r="D12" s="144" t="n"/>
-      <c r="E12" s="144" t="n"/>
-      <c r="F12" s="144" t="n"/>
-      <c r="G12" s="144" t="n"/>
-      <c r="H12" s="144" t="n"/>
-      <c r="I12" s="144" t="n"/>
-      <c r="J12" s="144" t="n"/>
-      <c r="K12" s="145" t="n"/>
-    </row>
-    <row r="13" ht="15" customFormat="1" customHeight="1" s="66">
+      <c r="C12" s="70" t="n"/>
+      <c r="D12" s="143" t="n"/>
+      <c r="E12" s="143" t="n"/>
+      <c r="F12" s="143" t="n"/>
+      <c r="G12" s="143" t="n"/>
+      <c r="H12" s="143" t="n"/>
+      <c r="I12" s="143" t="n"/>
+      <c r="J12" s="143" t="n"/>
+      <c r="K12" s="144" t="n"/>
+    </row>
+    <row r="13" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A13" s="21" t="inlineStr">
         <is>
           <t>No de Contrato</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="77" t="n"/>
-      <c r="D13" s="144" t="n"/>
-      <c r="E13" s="144" t="n"/>
+      <c r="C13" s="73" t="n"/>
+      <c r="D13" s="143" t="n"/>
+      <c r="E13" s="143" t="n"/>
       <c r="F13" s="24" t="n"/>
       <c r="G13" s="24" t="n"/>
       <c r="H13" s="24" t="n"/>
-      <c r="I13" s="78" t="inlineStr">
+      <c r="I13" s="74" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="J13" s="145" t="n"/>
-      <c r="K13" s="76" t="n"/>
-    </row>
-    <row r="14" ht="15" customFormat="1" customHeight="1" s="66">
+      <c r="J13" s="144" t="n"/>
+      <c r="K13" s="72" t="n"/>
+    </row>
+    <row r="14" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Contratista</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="79" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="D14" s="144" t="n"/>
-      <c r="E14" s="144" t="n"/>
+      <c r="D14" s="143" t="n"/>
+      <c r="E14" s="143" t="n"/>
       <c r="F14" s="24" t="n"/>
       <c r="G14" s="24" t="n"/>
       <c r="H14" s="24" t="n"/>
-      <c r="I14" s="78" t="inlineStr">
+      <c r="I14" s="74" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="J14" s="145" t="n"/>
-      <c r="K14" s="76" t="n"/>
-    </row>
-    <row r="15" ht="15" customFormat="1" customHeight="1" s="66" thickBot="1">
-      <c r="A15" s="80" t="n"/>
-      <c r="B15" s="146" t="n"/>
-      <c r="C15" s="146" t="n"/>
-      <c r="D15" s="146" t="n"/>
-      <c r="E15" s="146" t="n"/>
-      <c r="F15" s="146" t="n"/>
-      <c r="G15" s="146" t="n"/>
-      <c r="H15" s="146" t="n"/>
-      <c r="I15" s="146" t="n"/>
-      <c r="J15" s="146" t="n"/>
-      <c r="K15" s="146" t="n"/>
-    </row>
-    <row r="16" ht="19.95" customFormat="1" customHeight="1" s="66" thickBot="1" thickTop="1">
-      <c r="A16" s="82" t="inlineStr">
+      <c r="J14" s="144" t="n"/>
+      <c r="K14" s="72" t="n"/>
+    </row>
+    <row r="15" ht="15" customFormat="1" customHeight="1" s="62" thickBot="1">
+      <c r="A15" s="76" t="n"/>
+      <c r="B15" s="145" t="n"/>
+      <c r="C15" s="145" t="n"/>
+      <c r="D15" s="145" t="n"/>
+      <c r="E15" s="145" t="n"/>
+      <c r="F15" s="145" t="n"/>
+      <c r="G15" s="145" t="n"/>
+      <c r="H15" s="145" t="n"/>
+      <c r="I15" s="145" t="n"/>
+      <c r="J15" s="145" t="n"/>
+      <c r="K15" s="145" t="n"/>
+    </row>
+    <row r="16" ht="19.95" customFormat="1" customHeight="1" s="62" thickBot="1" thickTop="1">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
       <c r="B16" s="26" t="n"/>
-      <c r="C16" s="82" t="inlineStr">
+      <c r="C16" s="78" t="inlineStr">
         <is>
           <t>CUADRILLA</t>
         </is>
       </c>
-      <c r="D16" s="84" t="n"/>
-      <c r="E16" s="82" t="inlineStr">
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="78" t="inlineStr">
         <is>
           <t>JORNADA</t>
         </is>
       </c>
-      <c r="F16" s="147" t="n"/>
-      <c r="G16" s="122" t="n"/>
-      <c r="H16" s="82" t="inlineStr">
+      <c r="F16" s="146" t="n"/>
+      <c r="G16" s="116" t="n"/>
+      <c r="H16" s="78" t="inlineStr">
         <is>
           <t>RENDIMIENTO</t>
         </is>
       </c>
-      <c r="I16" s="147" t="n"/>
-      <c r="J16" s="88" t="n"/>
-      <c r="K16" s="82" t="inlineStr">
+      <c r="I16" s="146" t="n"/>
+      <c r="J16" s="84" t="n"/>
+      <c r="K16" s="78" t="inlineStr">
         <is>
           <t>CONSUMO M.O.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25.05" customFormat="1" customHeight="1" s="66" thickBot="1" thickTop="1">
-      <c r="A17" s="86">
+    <row r="17" ht="25.05" customFormat="1" customHeight="1" s="62" thickBot="1" thickTop="1">
+      <c r="A17" s="82">
         <f>Q4</f>
         <v/>
       </c>
       <c r="B17" s="26" t="n"/>
-      <c r="C17" s="86">
+      <c r="C17" s="82">
         <f>T4</f>
         <v/>
       </c>
-      <c r="D17" s="148" t="n"/>
-      <c r="E17" s="86">
+      <c r="D17" s="147" t="n"/>
+      <c r="E17" s="82">
         <f>V4</f>
         <v/>
       </c>
-      <c r="F17" s="149" t="n"/>
-      <c r="G17" s="123" t="n"/>
-      <c r="H17" s="86">
+      <c r="F17" s="148" t="n"/>
+      <c r="G17" s="117" t="n"/>
+      <c r="H17" s="82">
         <f>A1&amp;" "&amp;A17&amp;"/jornada"</f>
         <v/>
       </c>
-      <c r="I17" s="149" t="n"/>
-      <c r="K17" s="128">
+      <c r="I17" s="148" t="n"/>
+      <c r="K17" s="122">
         <f>IFERROR(1/W4,0)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="28" thickTop="1">
-      <c r="A18" s="89" t="n"/>
-      <c r="B18" s="150" t="n"/>
-      <c r="C18" s="150" t="n"/>
-      <c r="D18" s="150" t="n"/>
-      <c r="E18" s="150" t="n"/>
-      <c r="F18" s="150" t="n"/>
-      <c r="G18" s="150" t="n"/>
-      <c r="H18" s="150" t="n"/>
-      <c r="I18" s="150" t="n"/>
-      <c r="J18" s="150" t="n"/>
-      <c r="K18" s="150" t="n"/>
+      <c r="A18" s="85" t="n"/>
+      <c r="B18" s="149" t="n"/>
+      <c r="C18" s="149" t="n"/>
+      <c r="D18" s="149" t="n"/>
+      <c r="E18" s="149" t="n"/>
+      <c r="F18" s="149" t="n"/>
+      <c r="G18" s="149" t="n"/>
+      <c r="H18" s="149" t="n"/>
+      <c r="I18" s="149" t="n"/>
+      <c r="J18" s="149" t="n"/>
+      <c r="K18" s="149" t="n"/>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A19" s="30" t="inlineStr">
@@ -2136,29 +2153,29 @@
         </is>
       </c>
       <c r="B19" s="31" t="n"/>
-      <c r="C19" s="91" t="inlineStr">
+      <c r="C19" s="87" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="D19" s="151" t="n"/>
-      <c r="E19" s="93" t="n"/>
-      <c r="F19" s="152" t="n"/>
-      <c r="G19" s="152" t="n"/>
-      <c r="H19" s="152" t="n"/>
-      <c r="I19" s="152" t="n"/>
-      <c r="J19" s="152" t="n"/>
-      <c r="K19" s="153" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="D19" s="150" t="n"/>
+      <c r="E19" s="89" t="n"/>
+      <c r="F19" s="151" t="n"/>
+      <c r="G19" s="151" t="n"/>
+      <c r="H19" s="151" t="n"/>
+      <c r="I19" s="151" t="n"/>
+      <c r="J19" s="151" t="n"/>
+      <c r="K19" s="152" t="n"/>
+    </row>
+    <row r="20" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A20" s="124" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B20" s="154" t="n"/>
-      <c r="C20" s="154" t="n"/>
-      <c r="D20" s="154" t="n"/>
+      <c r="B20" s="153" t="n"/>
+      <c r="C20" s="153" t="n"/>
+      <c r="D20" s="153" t="n"/>
       <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Und</t>
@@ -2188,569 +2205,569 @@
       </c>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="34">
-      <c r="A21" s="96" t="n"/>
-      <c r="B21" s="155" t="n"/>
-      <c r="C21" s="155" t="n"/>
-      <c r="D21" s="155" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="37" t="n"/>
-      <c r="G21" s="37" t="n"/>
-      <c r="H21" s="37" t="n"/>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="38" t="n"/>
-      <c r="K21" s="39">
+      <c r="A21" s="92" t="n"/>
+      <c r="B21" s="154" t="n"/>
+      <c r="C21" s="154" t="n"/>
+      <c r="D21" s="154" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="37" t="n"/>
+      <c r="J21" s="37" t="n"/>
+      <c r="K21" s="38">
         <f>F21*IF(H21=0,1,H21)*I21</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A22" s="96" t="n"/>
-      <c r="B22" s="155" t="n"/>
-      <c r="C22" s="155" t="n"/>
-      <c r="D22" s="155" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="37" t="n"/>
-      <c r="G22" s="37" t="n"/>
-      <c r="H22" s="37" t="n"/>
-      <c r="I22" s="38" t="n"/>
-      <c r="J22" s="38" t="n"/>
-      <c r="K22" s="39">
+    <row r="22" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A22" s="92" t="n"/>
+      <c r="B22" s="154" t="n"/>
+      <c r="C22" s="154" t="n"/>
+      <c r="D22" s="154" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="37" t="n"/>
+      <c r="K22" s="38">
         <f>F22*IF(H22=0,1,H22)*I22</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A23" s="96" t="n"/>
-      <c r="B23" s="155" t="n"/>
-      <c r="C23" s="155" t="n"/>
-      <c r="D23" s="155" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="37" t="n"/>
-      <c r="G23" s="37" t="n"/>
-      <c r="H23" s="37" t="n"/>
-      <c r="I23" s="38" t="n"/>
-      <c r="J23" s="38" t="n"/>
-      <c r="K23" s="39">
+    <row r="23" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A23" s="92" t="n"/>
+      <c r="B23" s="154" t="n"/>
+      <c r="C23" s="154" t="n"/>
+      <c r="D23" s="154" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="37" t="n"/>
+      <c r="J23" s="37" t="n"/>
+      <c r="K23" s="38">
         <f>F23*IF(H23=0,1,H23)*I23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A24" s="96" t="n"/>
-      <c r="B24" s="155" t="n"/>
-      <c r="C24" s="155" t="n"/>
-      <c r="D24" s="155" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
-      <c r="H24" s="37" t="n"/>
-      <c r="I24" s="38" t="n"/>
-      <c r="J24" s="38" t="n"/>
-      <c r="K24" s="39">
+    <row r="24" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A24" s="92" t="n"/>
+      <c r="B24" s="154" t="n"/>
+      <c r="C24" s="154" t="n"/>
+      <c r="D24" s="154" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="37" t="n"/>
+      <c r="J24" s="37" t="n"/>
+      <c r="K24" s="38">
         <f>F24*IF(H24=0,1,H24)*I24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A25" s="96" t="n"/>
-      <c r="B25" s="155" t="n"/>
-      <c r="C25" s="155" t="n"/>
-      <c r="D25" s="155" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="37" t="n"/>
-      <c r="G25" s="37" t="n"/>
-      <c r="H25" s="37" t="n"/>
-      <c r="I25" s="38" t="n"/>
-      <c r="J25" s="38" t="n"/>
-      <c r="K25" s="39">
+    <row r="25" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A25" s="92" t="n"/>
+      <c r="B25" s="154" t="n"/>
+      <c r="C25" s="154" t="n"/>
+      <c r="D25" s="154" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="37" t="n"/>
+      <c r="J25" s="37" t="n"/>
+      <c r="K25" s="38">
         <f>F25*IF(H25=0,1,H25)*I25</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A26" s="96" t="n"/>
-      <c r="B26" s="155" t="n"/>
-      <c r="C26" s="155" t="n"/>
-      <c r="D26" s="155" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="37" t="n"/>
-      <c r="H26" s="37" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="40" t="n"/>
-      <c r="K26" s="39">
+    <row r="26" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A26" s="92" t="n"/>
+      <c r="B26" s="154" t="n"/>
+      <c r="C26" s="154" t="n"/>
+      <c r="D26" s="154" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="39" t="n"/>
+      <c r="K26" s="38">
         <f>F26*IF(H26=0,1,H26)*I26</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A27" s="96" t="n"/>
-      <c r="B27" s="155" t="n"/>
-      <c r="C27" s="155" t="n"/>
-      <c r="D27" s="155" t="n"/>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="37" t="n"/>
-      <c r="H27" s="37" t="n"/>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="38" t="n"/>
-      <c r="K27" s="39">
+    <row r="27" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A27" s="92" t="n"/>
+      <c r="B27" s="154" t="n"/>
+      <c r="C27" s="154" t="n"/>
+      <c r="D27" s="154" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="37" t="n"/>
+      <c r="J27" s="37" t="n"/>
+      <c r="K27" s="38">
         <f>F27*IF(H27=0,1,H27)*I27</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15.6" customHeight="1">
-      <c r="A28" s="96" t="n"/>
-      <c r="B28" s="155" t="n"/>
-      <c r="C28" s="155" t="n"/>
-      <c r="D28" s="155" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
-      <c r="H28" s="37" t="n"/>
-      <c r="I28" s="38" t="n"/>
-      <c r="J28" s="38" t="n"/>
-      <c r="K28" s="39">
+      <c r="A28" s="92" t="n"/>
+      <c r="B28" s="154" t="n"/>
+      <c r="C28" s="154" t="n"/>
+      <c r="D28" s="154" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="37" t="n"/>
+      <c r="K28" s="38">
         <f>F28*IF(H28=0,1,H28)*I28</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15.6" customHeight="1">
-      <c r="A29" s="96" t="n"/>
-      <c r="B29" s="155" t="n"/>
-      <c r="C29" s="155" t="n"/>
-      <c r="D29" s="155" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="37" t="n"/>
-      <c r="G29" s="37" t="n"/>
-      <c r="H29" s="37" t="n"/>
-      <c r="I29" s="38" t="n"/>
-      <c r="J29" s="38" t="n"/>
-      <c r="K29" s="39">
+      <c r="A29" s="92" t="n"/>
+      <c r="B29" s="154" t="n"/>
+      <c r="C29" s="154" t="n"/>
+      <c r="D29" s="154" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="37" t="n"/>
+      <c r="J29" s="37" t="n"/>
+      <c r="K29" s="38">
         <f>F29*IF(H29=0,1,H29)*I29</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1">
-      <c r="A30" s="96" t="n"/>
-      <c r="B30" s="155" t="n"/>
-      <c r="C30" s="155" t="n"/>
-      <c r="D30" s="155" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="37" t="n"/>
-      <c r="H30" s="37" t="n"/>
-      <c r="I30" s="38" t="n"/>
-      <c r="J30" s="38" t="n"/>
-      <c r="K30" s="39">
+      <c r="A30" s="92" t="n"/>
+      <c r="B30" s="154" t="n"/>
+      <c r="C30" s="154" t="n"/>
+      <c r="D30" s="154" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="37" t="n"/>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="38">
         <f>F30*IF(H30=0,1,H30)*I30</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15.6" customHeight="1">
-      <c r="A31" s="96" t="n"/>
-      <c r="B31" s="155" t="n"/>
-      <c r="C31" s="155" t="n"/>
-      <c r="D31" s="155" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="37" t="n"/>
-      <c r="I31" s="38" t="n"/>
-      <c r="J31" s="38" t="n"/>
-      <c r="K31" s="39">
+      <c r="A31" s="92" t="n"/>
+      <c r="B31" s="154" t="n"/>
+      <c r="C31" s="154" t="n"/>
+      <c r="D31" s="154" t="n"/>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="37" t="n"/>
+      <c r="J31" s="37" t="n"/>
+      <c r="K31" s="38">
         <f>F31*IF(H31=0,1,H31)*I31</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15.6" customHeight="1">
-      <c r="A32" s="96" t="n"/>
-      <c r="B32" s="155" t="n"/>
-      <c r="C32" s="155" t="n"/>
-      <c r="D32" s="155" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
-      <c r="H32" s="37" t="n"/>
-      <c r="I32" s="38" t="n"/>
-      <c r="J32" s="38" t="n"/>
-      <c r="K32" s="39">
+      <c r="A32" s="92" t="n"/>
+      <c r="B32" s="154" t="n"/>
+      <c r="C32" s="154" t="n"/>
+      <c r="D32" s="154" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="37" t="n"/>
+      <c r="J32" s="37" t="n"/>
+      <c r="K32" s="38">
         <f>F32*IF(H32=0,1,H32)*I32</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15.6" customHeight="1">
-      <c r="A33" s="96" t="n"/>
-      <c r="B33" s="155" t="n"/>
-      <c r="C33" s="155" t="n"/>
-      <c r="D33" s="155" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="37" t="n"/>
-      <c r="G33" s="37" t="n"/>
-      <c r="H33" s="37" t="n"/>
-      <c r="I33" s="38" t="n"/>
-      <c r="J33" s="38" t="n"/>
-      <c r="K33" s="39">
+      <c r="A33" s="92" t="n"/>
+      <c r="B33" s="154" t="n"/>
+      <c r="C33" s="154" t="n"/>
+      <c r="D33" s="154" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="36" t="n"/>
+      <c r="I33" s="37" t="n"/>
+      <c r="J33" s="37" t="n"/>
+      <c r="K33" s="38">
         <f>F33*IF(H33=0,1,H33)*I33</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15.6" customHeight="1">
-      <c r="A34" s="96" t="n"/>
-      <c r="B34" s="155" t="n"/>
-      <c r="C34" s="155" t="n"/>
-      <c r="D34" s="155" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="37" t="n"/>
-      <c r="H34" s="37" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="38" t="n"/>
-      <c r="K34" s="39">
+      <c r="A34" s="92" t="n"/>
+      <c r="B34" s="154" t="n"/>
+      <c r="C34" s="154" t="n"/>
+      <c r="D34" s="154" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="36" t="n"/>
+      <c r="G34" s="36" t="n"/>
+      <c r="H34" s="36" t="n"/>
+      <c r="I34" s="37" t="n"/>
+      <c r="J34" s="37" t="n"/>
+      <c r="K34" s="38">
         <f>F34*IF(H34=0,1,H34)*I34</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15.6" customHeight="1">
-      <c r="A35" s="96" t="n"/>
-      <c r="B35" s="155" t="n"/>
-      <c r="C35" s="155" t="n"/>
-      <c r="D35" s="155" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="37" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="37" t="n"/>
-      <c r="I35" s="38" t="n"/>
-      <c r="J35" s="38" t="n"/>
-      <c r="K35" s="39">
+      <c r="A35" s="92" t="n"/>
+      <c r="B35" s="154" t="n"/>
+      <c r="C35" s="154" t="n"/>
+      <c r="D35" s="154" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="37" t="n"/>
+      <c r="J35" s="37" t="n"/>
+      <c r="K35" s="38">
         <f>F35*IF(H35=0,1,H35)*I35</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A36" s="98" t="n"/>
-      <c r="B36" s="156" t="n"/>
-      <c r="C36" s="156" t="n"/>
-      <c r="D36" s="156" t="n"/>
-      <c r="E36" s="100" t="inlineStr">
+    <row r="36" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A36" s="94" t="n"/>
+      <c r="B36" s="155" t="n"/>
+      <c r="C36" s="155" t="n"/>
+      <c r="D36" s="155" t="n"/>
+      <c r="E36" s="96" t="inlineStr">
         <is>
           <t>SUBTOTAL MATERIALES</t>
         </is>
       </c>
-      <c r="F36" s="156" t="n"/>
-      <c r="G36" s="156" t="n"/>
-      <c r="H36" s="156" t="n"/>
-      <c r="I36" s="156" t="n"/>
-      <c r="J36" s="156" t="n"/>
-      <c r="K36" s="41">
+      <c r="F36" s="155" t="n"/>
+      <c r="G36" s="155" t="n"/>
+      <c r="H36" s="155" t="n"/>
+      <c r="I36" s="155" t="n"/>
+      <c r="J36" s="155" t="n"/>
+      <c r="K36" s="40">
         <f>SUM(K21:K35)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A37" s="42" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B37" s="43" t="n"/>
-      <c r="C37" s="44" t="inlineStr">
+      <c r="B37" s="42" t="n"/>
+      <c r="C37" s="137" t="inlineStr">
         <is>
           <t>MANO DE OBRA</t>
         </is>
       </c>
-      <c r="D37" s="44" t="n"/>
-      <c r="E37" s="101" t="n"/>
-      <c r="F37" s="157" t="n"/>
-      <c r="G37" s="157" t="n"/>
-      <c r="H37" s="157" t="n"/>
-      <c r="I37" s="157" t="n"/>
-      <c r="J37" s="157" t="n"/>
-      <c r="K37" s="158" t="n"/>
-    </row>
-    <row r="38" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A38" s="133" t="inlineStr">
+      <c r="D37" s="43" t="n"/>
+      <c r="E37" s="97" t="n"/>
+      <c r="F37" s="156" t="n"/>
+      <c r="G37" s="156" t="n"/>
+      <c r="H37" s="156" t="n"/>
+      <c r="I37" s="156" t="n"/>
+      <c r="J37" s="156" t="n"/>
+      <c r="K37" s="157" t="n"/>
+    </row>
+    <row r="38" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A38" s="127" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B38" s="155" t="n"/>
-      <c r="C38" s="155" t="n"/>
-      <c r="D38" s="155" t="n"/>
-      <c r="E38" s="132" t="inlineStr">
+      <c r="B38" s="154" t="n"/>
+      <c r="C38" s="154" t="n"/>
+      <c r="D38" s="154" t="n"/>
+      <c r="E38" s="126" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F38" s="132" t="inlineStr">
+      <c r="F38" s="126" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G38" s="132" t="n"/>
-      <c r="H38" s="132" t="inlineStr">
+      <c r="G38" s="126" t="n"/>
+      <c r="H38" s="126" t="inlineStr">
         <is>
           <t>Rendimiento</t>
         </is>
       </c>
-      <c r="I38" s="132" t="inlineStr">
+      <c r="I38" s="126" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="J38" s="132" t="n"/>
-      <c r="K38" s="46" t="inlineStr">
+      <c r="J38" s="126" t="n"/>
+      <c r="K38" s="45" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A39" s="104" t="n"/>
-      <c r="B39" s="155" t="n"/>
-      <c r="C39" s="155" t="n"/>
-      <c r="D39" s="155" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="48" t="n"/>
-      <c r="G39" s="48" t="n"/>
-      <c r="H39" s="48" t="n"/>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="49">
+    <row r="39" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A39" s="100" t="n"/>
+      <c r="B39" s="154" t="n"/>
+      <c r="C39" s="154" t="n"/>
+      <c r="D39" s="154" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="46" t="n"/>
+      <c r="G39" s="46" t="n"/>
+      <c r="H39" s="46" t="n"/>
+      <c r="I39" s="37" t="n"/>
+      <c r="J39" s="37" t="n"/>
+      <c r="K39" s="47">
         <f>F39*IF(H39=0,1,H39)*I39</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A40" s="104" t="n"/>
-      <c r="B40" s="155" t="n"/>
-      <c r="C40" s="155" t="n"/>
-      <c r="D40" s="155" t="n"/>
-      <c r="E40" s="36" t="n"/>
-      <c r="F40" s="48" t="n"/>
-      <c r="G40" s="48" t="n"/>
-      <c r="H40" s="48" t="n"/>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="38" t="n"/>
-      <c r="K40" s="49">
+    <row r="40" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A40" s="100" t="n"/>
+      <c r="B40" s="154" t="n"/>
+      <c r="C40" s="154" t="n"/>
+      <c r="D40" s="154" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="46" t="n"/>
+      <c r="G40" s="46" t="n"/>
+      <c r="H40" s="46" t="n"/>
+      <c r="I40" s="37" t="n"/>
+      <c r="J40" s="37" t="n"/>
+      <c r="K40" s="47">
         <f>F40*IF(H40=0,1,H40)*I40</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A41" s="104" t="n"/>
-      <c r="B41" s="155" t="n"/>
-      <c r="C41" s="155" t="n"/>
-      <c r="D41" s="155" t="n"/>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="48" t="n"/>
-      <c r="G41" s="48" t="n"/>
-      <c r="H41" s="48" t="n"/>
-      <c r="I41" s="38" t="n"/>
-      <c r="J41" s="38" t="n"/>
-      <c r="K41" s="49">
+    <row r="41" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A41" s="100" t="n"/>
+      <c r="B41" s="154" t="n"/>
+      <c r="C41" s="154" t="n"/>
+      <c r="D41" s="154" t="n"/>
+      <c r="E41" s="35" t="n"/>
+      <c r="F41" s="46" t="n"/>
+      <c r="G41" s="46" t="n"/>
+      <c r="H41" s="46" t="n"/>
+      <c r="I41" s="37" t="n"/>
+      <c r="J41" s="37" t="n"/>
+      <c r="K41" s="47">
         <f>F41*IF(H41=0,1,H41)*I41</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A42" s="104" t="n"/>
-      <c r="B42" s="155" t="n"/>
-      <c r="C42" s="155" t="n"/>
-      <c r="D42" s="155" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="48" t="n"/>
-      <c r="G42" s="48" t="n"/>
-      <c r="H42" s="48" t="n"/>
-      <c r="I42" s="38" t="n"/>
-      <c r="J42" s="38" t="n"/>
-      <c r="K42" s="49">
+    <row r="42" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A42" s="100" t="n"/>
+      <c r="B42" s="154" t="n"/>
+      <c r="C42" s="154" t="n"/>
+      <c r="D42" s="154" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="46" t="n"/>
+      <c r="G42" s="46" t="n"/>
+      <c r="H42" s="46" t="n"/>
+      <c r="I42" s="37" t="n"/>
+      <c r="J42" s="37" t="n"/>
+      <c r="K42" s="47">
         <f>F42*IF(H42=0,1,H42)*I42</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A43" s="104" t="n"/>
-      <c r="B43" s="155" t="n"/>
-      <c r="C43" s="155" t="n"/>
-      <c r="D43" s="155" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="48" t="n"/>
-      <c r="G43" s="48" t="n"/>
-      <c r="H43" s="48" t="n"/>
-      <c r="I43" s="38" t="n"/>
-      <c r="J43" s="38" t="n"/>
-      <c r="K43" s="49">
+    <row r="43" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A43" s="100" t="n"/>
+      <c r="B43" s="154" t="n"/>
+      <c r="C43" s="154" t="n"/>
+      <c r="D43" s="154" t="n"/>
+      <c r="E43" s="35" t="n"/>
+      <c r="F43" s="46" t="n"/>
+      <c r="G43" s="46" t="n"/>
+      <c r="H43" s="46" t="n"/>
+      <c r="I43" s="37" t="n"/>
+      <c r="J43" s="37" t="n"/>
+      <c r="K43" s="47">
         <f>F43*IF(H43=0,1,H43)*I43</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A44" s="104" t="n"/>
-      <c r="B44" s="155" t="n"/>
-      <c r="C44" s="155" t="n"/>
-      <c r="D44" s="155" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="48" t="n"/>
-      <c r="G44" s="48" t="n"/>
-      <c r="H44" s="48" t="n"/>
-      <c r="I44" s="40" t="n"/>
-      <c r="J44" s="40" t="n"/>
-      <c r="K44" s="49">
+    <row r="44" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A44" s="100" t="n"/>
+      <c r="B44" s="154" t="n"/>
+      <c r="C44" s="154" t="n"/>
+      <c r="D44" s="154" t="n"/>
+      <c r="E44" s="35" t="n"/>
+      <c r="F44" s="46" t="n"/>
+      <c r="G44" s="46" t="n"/>
+      <c r="H44" s="46" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="47">
         <f>F44*IF(H44=0,1,H44)*I44</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A45" s="104" t="n"/>
-      <c r="B45" s="97" t="n"/>
-      <c r="C45" s="97" t="n"/>
-      <c r="D45" s="97" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="48" t="n"/>
-      <c r="G45" s="48" t="n"/>
-      <c r="H45" s="48" t="n"/>
-      <c r="I45" s="38" t="n"/>
-      <c r="J45" s="38" t="n"/>
-      <c r="K45" s="49">
+    <row r="45" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A45" s="100" t="n"/>
+      <c r="B45" s="154" t="n"/>
+      <c r="C45" s="154" t="n"/>
+      <c r="D45" s="154" t="n"/>
+      <c r="E45" s="35" t="n"/>
+      <c r="F45" s="46" t="n"/>
+      <c r="G45" s="46" t="n"/>
+      <c r="H45" s="46" t="n"/>
+      <c r="I45" s="37" t="n"/>
+      <c r="J45" s="37" t="n"/>
+      <c r="K45" s="47">
         <f>F45*IF(H45=0,1,H45)*I45</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15.6" customHeight="1">
-      <c r="A46" s="104" t="n"/>
-      <c r="B46" s="97" t="n"/>
-      <c r="C46" s="97" t="n"/>
-      <c r="D46" s="97" t="n"/>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="48" t="n"/>
-      <c r="G46" s="48" t="n"/>
-      <c r="H46" s="48" t="n"/>
-      <c r="I46" s="38" t="n"/>
-      <c r="J46" s="38" t="n"/>
-      <c r="K46" s="49">
+      <c r="A46" s="100" t="n"/>
+      <c r="B46" s="154" t="n"/>
+      <c r="C46" s="154" t="n"/>
+      <c r="D46" s="154" t="n"/>
+      <c r="E46" s="35" t="n"/>
+      <c r="F46" s="46" t="n"/>
+      <c r="G46" s="46" t="n"/>
+      <c r="H46" s="46" t="n"/>
+      <c r="I46" s="37" t="n"/>
+      <c r="J46" s="37" t="n"/>
+      <c r="K46" s="47">
         <f>F46*IF(H46=0,1,H46)*I46</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15.6" customHeight="1">
-      <c r="A47" s="104" t="n"/>
-      <c r="B47" s="97" t="n"/>
-      <c r="C47" s="97" t="n"/>
-      <c r="D47" s="97" t="n"/>
-      <c r="E47" s="36" t="n"/>
-      <c r="F47" s="48" t="n"/>
-      <c r="G47" s="48" t="n"/>
-      <c r="H47" s="48" t="n"/>
-      <c r="I47" s="38" t="n"/>
-      <c r="J47" s="38" t="n"/>
-      <c r="K47" s="49">
+      <c r="A47" s="100" t="n"/>
+      <c r="B47" s="154" t="n"/>
+      <c r="C47" s="154" t="n"/>
+      <c r="D47" s="154" t="n"/>
+      <c r="E47" s="35" t="n"/>
+      <c r="F47" s="46" t="n"/>
+      <c r="G47" s="46" t="n"/>
+      <c r="H47" s="46" t="n"/>
+      <c r="I47" s="37" t="n"/>
+      <c r="J47" s="37" t="n"/>
+      <c r="K47" s="47">
         <f>F47*IF(H47=0,1,H47)*I47</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15.6" customHeight="1">
-      <c r="A48" s="104" t="n"/>
-      <c r="B48" s="97" t="n"/>
-      <c r="C48" s="97" t="n"/>
-      <c r="D48" s="97" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="48" t="n"/>
-      <c r="H48" s="48" t="n"/>
-      <c r="I48" s="38" t="n"/>
-      <c r="J48" s="38" t="n"/>
-      <c r="K48" s="49">
+      <c r="A48" s="100" t="n"/>
+      <c r="B48" s="154" t="n"/>
+      <c r="C48" s="154" t="n"/>
+      <c r="D48" s="154" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="46" t="n"/>
+      <c r="G48" s="46" t="n"/>
+      <c r="H48" s="46" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
+      <c r="K48" s="47">
         <f>F48*IF(H48=0,1,H48)*I48</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15.6" customHeight="1">
-      <c r="A49" s="104" t="n"/>
-      <c r="B49" s="97" t="n"/>
-      <c r="C49" s="97" t="n"/>
-      <c r="D49" s="97" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="48" t="n"/>
-      <c r="H49" s="48" t="n"/>
-      <c r="I49" s="38" t="n"/>
-      <c r="J49" s="38" t="n"/>
-      <c r="K49" s="49">
+      <c r="A49" s="100" t="n"/>
+      <c r="B49" s="154" t="n"/>
+      <c r="C49" s="154" t="n"/>
+      <c r="D49" s="154" t="n"/>
+      <c r="E49" s="35" t="n"/>
+      <c r="F49" s="46" t="n"/>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="46" t="n"/>
+      <c r="I49" s="37" t="n"/>
+      <c r="J49" s="37" t="n"/>
+      <c r="K49" s="47">
         <f>F49*IF(H49=0,1,H49)*I49</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15.6" customHeight="1">
-      <c r="A50" s="104" t="n"/>
-      <c r="B50" s="97" t="n"/>
-      <c r="C50" s="97" t="n"/>
-      <c r="D50" s="97" t="n"/>
-      <c r="E50" s="36" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="48" t="n"/>
-      <c r="H50" s="48" t="n"/>
-      <c r="I50" s="38" t="n"/>
-      <c r="J50" s="38" t="n"/>
-      <c r="K50" s="49">
+      <c r="A50" s="100" t="n"/>
+      <c r="B50" s="154" t="n"/>
+      <c r="C50" s="154" t="n"/>
+      <c r="D50" s="154" t="n"/>
+      <c r="E50" s="35" t="n"/>
+      <c r="F50" s="46" t="n"/>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="46" t="n"/>
+      <c r="I50" s="37" t="n"/>
+      <c r="J50" s="37" t="n"/>
+      <c r="K50" s="47">
         <f>F50*IF(H50=0,1,H50)*I50</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15.6" customHeight="1">
-      <c r="A51" s="104" t="n"/>
-      <c r="B51" s="97" t="n"/>
-      <c r="C51" s="97" t="n"/>
-      <c r="D51" s="97" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="48" t="n"/>
-      <c r="H51" s="48" t="n"/>
-      <c r="I51" s="38" t="n"/>
-      <c r="J51" s="38" t="n"/>
-      <c r="K51" s="49">
+      <c r="A51" s="100" t="n"/>
+      <c r="B51" s="154" t="n"/>
+      <c r="C51" s="154" t="n"/>
+      <c r="D51" s="154" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="46" t="n"/>
+      <c r="G51" s="46" t="n"/>
+      <c r="H51" s="46" t="n"/>
+      <c r="I51" s="37" t="n"/>
+      <c r="J51" s="37" t="n"/>
+      <c r="K51" s="47">
         <f>F51*IF(H51=0,1,H51)*I51</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15.6" customHeight="1">
-      <c r="A52" s="104" t="n"/>
-      <c r="B52" s="97" t="n"/>
-      <c r="C52" s="97" t="n"/>
-      <c r="D52" s="97" t="n"/>
-      <c r="E52" s="36" t="n"/>
-      <c r="F52" s="48" t="n"/>
-      <c r="G52" s="48" t="n"/>
-      <c r="H52" s="48" t="n"/>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="38" t="n"/>
-      <c r="K52" s="49">
+      <c r="A52" s="100" t="n"/>
+      <c r="B52" s="154" t="n"/>
+      <c r="C52" s="154" t="n"/>
+      <c r="D52" s="154" t="n"/>
+      <c r="E52" s="35" t="n"/>
+      <c r="F52" s="46" t="n"/>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="46" t="n"/>
+      <c r="I52" s="37" t="n"/>
+      <c r="J52" s="37" t="n"/>
+      <c r="K52" s="47">
         <f>F52*IF(H52=0,1,H52)*I52</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15.6" customHeight="1">
-      <c r="A53" s="104" t="n"/>
-      <c r="B53" s="97" t="n"/>
-      <c r="C53" s="97" t="n"/>
-      <c r="D53" s="97" t="n"/>
-      <c r="E53" s="36" t="n"/>
-      <c r="F53" s="48" t="n"/>
-      <c r="G53" s="48" t="n"/>
-      <c r="H53" s="48" t="n"/>
-      <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
-      <c r="K53" s="49">
+      <c r="A53" s="100" t="n"/>
+      <c r="B53" s="154" t="n"/>
+      <c r="C53" s="154" t="n"/>
+      <c r="D53" s="154" t="n"/>
+      <c r="E53" s="35" t="n"/>
+      <c r="F53" s="46" t="n"/>
+      <c r="G53" s="46" t="n"/>
+      <c r="H53" s="46" t="n"/>
+      <c r="I53" s="37" t="n"/>
+      <c r="J53" s="37" t="n"/>
+      <c r="K53" s="47">
         <f>F53*IF(H53=0,1,H53)*I53</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A54" s="105" t="n"/>
-      <c r="B54" s="155" t="n"/>
-      <c r="C54" s="155" t="n"/>
-      <c r="D54" s="155" t="n"/>
-      <c r="E54" s="106" t="inlineStr">
+    <row r="54" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A54" s="101" t="n"/>
+      <c r="B54" s="154" t="n"/>
+      <c r="C54" s="154" t="n"/>
+      <c r="D54" s="154" t="n"/>
+      <c r="E54" s="96" t="inlineStr">
         <is>
           <t>SUBTOTAL MANO DE OBRA</t>
         </is>
@@ -2760,433 +2777,433 @@
       <c r="H54" s="155" t="n"/>
       <c r="I54" s="155" t="n"/>
       <c r="J54" s="155" t="n"/>
-      <c r="K54" s="50">
+      <c r="K54" s="48">
         <f>SUM(K39:K53)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A55" s="51" t="inlineStr">
+    <row r="55" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A55" s="49" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B55" s="52" t="n"/>
-      <c r="C55" s="53" t="inlineStr">
+      <c r="B55" s="50" t="n"/>
+      <c r="C55" s="128" t="inlineStr">
         <is>
           <t>EQUIPOS Y HERRAMIENTAS</t>
         </is>
       </c>
-      <c r="D55" s="53" t="n"/>
-      <c r="E55" s="107" t="n"/>
-      <c r="F55" s="155" t="n"/>
-      <c r="G55" s="155" t="n"/>
-      <c r="H55" s="155" t="n"/>
-      <c r="I55" s="155" t="n"/>
-      <c r="J55" s="155" t="n"/>
-      <c r="K55" s="159" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="66">
-      <c r="A56" s="133" t="inlineStr">
+      <c r="D55" s="51" t="n"/>
+      <c r="E55" s="103" t="n"/>
+      <c r="F55" s="154" t="n"/>
+      <c r="G55" s="154" t="n"/>
+      <c r="H55" s="154" t="n"/>
+      <c r="I55" s="154" t="n"/>
+      <c r="J55" s="154" t="n"/>
+      <c r="K55" s="158" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="62">
+      <c r="A56" s="127" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B56" s="155" t="n"/>
-      <c r="C56" s="155" t="n"/>
-      <c r="D56" s="155" t="n"/>
-      <c r="E56" s="132" t="inlineStr">
+      <c r="B56" s="154" t="n"/>
+      <c r="C56" s="154" t="n"/>
+      <c r="D56" s="154" t="n"/>
+      <c r="E56" s="126" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="F56" s="132" t="inlineStr">
+      <c r="F56" s="126" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="G56" s="132" t="n"/>
-      <c r="H56" s="132" t="inlineStr">
+      <c r="G56" s="126" t="n"/>
+      <c r="H56" s="126" t="inlineStr">
         <is>
           <t>Rendimiento</t>
         </is>
       </c>
-      <c r="I56" s="132" t="inlineStr">
+      <c r="I56" s="126" t="inlineStr">
         <is>
           <t>Vr Unit.</t>
         </is>
       </c>
-      <c r="J56" s="132" t="n"/>
-      <c r="K56" s="46" t="inlineStr">
+      <c r="J56" s="126" t="n"/>
+      <c r="K56" s="45" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A57" s="104" t="n"/>
-      <c r="B57" s="155" t="n"/>
-      <c r="C57" s="155" t="n"/>
-      <c r="D57" s="155" t="n"/>
-      <c r="E57" s="36" t="n"/>
-      <c r="F57" s="48" t="n"/>
-      <c r="G57" s="48" t="n"/>
-      <c r="H57" s="48" t="n"/>
-      <c r="I57" s="38" t="n"/>
-      <c r="J57" s="38" t="n"/>
-      <c r="K57" s="49">
+    <row r="57" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A57" s="100" t="n"/>
+      <c r="B57" s="154" t="n"/>
+      <c r="C57" s="154" t="n"/>
+      <c r="D57" s="154" t="n"/>
+      <c r="E57" s="35" t="n"/>
+      <c r="F57" s="46" t="n"/>
+      <c r="G57" s="46" t="n"/>
+      <c r="H57" s="46" t="n"/>
+      <c r="I57" s="37" t="n"/>
+      <c r="J57" s="37" t="n"/>
+      <c r="K57" s="47">
         <f>F57*IF(H57=0,1,H57)*I57</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A58" s="104" t="n"/>
-      <c r="B58" s="155" t="n"/>
-      <c r="C58" s="155" t="n"/>
-      <c r="D58" s="155" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="48" t="n"/>
-      <c r="G58" s="48" t="n"/>
-      <c r="H58" s="48" t="n"/>
-      <c r="I58" s="38" t="n"/>
-      <c r="J58" s="38" t="n"/>
-      <c r="K58" s="49">
+    <row r="58" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A58" s="100" t="n"/>
+      <c r="B58" s="154" t="n"/>
+      <c r="C58" s="154" t="n"/>
+      <c r="D58" s="154" t="n"/>
+      <c r="E58" s="35" t="n"/>
+      <c r="F58" s="46" t="n"/>
+      <c r="G58" s="46" t="n"/>
+      <c r="H58" s="46" t="n"/>
+      <c r="I58" s="37" t="n"/>
+      <c r="J58" s="37" t="n"/>
+      <c r="K58" s="47">
         <f>F58*IF(H58=0,1,H58)*I58</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A59" s="104" t="n"/>
-      <c r="B59" s="155" t="n"/>
-      <c r="C59" s="155" t="n"/>
-      <c r="D59" s="155" t="n"/>
-      <c r="E59" s="36" t="n"/>
-      <c r="F59" s="48" t="n"/>
-      <c r="G59" s="48" t="n"/>
-      <c r="H59" s="48" t="n"/>
-      <c r="I59" s="38" t="n"/>
-      <c r="J59" s="38" t="n"/>
-      <c r="K59" s="49">
+    <row r="59" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A59" s="100" t="n"/>
+      <c r="B59" s="154" t="n"/>
+      <c r="C59" s="154" t="n"/>
+      <c r="D59" s="154" t="n"/>
+      <c r="E59" s="35" t="n"/>
+      <c r="F59" s="46" t="n"/>
+      <c r="G59" s="46" t="n"/>
+      <c r="H59" s="46" t="n"/>
+      <c r="I59" s="37" t="n"/>
+      <c r="J59" s="37" t="n"/>
+      <c r="K59" s="47">
         <f>F59*IF(H59=0,1,H59)*I59</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A60" s="104" t="n"/>
-      <c r="B60" s="155" t="n"/>
-      <c r="C60" s="155" t="n"/>
-      <c r="D60" s="155" t="n"/>
-      <c r="E60" s="36" t="n"/>
-      <c r="F60" s="48" t="n"/>
-      <c r="G60" s="48" t="n"/>
-      <c r="H60" s="48" t="n"/>
-      <c r="I60" s="38" t="n"/>
-      <c r="J60" s="38" t="n"/>
-      <c r="K60" s="49">
+    <row r="60" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A60" s="100" t="n"/>
+      <c r="B60" s="154" t="n"/>
+      <c r="C60" s="154" t="n"/>
+      <c r="D60" s="154" t="n"/>
+      <c r="E60" s="35" t="n"/>
+      <c r="F60" s="46" t="n"/>
+      <c r="G60" s="46" t="n"/>
+      <c r="H60" s="46" t="n"/>
+      <c r="I60" s="37" t="n"/>
+      <c r="J60" s="37" t="n"/>
+      <c r="K60" s="47">
         <f>F60*IF(H60=0,1,H60)*I60</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A61" s="104" t="n"/>
-      <c r="B61" s="155" t="n"/>
-      <c r="C61" s="155" t="n"/>
-      <c r="D61" s="155" t="n"/>
-      <c r="E61" s="36" t="n"/>
-      <c r="F61" s="48" t="n"/>
-      <c r="G61" s="48" t="n"/>
-      <c r="H61" s="48" t="n"/>
-      <c r="I61" s="38" t="n"/>
-      <c r="J61" s="38" t="n"/>
-      <c r="K61" s="49">
+    <row r="61" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A61" s="100" t="n"/>
+      <c r="B61" s="154" t="n"/>
+      <c r="C61" s="154" t="n"/>
+      <c r="D61" s="154" t="n"/>
+      <c r="E61" s="35" t="n"/>
+      <c r="F61" s="46" t="n"/>
+      <c r="G61" s="46" t="n"/>
+      <c r="H61" s="46" t="n"/>
+      <c r="I61" s="37" t="n"/>
+      <c r="J61" s="37" t="n"/>
+      <c r="K61" s="47">
         <f>F61*IF(H61=0,1,H61)*I61</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A62" s="104" t="n"/>
-      <c r="B62" s="155" t="n"/>
-      <c r="C62" s="155" t="n"/>
-      <c r="D62" s="155" t="n"/>
-      <c r="E62" s="36" t="n"/>
-      <c r="F62" s="48" t="n"/>
-      <c r="G62" s="48" t="n"/>
-      <c r="H62" s="48" t="n"/>
-      <c r="I62" s="38" t="n"/>
-      <c r="J62" s="38" t="n"/>
-      <c r="K62" s="49">
+    <row r="62" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A62" s="100" t="n"/>
+      <c r="B62" s="154" t="n"/>
+      <c r="C62" s="154" t="n"/>
+      <c r="D62" s="154" t="n"/>
+      <c r="E62" s="35" t="n"/>
+      <c r="F62" s="46" t="n"/>
+      <c r="G62" s="46" t="n"/>
+      <c r="H62" s="46" t="n"/>
+      <c r="I62" s="37" t="n"/>
+      <c r="J62" s="37" t="n"/>
+      <c r="K62" s="47">
         <f>F62*IF(H62=0,1,H62)*I62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A63" s="104" t="n"/>
-      <c r="B63" s="97" t="n"/>
-      <c r="C63" s="97" t="n"/>
-      <c r="D63" s="97" t="n"/>
-      <c r="E63" s="36" t="n"/>
-      <c r="F63" s="48" t="n"/>
-      <c r="G63" s="48" t="n"/>
-      <c r="H63" s="48" t="n"/>
-      <c r="I63" s="38" t="n"/>
-      <c r="J63" s="38" t="n"/>
-      <c r="K63" s="49">
+    <row r="63" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A63" s="100" t="n"/>
+      <c r="B63" s="154" t="n"/>
+      <c r="C63" s="154" t="n"/>
+      <c r="D63" s="154" t="n"/>
+      <c r="E63" s="35" t="n"/>
+      <c r="F63" s="46" t="n"/>
+      <c r="G63" s="46" t="n"/>
+      <c r="H63" s="46" t="n"/>
+      <c r="I63" s="37" t="n"/>
+      <c r="J63" s="37" t="n"/>
+      <c r="K63" s="47">
         <f>F63*IF(H63=0,1,H63)*I63</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15.6" customHeight="1">
-      <c r="A64" s="104" t="n"/>
-      <c r="B64" s="97" t="n"/>
-      <c r="C64" s="97" t="n"/>
-      <c r="D64" s="97" t="n"/>
-      <c r="E64" s="36" t="n"/>
-      <c r="F64" s="48" t="n"/>
-      <c r="G64" s="48" t="n"/>
-      <c r="H64" s="48" t="n"/>
-      <c r="I64" s="38" t="n"/>
-      <c r="J64" s="38" t="n"/>
-      <c r="K64" s="49">
+      <c r="A64" s="100" t="n"/>
+      <c r="B64" s="154" t="n"/>
+      <c r="C64" s="154" t="n"/>
+      <c r="D64" s="154" t="n"/>
+      <c r="E64" s="35" t="n"/>
+      <c r="F64" s="46" t="n"/>
+      <c r="G64" s="46" t="n"/>
+      <c r="H64" s="46" t="n"/>
+      <c r="I64" s="37" t="n"/>
+      <c r="J64" s="37" t="n"/>
+      <c r="K64" s="47">
         <f>F64*IF(H64=0,1,H64)*I64</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15.6" customHeight="1">
-      <c r="A65" s="104" t="n"/>
-      <c r="B65" s="97" t="n"/>
-      <c r="C65" s="97" t="n"/>
-      <c r="D65" s="97" t="n"/>
-      <c r="E65" s="36" t="n"/>
-      <c r="F65" s="48" t="n"/>
-      <c r="G65" s="48" t="n"/>
-      <c r="H65" s="48" t="n"/>
-      <c r="I65" s="38" t="n"/>
-      <c r="J65" s="38" t="n"/>
-      <c r="K65" s="49">
+      <c r="A65" s="100" t="n"/>
+      <c r="B65" s="154" t="n"/>
+      <c r="C65" s="154" t="n"/>
+      <c r="D65" s="154" t="n"/>
+      <c r="E65" s="35" t="n"/>
+      <c r="F65" s="46" t="n"/>
+      <c r="G65" s="46" t="n"/>
+      <c r="H65" s="46" t="n"/>
+      <c r="I65" s="37" t="n"/>
+      <c r="J65" s="37" t="n"/>
+      <c r="K65" s="47">
         <f>F65*IF(H65=0,1,H65)*I65</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15.6" customHeight="1">
-      <c r="A66" s="104" t="n"/>
-      <c r="B66" s="97" t="n"/>
-      <c r="C66" s="97" t="n"/>
-      <c r="D66" s="97" t="n"/>
-      <c r="E66" s="36" t="n"/>
-      <c r="F66" s="48" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="48" t="n"/>
-      <c r="I66" s="38" t="n"/>
-      <c r="J66" s="38" t="n"/>
-      <c r="K66" s="49">
+      <c r="A66" s="100" t="n"/>
+      <c r="B66" s="154" t="n"/>
+      <c r="C66" s="154" t="n"/>
+      <c r="D66" s="154" t="n"/>
+      <c r="E66" s="35" t="n"/>
+      <c r="F66" s="46" t="n"/>
+      <c r="G66" s="46" t="n"/>
+      <c r="H66" s="46" t="n"/>
+      <c r="I66" s="37" t="n"/>
+      <c r="J66" s="37" t="n"/>
+      <c r="K66" s="47">
         <f>F66*IF(H66=0,1,H66)*I66</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15.6" customHeight="1">
-      <c r="A67" s="104" t="n"/>
-      <c r="B67" s="97" t="n"/>
-      <c r="C67" s="97" t="n"/>
-      <c r="D67" s="97" t="n"/>
-      <c r="E67" s="36" t="n"/>
-      <c r="F67" s="48" t="n"/>
-      <c r="G67" s="48" t="n"/>
-      <c r="H67" s="48" t="n"/>
-      <c r="I67" s="38" t="n"/>
-      <c r="J67" s="38" t="n"/>
-      <c r="K67" s="49">
+      <c r="A67" s="100" t="n"/>
+      <c r="B67" s="154" t="n"/>
+      <c r="C67" s="154" t="n"/>
+      <c r="D67" s="154" t="n"/>
+      <c r="E67" s="35" t="n"/>
+      <c r="F67" s="46" t="n"/>
+      <c r="G67" s="46" t="n"/>
+      <c r="H67" s="46" t="n"/>
+      <c r="I67" s="37" t="n"/>
+      <c r="J67" s="37" t="n"/>
+      <c r="K67" s="47">
         <f>F67*IF(H67=0,1,H67)*I67</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1">
-      <c r="A68" s="104" t="n"/>
-      <c r="B68" s="97" t="n"/>
-      <c r="C68" s="97" t="n"/>
-      <c r="D68" s="97" t="n"/>
-      <c r="E68" s="36" t="n"/>
-      <c r="F68" s="48" t="n"/>
-      <c r="G68" s="48" t="n"/>
-      <c r="H68" s="48" t="n"/>
-      <c r="I68" s="38" t="n"/>
-      <c r="J68" s="38" t="n"/>
-      <c r="K68" s="49">
+      <c r="A68" s="100" t="n"/>
+      <c r="B68" s="154" t="n"/>
+      <c r="C68" s="154" t="n"/>
+      <c r="D68" s="154" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="46" t="n"/>
+      <c r="G68" s="46" t="n"/>
+      <c r="H68" s="46" t="n"/>
+      <c r="I68" s="37" t="n"/>
+      <c r="J68" s="37" t="n"/>
+      <c r="K68" s="47">
         <f>F68*IF(H68=0,1,H68)*I68</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15.6" customHeight="1">
-      <c r="A69" s="104" t="n"/>
-      <c r="B69" s="97" t="n"/>
-      <c r="C69" s="97" t="n"/>
-      <c r="D69" s="97" t="n"/>
-      <c r="E69" s="36" t="n"/>
-      <c r="F69" s="48" t="n"/>
-      <c r="G69" s="48" t="n"/>
-      <c r="H69" s="48" t="n"/>
-      <c r="I69" s="38" t="n"/>
-      <c r="J69" s="38" t="n"/>
-      <c r="K69" s="49">
+      <c r="A69" s="100" t="n"/>
+      <c r="B69" s="154" t="n"/>
+      <c r="C69" s="154" t="n"/>
+      <c r="D69" s="154" t="n"/>
+      <c r="E69" s="35" t="n"/>
+      <c r="F69" s="46" t="n"/>
+      <c r="G69" s="46" t="n"/>
+      <c r="H69" s="46" t="n"/>
+      <c r="I69" s="37" t="n"/>
+      <c r="J69" s="37" t="n"/>
+      <c r="K69" s="47">
         <f>F69*IF(H69=0,1,H69)*I69</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15.6" customHeight="1">
-      <c r="A70" s="104" t="n"/>
-      <c r="B70" s="97" t="n"/>
-      <c r="C70" s="97" t="n"/>
-      <c r="D70" s="97" t="n"/>
-      <c r="E70" s="36" t="n"/>
-      <c r="F70" s="48" t="n"/>
-      <c r="G70" s="48" t="n"/>
-      <c r="H70" s="48" t="n"/>
-      <c r="I70" s="38" t="n"/>
-      <c r="J70" s="38" t="n"/>
-      <c r="K70" s="49">
+      <c r="A70" s="100" t="n"/>
+      <c r="B70" s="154" t="n"/>
+      <c r="C70" s="154" t="n"/>
+      <c r="D70" s="154" t="n"/>
+      <c r="E70" s="35" t="n"/>
+      <c r="F70" s="46" t="n"/>
+      <c r="G70" s="46" t="n"/>
+      <c r="H70" s="46" t="n"/>
+      <c r="I70" s="37" t="n"/>
+      <c r="J70" s="37" t="n"/>
+      <c r="K70" s="47">
         <f>F70*IF(H70=0,1,H70)*I70</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15.6" customHeight="1">
-      <c r="A71" s="104" t="n"/>
-      <c r="B71" s="97" t="n"/>
-      <c r="C71" s="97" t="n"/>
-      <c r="D71" s="97" t="n"/>
-      <c r="E71" s="36" t="n"/>
-      <c r="F71" s="48" t="n"/>
-      <c r="G71" s="48" t="n"/>
-      <c r="H71" s="48" t="n"/>
-      <c r="I71" s="38" t="n"/>
-      <c r="J71" s="38" t="n"/>
-      <c r="K71" s="49">
+      <c r="A71" s="100" t="n"/>
+      <c r="B71" s="154" t="n"/>
+      <c r="C71" s="154" t="n"/>
+      <c r="D71" s="154" t="n"/>
+      <c r="E71" s="35" t="n"/>
+      <c r="F71" s="46" t="n"/>
+      <c r="G71" s="46" t="n"/>
+      <c r="H71" s="46" t="n"/>
+      <c r="I71" s="37" t="n"/>
+      <c r="J71" s="37" t="n"/>
+      <c r="K71" s="47">
         <f>F71*IF(H71=0,1,H71)*I71</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A72" s="105" t="n"/>
-      <c r="B72" s="155" t="n"/>
-      <c r="C72" s="155" t="n"/>
-      <c r="D72" s="155" t="n"/>
-      <c r="E72" s="106" t="inlineStr">
+    <row r="72" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A72" s="101" t="n"/>
+      <c r="B72" s="154" t="n"/>
+      <c r="C72" s="154" t="n"/>
+      <c r="D72" s="154" t="n"/>
+      <c r="E72" s="102" t="inlineStr">
         <is>
           <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
         </is>
       </c>
-      <c r="F72" s="155" t="n"/>
-      <c r="G72" s="155" t="n"/>
-      <c r="H72" s="155" t="n"/>
-      <c r="I72" s="155" t="n"/>
-      <c r="J72" s="155" t="n"/>
-      <c r="K72" s="50">
+      <c r="F72" s="154" t="n"/>
+      <c r="G72" s="154" t="n"/>
+      <c r="H72" s="154" t="n"/>
+      <c r="I72" s="154" t="n"/>
+      <c r="J72" s="154" t="n"/>
+      <c r="K72" s="48">
         <f>SUM(K57:K71)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="24.75" customFormat="1" customHeight="1" s="66">
-      <c r="A73" s="109" t="inlineStr">
+    <row r="73" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A73" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">                Materiales</t>
         </is>
       </c>
-      <c r="B73" s="155" t="n"/>
-      <c r="C73" s="155" t="n"/>
-      <c r="D73" s="155" t="n"/>
-      <c r="E73" s="155" t="n"/>
-      <c r="F73" s="155" t="n"/>
-      <c r="G73" s="155" t="n"/>
-      <c r="H73" s="155" t="n"/>
-      <c r="I73" s="155" t="n"/>
-      <c r="J73" s="155" t="n"/>
-      <c r="K73" s="54">
+      <c r="B73" s="154" t="n"/>
+      <c r="C73" s="154" t="n"/>
+      <c r="D73" s="154" t="n"/>
+      <c r="E73" s="154" t="n"/>
+      <c r="F73" s="154" t="n"/>
+      <c r="G73" s="154" t="n"/>
+      <c r="H73" s="154" t="n"/>
+      <c r="I73" s="154" t="n"/>
+      <c r="J73" s="154" t="n"/>
+      <c r="K73" s="52">
         <f>K36</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="24.75" customFormat="1" customHeight="1" s="66">
-      <c r="A74" s="109" t="inlineStr">
+    <row r="74" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A74" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">                Mano de Obra</t>
         </is>
       </c>
-      <c r="B74" s="155" t="n"/>
-      <c r="C74" s="155" t="n"/>
-      <c r="D74" s="155" t="n"/>
-      <c r="E74" s="155" t="n"/>
-      <c r="F74" s="155" t="n"/>
-      <c r="G74" s="155" t="n"/>
-      <c r="H74" s="155" t="n"/>
-      <c r="I74" s="155" t="n"/>
-      <c r="J74" s="155" t="n"/>
-      <c r="K74" s="54">
+      <c r="B74" s="154" t="n"/>
+      <c r="C74" s="154" t="n"/>
+      <c r="D74" s="154" t="n"/>
+      <c r="E74" s="154" t="n"/>
+      <c r="F74" s="154" t="n"/>
+      <c r="G74" s="154" t="n"/>
+      <c r="H74" s="154" t="n"/>
+      <c r="I74" s="154" t="n"/>
+      <c r="J74" s="154" t="n"/>
+      <c r="K74" s="52">
         <f>K54</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="24.75" customFormat="1" customHeight="1" s="66">
-      <c r="A75" s="109" t="inlineStr">
+    <row r="75" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A75" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">                Equipos y herramientas</t>
         </is>
       </c>
-      <c r="B75" s="155" t="n"/>
-      <c r="C75" s="155" t="n"/>
-      <c r="D75" s="155" t="n"/>
-      <c r="E75" s="155" t="n"/>
-      <c r="F75" s="155" t="n"/>
-      <c r="G75" s="155" t="n"/>
-      <c r="H75" s="155" t="n"/>
-      <c r="I75" s="155" t="n"/>
-      <c r="J75" s="155" t="n"/>
-      <c r="K75" s="54">
+      <c r="B75" s="154" t="n"/>
+      <c r="C75" s="154" t="n"/>
+      <c r="D75" s="154" t="n"/>
+      <c r="E75" s="154" t="n"/>
+      <c r="F75" s="154" t="n"/>
+      <c r="G75" s="154" t="n"/>
+      <c r="H75" s="154" t="n"/>
+      <c r="I75" s="154" t="n"/>
+      <c r="J75" s="154" t="n"/>
+      <c r="K75" s="52">
         <f>K72</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="19.95" customFormat="1" customHeight="1" s="66">
-      <c r="A76" s="110" t="inlineStr">
+    <row r="76" ht="19.95" customFormat="1" customHeight="1" s="62">
+      <c r="A76" s="106" t="inlineStr">
         <is>
           <t>TOTAL DIRECTO UNITARIO</t>
         </is>
       </c>
-      <c r="B76" s="160" t="n"/>
-      <c r="C76" s="160" t="n"/>
-      <c r="D76" s="160" t="n"/>
-      <c r="E76" s="160" t="n"/>
-      <c r="F76" s="160" t="n"/>
-      <c r="G76" s="160" t="n"/>
-      <c r="H76" s="160" t="n"/>
-      <c r="I76" s="160" t="n"/>
-      <c r="J76" s="160" t="n"/>
-      <c r="K76" s="55">
+      <c r="B76" s="159" t="n"/>
+      <c r="C76" s="159" t="n"/>
+      <c r="D76" s="159" t="n"/>
+      <c r="E76" s="159" t="n"/>
+      <c r="F76" s="159" t="n"/>
+      <c r="G76" s="159" t="n"/>
+      <c r="H76" s="159" t="n"/>
+      <c r="I76" s="159" t="n"/>
+      <c r="J76" s="159" t="n"/>
+      <c r="K76" s="53">
         <f>SUM(K73:K75)</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="4.5" customFormat="1" customHeight="1" s="66">
-      <c r="A77" s="56" t="n"/>
-      <c r="B77" s="57" t="n"/>
-      <c r="C77" s="57" t="n"/>
-      <c r="D77" s="57" t="n"/>
-      <c r="E77" s="57" t="n"/>
-      <c r="F77" s="57" t="n"/>
-      <c r="G77" s="57" t="n"/>
-      <c r="H77" s="57" t="n"/>
-      <c r="I77" s="57" t="n"/>
-      <c r="J77" s="57" t="n"/>
-      <c r="K77" s="58" t="n"/>
-    </row>
-    <row r="78" ht="15.75" customFormat="1" customHeight="1" s="66">
-      <c r="A78" s="112" t="inlineStr">
+    <row r="77" ht="4.5" customFormat="1" customHeight="1" s="62">
+      <c r="A77" s="54" t="n"/>
+      <c r="B77" s="55" t="n"/>
+      <c r="C77" s="55" t="n"/>
+      <c r="D77" s="55" t="n"/>
+      <c r="E77" s="55" t="n"/>
+      <c r="F77" s="55" t="n"/>
+      <c r="G77" s="55" t="n"/>
+      <c r="H77" s="55" t="n"/>
+      <c r="I77" s="55" t="n"/>
+      <c r="J77" s="55" t="n"/>
+      <c r="K77" s="56" t="n"/>
+    </row>
+    <row r="78" ht="15.75" customFormat="1" customHeight="1" s="62">
+      <c r="A78" s="135" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="B78" s="161" t="n"/>
-      <c r="C78" s="161" t="n"/>
-      <c r="D78" s="113" t="n"/>
-      <c r="E78" s="121" t="n"/>
-      <c r="F78" s="114" t="inlineStr">
+      <c r="B78" s="160" t="n"/>
+      <c r="C78" s="160" t="n"/>
+      <c r="D78" s="160" t="n"/>
+      <c r="E78" s="160" t="n"/>
+      <c r="F78" s="109" t="inlineStr">
         <is>
           <t>Vo. Bo. INTERVENTORÍA:</t>
         </is>
@@ -3197,165 +3214,183 @@
       <c r="J78" s="161" t="n"/>
       <c r="K78" s="162" t="n"/>
     </row>
-    <row r="79" ht="42" customFormat="1" customHeight="1" s="66">
-      <c r="A79" s="61" t="inlineStr">
+    <row r="79" ht="42" customFormat="1" customHeight="1" s="62">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="B79" s="116" t="n"/>
+      <c r="B79" s="111" t="n"/>
       <c r="C79" s="163" t="n"/>
       <c r="D79" s="163" t="n"/>
       <c r="E79" s="163" t="n"/>
-      <c r="F79" s="62" t="inlineStr">
+      <c r="F79" s="134" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="G79" s="62" t="n"/>
-      <c r="H79" s="118" t="n"/>
+      <c r="G79" s="113" t="n"/>
+      <c r="H79" s="163" t="n"/>
       <c r="I79" s="163" t="n"/>
       <c r="J79" s="163" t="n"/>
       <c r="K79" s="164" t="n"/>
     </row>
-    <row r="80" ht="24.75" customFormat="1" customHeight="1" s="66">
-      <c r="A80" s="61" t="inlineStr">
+    <row r="80" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A80" s="57" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="B80" s="116" t="n"/>
+      <c r="B80" s="111" t="n"/>
       <c r="C80" s="163" t="n"/>
       <c r="D80" s="163" t="n"/>
       <c r="E80" s="163" t="n"/>
-      <c r="F80" s="62" t="inlineStr">
+      <c r="F80" s="134" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="G80" s="62" t="n"/>
-      <c r="H80" s="118" t="n"/>
+      <c r="G80" s="113" t="n"/>
+      <c r="H80" s="163" t="n"/>
       <c r="I80" s="163" t="n"/>
       <c r="J80" s="163" t="n"/>
       <c r="K80" s="164" t="n"/>
     </row>
-    <row r="81" ht="24.75" customFormat="1" customHeight="1" s="66">
-      <c r="A81" s="61" t="inlineStr">
+    <row r="81" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="B81" s="116" t="n"/>
+      <c r="B81" s="111" t="n"/>
       <c r="C81" s="163" t="n"/>
       <c r="D81" s="163" t="n"/>
       <c r="E81" s="163" t="n"/>
-      <c r="F81" s="62" t="inlineStr">
+      <c r="F81" s="134" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="G81" s="62" t="n"/>
-      <c r="H81" s="118" t="n"/>
+      <c r="G81" s="113" t="n"/>
+      <c r="H81" s="163" t="n"/>
       <c r="I81" s="163" t="n"/>
       <c r="J81" s="163" t="n"/>
       <c r="K81" s="164" t="n"/>
     </row>
-    <row r="82" ht="15" customFormat="1" customHeight="1" s="66">
-      <c r="A82" s="63" t="inlineStr">
+    <row r="82" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A82" s="59" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B82" s="120" t="n"/>
-      <c r="C82" s="139" t="n"/>
-      <c r="D82" s="139" t="n"/>
-      <c r="E82" s="139" t="n"/>
-      <c r="F82" s="139" t="n"/>
-      <c r="G82" s="139" t="n"/>
-      <c r="H82" s="139" t="n"/>
-      <c r="I82" s="139" t="n"/>
-      <c r="J82" s="139" t="n"/>
-      <c r="K82" s="64">
+      <c r="B82" s="114" t="n"/>
+      <c r="C82" s="138" t="n"/>
+      <c r="D82" s="138" t="n"/>
+      <c r="E82" s="138" t="n"/>
+      <c r="F82" s="138" t="n"/>
+      <c r="G82" s="138" t="n"/>
+      <c r="H82" s="138" t="n"/>
+      <c r="I82" s="138" t="n"/>
+      <c r="J82" s="138" t="n"/>
+      <c r="K82" s="60">
         <f>K4</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customFormat="1" customHeight="1" s="66"/>
+    <row r="83" ht="15" customFormat="1" customHeight="1" s="62"/>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="H80:K80"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A35:D35"/>
+  <mergeCells count="91">
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="D1:K1"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="B82:J82"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B79:E79"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="E55:K55"/>
     <mergeCell ref="A60:D60"/>
-    <mergeCell ref="E54:J54"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="E72:J72"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E4:H4"/>
     <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A41:D41"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="E19:K19"/>
-    <mergeCell ref="F78:K78"/>
-    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="G79:K79"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A75:J75"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="H79:K79"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A26:D26"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="H81:K81"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="G80:K80"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="G81:K81"/>
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B82:J82"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E54:J54"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="E72:J72"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F78:K78"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>

--- a/public/plantilla-apu.xlsx
+++ b/public/plantilla-apu.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -257,6 +257,20 @@
       <i val="1"/>
       <color theme="0" tint="-0.249977111117893"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF17365D"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1135,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1503,6 +1517,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1808,7 +1828,7 @@
     <tabColor theme="9" tint="-0.499984740745262"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X82"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col width="20.77734375" customWidth="1" style="62" min="1" max="1"/>
@@ -2073,34 +2093,34 @@
       <c r="J15" s="145" t="n"/>
       <c r="K15" s="145" t="n"/>
     </row>
-    <row r="16" ht="19.95" customFormat="1" customHeight="1" s="62" thickBot="1" thickTop="1">
-      <c r="A16" s="78" t="inlineStr">
+    <row r="16" ht="22" customFormat="1" customHeight="1" s="62" thickBot="1" thickTop="1">
+      <c r="A16" s="165" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
       <c r="B16" s="26" t="n"/>
-      <c r="C16" s="78" t="inlineStr">
+      <c r="C16" s="165" t="inlineStr">
         <is>
           <t>CUADRILLA</t>
         </is>
       </c>
       <c r="D16" s="80" t="n"/>
-      <c r="E16" s="78" t="inlineStr">
+      <c r="E16" s="165" t="inlineStr">
         <is>
           <t>JORNADA</t>
         </is>
       </c>
       <c r="F16" s="146" t="n"/>
       <c r="G16" s="116" t="n"/>
-      <c r="H16" s="78" t="inlineStr">
+      <c r="H16" s="165" t="inlineStr">
         <is>
           <t>RENDIMIENTO</t>
         </is>
       </c>
       <c r="I16" s="146" t="n"/>
       <c r="J16" s="84" t="n"/>
-      <c r="K16" s="78" t="inlineStr">
+      <c r="K16" s="165" t="inlineStr">
         <is>
           <t>CONSUMO M.O.</t>
         </is>
@@ -2128,7 +2148,7 @@
         <v/>
       </c>
       <c r="I17" s="148" t="n"/>
-      <c r="K17" s="122">
+      <c r="K17" s="166">
         <f>IFERROR(1/W4,0)</f>
         <v/>
       </c>
@@ -2332,197 +2352,197 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15.6" customHeight="1">
-      <c r="A29" s="92" t="n"/>
-      <c r="B29" s="154" t="n"/>
-      <c r="C29" s="154" t="n"/>
-      <c r="D29" s="154" t="n"/>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="37" t="n"/>
-      <c r="J29" s="37" t="n"/>
-      <c r="K29" s="38">
-        <f>F29*IF(H29=0,1,H29)*I29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15.6" customHeight="1">
-      <c r="A30" s="92" t="n"/>
-      <c r="B30" s="154" t="n"/>
-      <c r="C30" s="154" t="n"/>
-      <c r="D30" s="154" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="37" t="n"/>
-      <c r="J30" s="37" t="n"/>
-      <c r="K30" s="38">
-        <f>F30*IF(H30=0,1,H30)*I30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15.6" customHeight="1">
-      <c r="A31" s="92" t="n"/>
+    <row r="29" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A29" s="94" t="n"/>
+      <c r="B29" s="155" t="n"/>
+      <c r="C29" s="155" t="n"/>
+      <c r="D29" s="155" t="n"/>
+      <c r="E29" s="96" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES</t>
+        </is>
+      </c>
+      <c r="F29" s="155" t="n"/>
+      <c r="G29" s="155" t="n"/>
+      <c r="H29" s="155" t="n"/>
+      <c r="I29" s="155" t="n"/>
+      <c r="J29" s="155" t="n"/>
+      <c r="K29" s="40">
+        <f>SUM(K21:K28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="137" t="inlineStr">
+        <is>
+          <t>MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="n"/>
+      <c r="E30" s="97" t="n"/>
+      <c r="F30" s="156" t="n"/>
+      <c r="G30" s="156" t="n"/>
+      <c r="H30" s="156" t="n"/>
+      <c r="I30" s="156" t="n"/>
+      <c r="J30" s="156" t="n"/>
+      <c r="K30" s="157" t="n"/>
+    </row>
+    <row r="31" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A31" s="127" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
       <c r="B31" s="154" t="n"/>
       <c r="C31" s="154" t="n"/>
       <c r="D31" s="154" t="n"/>
-      <c r="E31" s="35" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="36" t="n"/>
-      <c r="I31" s="37" t="n"/>
-      <c r="J31" s="37" t="n"/>
-      <c r="K31" s="38">
-        <f>F31*IF(H31=0,1,H31)*I31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15.6" customHeight="1">
-      <c r="A32" s="92" t="n"/>
+      <c r="E31" s="126" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F31" s="126" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G31" s="126" t="n"/>
+      <c r="H31" s="126" t="inlineStr">
+        <is>
+          <t>Rendimiento</t>
+        </is>
+      </c>
+      <c r="I31" s="126" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="J31" s="126" t="n"/>
+      <c r="K31" s="45" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A32" s="100" t="n"/>
       <c r="B32" s="154" t="n"/>
       <c r="C32" s="154" t="n"/>
       <c r="D32" s="154" t="n"/>
       <c r="E32" s="35" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="46" t="n"/>
       <c r="I32" s="37" t="n"/>
       <c r="J32" s="37" t="n"/>
-      <c r="K32" s="38">
+      <c r="K32" s="47">
         <f>F32*IF(H32=0,1,H32)*I32</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15.6" customHeight="1">
-      <c r="A33" s="92" t="n"/>
+    <row r="33" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A33" s="100" t="n"/>
       <c r="B33" s="154" t="n"/>
       <c r="C33" s="154" t="n"/>
       <c r="D33" s="154" t="n"/>
       <c r="E33" s="35" t="n"/>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="36" t="n"/>
+      <c r="F33" s="46" t="n"/>
+      <c r="G33" s="46" t="n"/>
+      <c r="H33" s="46" t="n"/>
       <c r="I33" s="37" t="n"/>
       <c r="J33" s="37" t="n"/>
-      <c r="K33" s="38">
+      <c r="K33" s="47">
         <f>F33*IF(H33=0,1,H33)*I33</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15.6" customHeight="1">
-      <c r="A34" s="92" t="n"/>
+    <row r="34" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A34" s="100" t="n"/>
       <c r="B34" s="154" t="n"/>
       <c r="C34" s="154" t="n"/>
       <c r="D34" s="154" t="n"/>
       <c r="E34" s="35" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
+      <c r="F34" s="46" t="n"/>
+      <c r="G34" s="46" t="n"/>
+      <c r="H34" s="46" t="n"/>
       <c r="I34" s="37" t="n"/>
       <c r="J34" s="37" t="n"/>
-      <c r="K34" s="38">
+      <c r="K34" s="47">
         <f>F34*IF(H34=0,1,H34)*I34</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15.6" customHeight="1">
-      <c r="A35" s="92" t="n"/>
+    <row r="35" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A35" s="100" t="n"/>
       <c r="B35" s="154" t="n"/>
       <c r="C35" s="154" t="n"/>
       <c r="D35" s="154" t="n"/>
       <c r="E35" s="35" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="36" t="n"/>
+      <c r="F35" s="46" t="n"/>
+      <c r="G35" s="46" t="n"/>
+      <c r="H35" s="46" t="n"/>
       <c r="I35" s="37" t="n"/>
       <c r="J35" s="37" t="n"/>
-      <c r="K35" s="38">
+      <c r="K35" s="47">
         <f>F35*IF(H35=0,1,H35)*I35</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A36" s="94" t="n"/>
-      <c r="B36" s="155" t="n"/>
-      <c r="C36" s="155" t="n"/>
-      <c r="D36" s="155" t="n"/>
-      <c r="E36" s="96" t="inlineStr">
-        <is>
-          <t>SUBTOTAL MATERIALES</t>
-        </is>
-      </c>
-      <c r="F36" s="155" t="n"/>
-      <c r="G36" s="155" t="n"/>
-      <c r="H36" s="155" t="n"/>
-      <c r="I36" s="155" t="n"/>
-      <c r="J36" s="155" t="n"/>
-      <c r="K36" s="40">
-        <f>SUM(K21:K35)</f>
+      <c r="A36" s="100" t="n"/>
+      <c r="B36" s="154" t="n"/>
+      <c r="C36" s="154" t="n"/>
+      <c r="D36" s="154" t="n"/>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="46" t="n"/>
+      <c r="G36" s="46" t="n"/>
+      <c r="H36" s="46" t="n"/>
+      <c r="I36" s="37" t="n"/>
+      <c r="J36" s="37" t="n"/>
+      <c r="K36" s="47">
+        <f>F36*IF(H36=0,1,H36)*I36</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A37" s="41" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B37" s="42" t="n"/>
-      <c r="C37" s="137" t="inlineStr">
-        <is>
-          <t>MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="n"/>
-      <c r="E37" s="97" t="n"/>
-      <c r="F37" s="156" t="n"/>
-      <c r="G37" s="156" t="n"/>
-      <c r="H37" s="156" t="n"/>
-      <c r="I37" s="156" t="n"/>
-      <c r="J37" s="156" t="n"/>
-      <c r="K37" s="157" t="n"/>
+      <c r="A37" s="100" t="n"/>
+      <c r="B37" s="154" t="n"/>
+      <c r="C37" s="154" t="n"/>
+      <c r="D37" s="154" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="46" t="n"/>
+      <c r="G37" s="46" t="n"/>
+      <c r="H37" s="46" t="n"/>
+      <c r="I37" s="39" t="n"/>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="47">
+        <f>F37*IF(H37=0,1,H37)*I37</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A38" s="127" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
+      <c r="A38" s="100" t="n"/>
       <c r="B38" s="154" t="n"/>
       <c r="C38" s="154" t="n"/>
       <c r="D38" s="154" t="n"/>
-      <c r="E38" s="126" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="F38" s="126" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="G38" s="126" t="n"/>
-      <c r="H38" s="126" t="inlineStr">
-        <is>
-          <t>Rendimiento</t>
-        </is>
-      </c>
-      <c r="I38" s="126" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="J38" s="126" t="n"/>
-      <c r="K38" s="45" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
+      <c r="I38" s="37" t="n"/>
+      <c r="J38" s="37" t="n"/>
+      <c r="K38" s="47">
+        <f>F38*IF(H38=0,1,H38)*I38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15.6" customHeight="1">
       <c r="A39" s="100" t="n"/>
       <c r="B39" s="154" t="n"/>
       <c r="C39" s="154" t="n"/>
@@ -2539,51 +2559,81 @@
       </c>
     </row>
     <row r="40" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A40" s="100" t="n"/>
+      <c r="A40" s="101" t="n"/>
       <c r="B40" s="154" t="n"/>
       <c r="C40" s="154" t="n"/>
       <c r="D40" s="154" t="n"/>
-      <c r="E40" s="35" t="n"/>
-      <c r="F40" s="46" t="n"/>
-      <c r="G40" s="46" t="n"/>
-      <c r="H40" s="46" t="n"/>
-      <c r="I40" s="37" t="n"/>
-      <c r="J40" s="37" t="n"/>
-      <c r="K40" s="47">
-        <f>F40*IF(H40=0,1,H40)*I40</f>
+      <c r="E40" s="96" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="F40" s="155" t="n"/>
+      <c r="G40" s="155" t="n"/>
+      <c r="H40" s="155" t="n"/>
+      <c r="I40" s="155" t="n"/>
+      <c r="J40" s="155" t="n"/>
+      <c r="K40" s="48">
+        <f>SUM(K32:K39)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A41" s="100" t="n"/>
-      <c r="B41" s="154" t="n"/>
-      <c r="C41" s="154" t="n"/>
-      <c r="D41" s="154" t="n"/>
-      <c r="E41" s="35" t="n"/>
-      <c r="F41" s="46" t="n"/>
-      <c r="G41" s="46" t="n"/>
-      <c r="H41" s="46" t="n"/>
-      <c r="I41" s="37" t="n"/>
-      <c r="J41" s="37" t="n"/>
-      <c r="K41" s="47">
-        <f>F41*IF(H41=0,1,H41)*I41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A42" s="100" t="n"/>
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="128" t="inlineStr">
+        <is>
+          <t>EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="n"/>
+      <c r="E41" s="103" t="n"/>
+      <c r="F41" s="154" t="n"/>
+      <c r="G41" s="154" t="n"/>
+      <c r="H41" s="154" t="n"/>
+      <c r="I41" s="154" t="n"/>
+      <c r="J41" s="154" t="n"/>
+      <c r="K41" s="158" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customFormat="1" customHeight="1" s="62">
+      <c r="A42" s="127" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
       <c r="B42" s="154" t="n"/>
       <c r="C42" s="154" t="n"/>
       <c r="D42" s="154" t="n"/>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n"/>
-      <c r="H42" s="46" t="n"/>
-      <c r="I42" s="37" t="n"/>
-      <c r="J42" s="37" t="n"/>
-      <c r="K42" s="47">
-        <f>F42*IF(H42=0,1,H42)*I42</f>
-        <v/>
+      <c r="E42" s="126" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="F42" s="126" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="G42" s="126" t="n"/>
+      <c r="H42" s="126" t="inlineStr">
+        <is>
+          <t>Rendimiento</t>
+        </is>
+      </c>
+      <c r="I42" s="126" t="inlineStr">
+        <is>
+          <t>Vr Unit.</t>
+        </is>
+      </c>
+      <c r="J42" s="126" t="n"/>
+      <c r="K42" s="45" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="15" customFormat="1" customHeight="1" s="62">
@@ -2611,8 +2661,8 @@
       <c r="F44" s="46" t="n"/>
       <c r="G44" s="46" t="n"/>
       <c r="H44" s="46" t="n"/>
-      <c r="I44" s="39" t="n"/>
-      <c r="J44" s="39" t="n"/>
+      <c r="I44" s="37" t="n"/>
+      <c r="J44" s="37" t="n"/>
       <c r="K44" s="47">
         <f>F44*IF(H44=0,1,H44)*I44</f>
         <v/>
@@ -2634,7 +2684,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A46" s="100" t="n"/>
       <c r="B46" s="154" t="n"/>
       <c r="C46" s="154" t="n"/>
@@ -2650,7 +2700,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="15.6" customHeight="1">
+    <row r="47" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A47" s="100" t="n"/>
       <c r="B47" s="154" t="n"/>
       <c r="C47" s="154" t="n"/>
@@ -2666,7 +2716,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="15.6" customHeight="1">
+    <row r="48" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A48" s="100" t="n"/>
       <c r="B48" s="154" t="n"/>
       <c r="C48" s="154" t="n"/>
@@ -2682,7 +2732,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="15.6" customHeight="1">
+    <row r="49" ht="15" customFormat="1" customHeight="1" s="62">
       <c r="A49" s="100" t="n"/>
       <c r="B49" s="154" t="n"/>
       <c r="C49" s="154" t="n"/>
@@ -2714,683 +2764,296 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="15.6" customHeight="1">
-      <c r="A51" s="100" t="n"/>
+    <row r="51" ht="15" customFormat="1" customHeight="1" s="62">
+      <c r="A51" s="101" t="n"/>
       <c r="B51" s="154" t="n"/>
       <c r="C51" s="154" t="n"/>
       <c r="D51" s="154" t="n"/>
-      <c r="E51" s="35" t="n"/>
-      <c r="F51" s="46" t="n"/>
-      <c r="G51" s="46" t="n"/>
-      <c r="H51" s="46" t="n"/>
-      <c r="I51" s="37" t="n"/>
-      <c r="J51" s="37" t="n"/>
-      <c r="K51" s="47">
-        <f>F51*IF(H51=0,1,H51)*I51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15.6" customHeight="1">
-      <c r="A52" s="100" t="n"/>
+      <c r="E51" s="102" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
+        </is>
+      </c>
+      <c r="F51" s="154" t="n"/>
+      <c r="G51" s="154" t="n"/>
+      <c r="H51" s="154" t="n"/>
+      <c r="I51" s="154" t="n"/>
+      <c r="J51" s="154" t="n"/>
+      <c r="K51" s="48">
+        <f>SUM(K43:K50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A52" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Materiales</t>
+        </is>
+      </c>
       <c r="B52" s="154" t="n"/>
       <c r="C52" s="154" t="n"/>
       <c r="D52" s="154" t="n"/>
-      <c r="E52" s="35" t="n"/>
-      <c r="F52" s="46" t="n"/>
-      <c r="G52" s="46" t="n"/>
-      <c r="H52" s="46" t="n"/>
-      <c r="I52" s="37" t="n"/>
-      <c r="J52" s="37" t="n"/>
-      <c r="K52" s="47">
-        <f>F52*IF(H52=0,1,H52)*I52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15.6" customHeight="1">
-      <c r="A53" s="100" t="n"/>
+      <c r="E52" s="154" t="n"/>
+      <c r="F52" s="154" t="n"/>
+      <c r="G52" s="154" t="n"/>
+      <c r="H52" s="154" t="n"/>
+      <c r="I52" s="154" t="n"/>
+      <c r="J52" s="154" t="n"/>
+      <c r="K52" s="52">
+        <f>K29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A53" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Mano de Obra</t>
+        </is>
+      </c>
       <c r="B53" s="154" t="n"/>
       <c r="C53" s="154" t="n"/>
       <c r="D53" s="154" t="n"/>
-      <c r="E53" s="35" t="n"/>
-      <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n"/>
-      <c r="H53" s="46" t="n"/>
-      <c r="I53" s="37" t="n"/>
-      <c r="J53" s="37" t="n"/>
-      <c r="K53" s="47">
-        <f>F53*IF(H53=0,1,H53)*I53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A54" s="101" t="n"/>
+      <c r="E53" s="154" t="n"/>
+      <c r="F53" s="154" t="n"/>
+      <c r="G53" s="154" t="n"/>
+      <c r="H53" s="154" t="n"/>
+      <c r="I53" s="154" t="n"/>
+      <c r="J53" s="154" t="n"/>
+      <c r="K53" s="52">
+        <f>K40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A54" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Equipos y herramientas</t>
+        </is>
+      </c>
       <c r="B54" s="154" t="n"/>
       <c r="C54" s="154" t="n"/>
       <c r="D54" s="154" t="n"/>
-      <c r="E54" s="96" t="inlineStr">
-        <is>
-          <t>SUBTOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="F54" s="155" t="n"/>
-      <c r="G54" s="155" t="n"/>
-      <c r="H54" s="155" t="n"/>
-      <c r="I54" s="155" t="n"/>
-      <c r="J54" s="155" t="n"/>
-      <c r="K54" s="48">
-        <f>SUM(K39:K53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A55" s="49" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B55" s="50" t="n"/>
-      <c r="C55" s="128" t="inlineStr">
-        <is>
-          <t>EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="D55" s="51" t="n"/>
-      <c r="E55" s="103" t="n"/>
-      <c r="F55" s="154" t="n"/>
-      <c r="G55" s="154" t="n"/>
-      <c r="H55" s="154" t="n"/>
-      <c r="I55" s="154" t="n"/>
-      <c r="J55" s="154" t="n"/>
-      <c r="K55" s="158" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="62">
-      <c r="A56" s="127" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B56" s="154" t="n"/>
-      <c r="C56" s="154" t="n"/>
-      <c r="D56" s="154" t="n"/>
-      <c r="E56" s="126" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="F56" s="126" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="G56" s="126" t="n"/>
-      <c r="H56" s="126" t="inlineStr">
-        <is>
-          <t>Rendimiento</t>
-        </is>
-      </c>
-      <c r="I56" s="126" t="inlineStr">
-        <is>
-          <t>Vr Unit.</t>
-        </is>
-      </c>
-      <c r="J56" s="126" t="n"/>
-      <c r="K56" s="45" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A57" s="100" t="n"/>
-      <c r="B57" s="154" t="n"/>
-      <c r="C57" s="154" t="n"/>
-      <c r="D57" s="154" t="n"/>
-      <c r="E57" s="35" t="n"/>
-      <c r="F57" s="46" t="n"/>
-      <c r="G57" s="46" t="n"/>
-      <c r="H57" s="46" t="n"/>
-      <c r="I57" s="37" t="n"/>
-      <c r="J57" s="37" t="n"/>
-      <c r="K57" s="47">
-        <f>F57*IF(H57=0,1,H57)*I57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A58" s="100" t="n"/>
-      <c r="B58" s="154" t="n"/>
-      <c r="C58" s="154" t="n"/>
-      <c r="D58" s="154" t="n"/>
-      <c r="E58" s="35" t="n"/>
-      <c r="F58" s="46" t="n"/>
-      <c r="G58" s="46" t="n"/>
-      <c r="H58" s="46" t="n"/>
-      <c r="I58" s="37" t="n"/>
-      <c r="J58" s="37" t="n"/>
-      <c r="K58" s="47">
-        <f>F58*IF(H58=0,1,H58)*I58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A59" s="100" t="n"/>
-      <c r="B59" s="154" t="n"/>
-      <c r="C59" s="154" t="n"/>
-      <c r="D59" s="154" t="n"/>
-      <c r="E59" s="35" t="n"/>
-      <c r="F59" s="46" t="n"/>
-      <c r="G59" s="46" t="n"/>
-      <c r="H59" s="46" t="n"/>
-      <c r="I59" s="37" t="n"/>
-      <c r="J59" s="37" t="n"/>
-      <c r="K59" s="47">
-        <f>F59*IF(H59=0,1,H59)*I59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A60" s="100" t="n"/>
-      <c r="B60" s="154" t="n"/>
-      <c r="C60" s="154" t="n"/>
-      <c r="D60" s="154" t="n"/>
-      <c r="E60" s="35" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="37" t="n"/>
-      <c r="J60" s="37" t="n"/>
-      <c r="K60" s="47">
-        <f>F60*IF(H60=0,1,H60)*I60</f>
-        <v/>
-      </c>
+      <c r="E54" s="154" t="n"/>
+      <c r="F54" s="154" t="n"/>
+      <c r="G54" s="154" t="n"/>
+      <c r="H54" s="154" t="n"/>
+      <c r="I54" s="154" t="n"/>
+      <c r="J54" s="154" t="n"/>
+      <c r="K54" s="52">
+        <f>K51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="19.95" customFormat="1" customHeight="1" s="62">
+      <c r="A55" s="106" t="inlineStr">
+        <is>
+          <t>TOTAL DIRECTO UNITARIO</t>
+        </is>
+      </c>
+      <c r="B55" s="159" t="n"/>
+      <c r="C55" s="159" t="n"/>
+      <c r="D55" s="159" t="n"/>
+      <c r="E55" s="159" t="n"/>
+      <c r="F55" s="159" t="n"/>
+      <c r="G55" s="159" t="n"/>
+      <c r="H55" s="159" t="n"/>
+      <c r="I55" s="159" t="n"/>
+      <c r="J55" s="159" t="n"/>
+      <c r="K55" s="53">
+        <f>SUM(K52:K54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="4.5" customFormat="1" customHeight="1" s="62">
+      <c r="A56" s="54" t="n"/>
+      <c r="B56" s="55" t="n"/>
+      <c r="C56" s="55" t="n"/>
+      <c r="D56" s="55" t="n"/>
+      <c r="E56" s="55" t="n"/>
+      <c r="F56" s="55" t="n"/>
+      <c r="G56" s="55" t="n"/>
+      <c r="H56" s="55" t="n"/>
+      <c r="I56" s="55" t="n"/>
+      <c r="J56" s="55" t="n"/>
+      <c r="K56" s="56" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="62">
+      <c r="A57" s="135" t="inlineStr">
+        <is>
+          <t>ELABORADO POR</t>
+        </is>
+      </c>
+      <c r="B57" s="160" t="n"/>
+      <c r="C57" s="160" t="n"/>
+      <c r="D57" s="160" t="n"/>
+      <c r="E57" s="160" t="n"/>
+      <c r="F57" s="109" t="inlineStr">
+        <is>
+          <t>Vo. Bo. INTERVENTORÍA:</t>
+        </is>
+      </c>
+      <c r="G57" s="161" t="n"/>
+      <c r="H57" s="161" t="n"/>
+      <c r="I57" s="161" t="n"/>
+      <c r="J57" s="161" t="n"/>
+      <c r="K57" s="162" t="n"/>
+    </row>
+    <row r="58" ht="42" customFormat="1" customHeight="1" s="62">
+      <c r="A58" s="57" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="B58" s="111" t="n"/>
+      <c r="C58" s="163" t="n"/>
+      <c r="D58" s="163" t="n"/>
+      <c r="E58" s="163" t="n"/>
+      <c r="F58" s="134" t="inlineStr">
+        <is>
+          <t>FIRMA:</t>
+        </is>
+      </c>
+      <c r="G58" s="113" t="n"/>
+      <c r="H58" s="163" t="n"/>
+      <c r="I58" s="163" t="n"/>
+      <c r="J58" s="163" t="n"/>
+      <c r="K58" s="164" t="n"/>
+    </row>
+    <row r="59" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A59" s="57" t="inlineStr">
+        <is>
+          <t>NOMBRE:</t>
+        </is>
+      </c>
+      <c r="B59" s="111" t="n"/>
+      <c r="C59" s="163" t="n"/>
+      <c r="D59" s="163" t="n"/>
+      <c r="E59" s="163" t="n"/>
+      <c r="F59" s="134" t="inlineStr">
+        <is>
+          <t>NOMBRE:</t>
+        </is>
+      </c>
+      <c r="G59" s="113" t="n"/>
+      <c r="H59" s="163" t="n"/>
+      <c r="I59" s="163" t="n"/>
+      <c r="J59" s="163" t="n"/>
+      <c r="K59" s="164" t="n"/>
+    </row>
+    <row r="60" ht="24.75" customFormat="1" customHeight="1" s="62">
+      <c r="A60" s="57" t="inlineStr">
+        <is>
+          <t>CARGO:</t>
+        </is>
+      </c>
+      <c r="B60" s="111" t="n"/>
+      <c r="C60" s="163" t="n"/>
+      <c r="D60" s="163" t="n"/>
+      <c r="E60" s="163" t="n"/>
+      <c r="F60" s="134" t="inlineStr">
+        <is>
+          <t>CARGO:</t>
+        </is>
+      </c>
+      <c r="G60" s="113" t="n"/>
+      <c r="H60" s="163" t="n"/>
+      <c r="I60" s="163" t="n"/>
+      <c r="J60" s="163" t="n"/>
+      <c r="K60" s="164" t="n"/>
     </row>
     <row r="61" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A61" s="100" t="n"/>
-      <c r="B61" s="154" t="n"/>
-      <c r="C61" s="154" t="n"/>
-      <c r="D61" s="154" t="n"/>
-      <c r="E61" s="35" t="n"/>
-      <c r="F61" s="46" t="n"/>
-      <c r="G61" s="46" t="n"/>
-      <c r="H61" s="46" t="n"/>
-      <c r="I61" s="37" t="n"/>
-      <c r="J61" s="37" t="n"/>
-      <c r="K61" s="47">
-        <f>F61*IF(H61=0,1,H61)*I61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A62" s="100" t="n"/>
-      <c r="B62" s="154" t="n"/>
-      <c r="C62" s="154" t="n"/>
-      <c r="D62" s="154" t="n"/>
-      <c r="E62" s="35" t="n"/>
-      <c r="F62" s="46" t="n"/>
-      <c r="G62" s="46" t="n"/>
-      <c r="H62" s="46" t="n"/>
-      <c r="I62" s="37" t="n"/>
-      <c r="J62" s="37" t="n"/>
-      <c r="K62" s="47">
-        <f>F62*IF(H62=0,1,H62)*I62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A63" s="100" t="n"/>
-      <c r="B63" s="154" t="n"/>
-      <c r="C63" s="154" t="n"/>
-      <c r="D63" s="154" t="n"/>
-      <c r="E63" s="35" t="n"/>
-      <c r="F63" s="46" t="n"/>
-      <c r="G63" s="46" t="n"/>
-      <c r="H63" s="46" t="n"/>
-      <c r="I63" s="37" t="n"/>
-      <c r="J63" s="37" t="n"/>
-      <c r="K63" s="47">
-        <f>F63*IF(H63=0,1,H63)*I63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="15.6" customHeight="1">
-      <c r="A64" s="100" t="n"/>
-      <c r="B64" s="154" t="n"/>
-      <c r="C64" s="154" t="n"/>
-      <c r="D64" s="154" t="n"/>
-      <c r="E64" s="35" t="n"/>
-      <c r="F64" s="46" t="n"/>
-      <c r="G64" s="46" t="n"/>
-      <c r="H64" s="46" t="n"/>
-      <c r="I64" s="37" t="n"/>
-      <c r="J64" s="37" t="n"/>
-      <c r="K64" s="47">
-        <f>F64*IF(H64=0,1,H64)*I64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="15.6" customHeight="1">
-      <c r="A65" s="100" t="n"/>
-      <c r="B65" s="154" t="n"/>
-      <c r="C65" s="154" t="n"/>
-      <c r="D65" s="154" t="n"/>
-      <c r="E65" s="35" t="n"/>
-      <c r="F65" s="46" t="n"/>
-      <c r="G65" s="46" t="n"/>
-      <c r="H65" s="46" t="n"/>
-      <c r="I65" s="37" t="n"/>
-      <c r="J65" s="37" t="n"/>
-      <c r="K65" s="47">
-        <f>F65*IF(H65=0,1,H65)*I65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="15.6" customHeight="1">
-      <c r="A66" s="100" t="n"/>
-      <c r="B66" s="154" t="n"/>
-      <c r="C66" s="154" t="n"/>
-      <c r="D66" s="154" t="n"/>
-      <c r="E66" s="35" t="n"/>
-      <c r="F66" s="46" t="n"/>
-      <c r="G66" s="46" t="n"/>
-      <c r="H66" s="46" t="n"/>
-      <c r="I66" s="37" t="n"/>
-      <c r="J66" s="37" t="n"/>
-      <c r="K66" s="47">
-        <f>F66*IF(H66=0,1,H66)*I66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="15.6" customHeight="1">
-      <c r="A67" s="100" t="n"/>
-      <c r="B67" s="154" t="n"/>
-      <c r="C67" s="154" t="n"/>
-      <c r="D67" s="154" t="n"/>
-      <c r="E67" s="35" t="n"/>
-      <c r="F67" s="46" t="n"/>
-      <c r="G67" s="46" t="n"/>
-      <c r="H67" s="46" t="n"/>
-      <c r="I67" s="37" t="n"/>
-      <c r="J67" s="37" t="n"/>
-      <c r="K67" s="47">
-        <f>F67*IF(H67=0,1,H67)*I67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="15.6" customHeight="1">
-      <c r="A68" s="100" t="n"/>
-      <c r="B68" s="154" t="n"/>
-      <c r="C68" s="154" t="n"/>
-      <c r="D68" s="154" t="n"/>
-      <c r="E68" s="35" t="n"/>
-      <c r="F68" s="46" t="n"/>
-      <c r="G68" s="46" t="n"/>
-      <c r="H68" s="46" t="n"/>
-      <c r="I68" s="37" t="n"/>
-      <c r="J68" s="37" t="n"/>
-      <c r="K68" s="47">
-        <f>F68*IF(H68=0,1,H68)*I68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="15.6" customHeight="1">
-      <c r="A69" s="100" t="n"/>
-      <c r="B69" s="154" t="n"/>
-      <c r="C69" s="154" t="n"/>
-      <c r="D69" s="154" t="n"/>
-      <c r="E69" s="35" t="n"/>
-      <c r="F69" s="46" t="n"/>
-      <c r="G69" s="46" t="n"/>
-      <c r="H69" s="46" t="n"/>
-      <c r="I69" s="37" t="n"/>
-      <c r="J69" s="37" t="n"/>
-      <c r="K69" s="47">
-        <f>F69*IF(H69=0,1,H69)*I69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="15.6" customHeight="1">
-      <c r="A70" s="100" t="n"/>
-      <c r="B70" s="154" t="n"/>
-      <c r="C70" s="154" t="n"/>
-      <c r="D70" s="154" t="n"/>
-      <c r="E70" s="35" t="n"/>
-      <c r="F70" s="46" t="n"/>
-      <c r="G70" s="46" t="n"/>
-      <c r="H70" s="46" t="n"/>
-      <c r="I70" s="37" t="n"/>
-      <c r="J70" s="37" t="n"/>
-      <c r="K70" s="47">
-        <f>F70*IF(H70=0,1,H70)*I70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="15.6" customHeight="1">
-      <c r="A71" s="100" t="n"/>
-      <c r="B71" s="154" t="n"/>
-      <c r="C71" s="154" t="n"/>
-      <c r="D71" s="154" t="n"/>
-      <c r="E71" s="35" t="n"/>
-      <c r="F71" s="46" t="n"/>
-      <c r="G71" s="46" t="n"/>
-      <c r="H71" s="46" t="n"/>
-      <c r="I71" s="37" t="n"/>
-      <c r="J71" s="37" t="n"/>
-      <c r="K71" s="47">
-        <f>F71*IF(H71=0,1,H71)*I71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A72" s="101" t="n"/>
-      <c r="B72" s="154" t="n"/>
-      <c r="C72" s="154" t="n"/>
-      <c r="D72" s="154" t="n"/>
-      <c r="E72" s="102" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EQUIPOS Y HERRAMIENTAS</t>
-        </is>
-      </c>
-      <c r="F72" s="154" t="n"/>
-      <c r="G72" s="154" t="n"/>
-      <c r="H72" s="154" t="n"/>
-      <c r="I72" s="154" t="n"/>
-      <c r="J72" s="154" t="n"/>
-      <c r="K72" s="48">
-        <f>SUM(K57:K71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="24.75" customFormat="1" customHeight="1" s="62">
-      <c r="A73" s="105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Materiales</t>
-        </is>
-      </c>
-      <c r="B73" s="154" t="n"/>
-      <c r="C73" s="154" t="n"/>
-      <c r="D73" s="154" t="n"/>
-      <c r="E73" s="154" t="n"/>
-      <c r="F73" s="154" t="n"/>
-      <c r="G73" s="154" t="n"/>
-      <c r="H73" s="154" t="n"/>
-      <c r="I73" s="154" t="n"/>
-      <c r="J73" s="154" t="n"/>
-      <c r="K73" s="52">
-        <f>K36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="24.75" customFormat="1" customHeight="1" s="62">
-      <c r="A74" s="105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Mano de Obra</t>
-        </is>
-      </c>
-      <c r="B74" s="154" t="n"/>
-      <c r="C74" s="154" t="n"/>
-      <c r="D74" s="154" t="n"/>
-      <c r="E74" s="154" t="n"/>
-      <c r="F74" s="154" t="n"/>
-      <c r="G74" s="154" t="n"/>
-      <c r="H74" s="154" t="n"/>
-      <c r="I74" s="154" t="n"/>
-      <c r="J74" s="154" t="n"/>
-      <c r="K74" s="52">
-        <f>K54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="24.75" customFormat="1" customHeight="1" s="62">
-      <c r="A75" s="105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Equipos y herramientas</t>
-        </is>
-      </c>
-      <c r="B75" s="154" t="n"/>
-      <c r="C75" s="154" t="n"/>
-      <c r="D75" s="154" t="n"/>
-      <c r="E75" s="154" t="n"/>
-      <c r="F75" s="154" t="n"/>
-      <c r="G75" s="154" t="n"/>
-      <c r="H75" s="154" t="n"/>
-      <c r="I75" s="154" t="n"/>
-      <c r="J75" s="154" t="n"/>
-      <c r="K75" s="52">
-        <f>K72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="19.95" customFormat="1" customHeight="1" s="62">
-      <c r="A76" s="106" t="inlineStr">
-        <is>
-          <t>TOTAL DIRECTO UNITARIO</t>
-        </is>
-      </c>
-      <c r="B76" s="159" t="n"/>
-      <c r="C76" s="159" t="n"/>
-      <c r="D76" s="159" t="n"/>
-      <c r="E76" s="159" t="n"/>
-      <c r="F76" s="159" t="n"/>
-      <c r="G76" s="159" t="n"/>
-      <c r="H76" s="159" t="n"/>
-      <c r="I76" s="159" t="n"/>
-      <c r="J76" s="159" t="n"/>
-      <c r="K76" s="53">
-        <f>SUM(K73:K75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="4.5" customFormat="1" customHeight="1" s="62">
-      <c r="A77" s="54" t="n"/>
-      <c r="B77" s="55" t="n"/>
-      <c r="C77" s="55" t="n"/>
-      <c r="D77" s="55" t="n"/>
-      <c r="E77" s="55" t="n"/>
-      <c r="F77" s="55" t="n"/>
-      <c r="G77" s="55" t="n"/>
-      <c r="H77" s="55" t="n"/>
-      <c r="I77" s="55" t="n"/>
-      <c r="J77" s="55" t="n"/>
-      <c r="K77" s="56" t="n"/>
-    </row>
-    <row r="78" ht="15.75" customFormat="1" customHeight="1" s="62">
-      <c r="A78" s="135" t="inlineStr">
-        <is>
-          <t>ELABORADO POR</t>
-        </is>
-      </c>
-      <c r="B78" s="160" t="n"/>
-      <c r="C78" s="160" t="n"/>
-      <c r="D78" s="160" t="n"/>
-      <c r="E78" s="160" t="n"/>
-      <c r="F78" s="109" t="inlineStr">
-        <is>
-          <t>Vo. Bo. INTERVENTORÍA:</t>
-        </is>
-      </c>
-      <c r="G78" s="161" t="n"/>
-      <c r="H78" s="161" t="n"/>
-      <c r="I78" s="161" t="n"/>
-      <c r="J78" s="161" t="n"/>
-      <c r="K78" s="162" t="n"/>
-    </row>
-    <row r="79" ht="42" customFormat="1" customHeight="1" s="62">
-      <c r="A79" s="57" t="inlineStr">
-        <is>
-          <t>FIRMA:</t>
-        </is>
-      </c>
-      <c r="B79" s="111" t="n"/>
-      <c r="C79" s="163" t="n"/>
-      <c r="D79" s="163" t="n"/>
-      <c r="E79" s="163" t="n"/>
-      <c r="F79" s="134" t="inlineStr">
-        <is>
-          <t>FIRMA:</t>
-        </is>
-      </c>
-      <c r="G79" s="113" t="n"/>
-      <c r="H79" s="163" t="n"/>
-      <c r="I79" s="163" t="n"/>
-      <c r="J79" s="163" t="n"/>
-      <c r="K79" s="164" t="n"/>
-    </row>
-    <row r="80" ht="24.75" customFormat="1" customHeight="1" s="62">
-      <c r="A80" s="57" t="inlineStr">
-        <is>
-          <t>NOMBRE:</t>
-        </is>
-      </c>
-      <c r="B80" s="111" t="n"/>
-      <c r="C80" s="163" t="n"/>
-      <c r="D80" s="163" t="n"/>
-      <c r="E80" s="163" t="n"/>
-      <c r="F80" s="134" t="inlineStr">
-        <is>
-          <t>NOMBRE:</t>
-        </is>
-      </c>
-      <c r="G80" s="113" t="n"/>
-      <c r="H80" s="163" t="n"/>
-      <c r="I80" s="163" t="n"/>
-      <c r="J80" s="163" t="n"/>
-      <c r="K80" s="164" t="n"/>
-    </row>
-    <row r="81" ht="24.75" customFormat="1" customHeight="1" s="62">
-      <c r="A81" s="57" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="B81" s="111" t="n"/>
-      <c r="C81" s="163" t="n"/>
-      <c r="D81" s="163" t="n"/>
-      <c r="E81" s="163" t="n"/>
-      <c r="F81" s="134" t="inlineStr">
-        <is>
-          <t>CARGO:</t>
-        </is>
-      </c>
-      <c r="G81" s="113" t="n"/>
-      <c r="H81" s="163" t="n"/>
-      <c r="I81" s="163" t="n"/>
-      <c r="J81" s="163" t="n"/>
-      <c r="K81" s="164" t="n"/>
-    </row>
-    <row r="82" ht="15" customFormat="1" customHeight="1" s="62">
-      <c r="A82" s="59" t="inlineStr">
+      <c r="A61" s="59" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B82" s="114" t="n"/>
-      <c r="C82" s="138" t="n"/>
-      <c r="D82" s="138" t="n"/>
-      <c r="E82" s="138" t="n"/>
-      <c r="F82" s="138" t="n"/>
-      <c r="G82" s="138" t="n"/>
-      <c r="H82" s="138" t="n"/>
-      <c r="I82" s="138" t="n"/>
-      <c r="J82" s="138" t="n"/>
-      <c r="K82" s="60">
+      <c r="B61" s="114" t="n"/>
+      <c r="C61" s="138" t="n"/>
+      <c r="D61" s="138" t="n"/>
+      <c r="E61" s="138" t="n"/>
+      <c r="F61" s="138" t="n"/>
+      <c r="G61" s="138" t="n"/>
+      <c r="H61" s="138" t="n"/>
+      <c r="I61" s="138" t="n"/>
+      <c r="J61" s="138" t="n"/>
+      <c r="K61" s="60">
         <f>K4</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customFormat="1" customHeight="1" s="62"/>
+    <row r="62" ht="15" customFormat="1" customHeight="1" s="62"/>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="70">
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="E55:K55"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="G79:K79"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="G58:K58"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A54:J54"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A33:D33"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="E4:H4"/>
-    <mergeCell ref="G80:K80"/>
-    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A65:D65"/>
     <mergeCell ref="E19:K19"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A55:J55"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="G81:K81"/>
+    <mergeCell ref="G60:K60"/>
     <mergeCell ref="D1:K1"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B82:J82"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="E54:J54"/>
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E40:J40"/>
     <mergeCell ref="J16:J17"/>
-    <mergeCell ref="E72:J72"/>
+    <mergeCell ref="E51:J51"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F78:K78"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F57:K57"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.9840277777777779" bottom="0.9840277777777779" header="0.511811023622047" footer="0.511811023622047"/>
